--- a/docs/copy/izzah-copy-id-en.xlsx
+++ b/docs/copy/izzah-copy-id-en.xlsx
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>day / days</t>
+          <t>days</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>Rendered UPPERCASE, countdown 60→0.</t>
+          <t>Rendered UPPERCASE, countdown 60→0. PLURAL in EN.</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr"/>
@@ -8058,7 +8058,11 @@
           <t>{n} days</t>
         </is>
       </c>
-      <c r="G219" s="5" t="inlineStr"/>
+      <c r="G219" s="5" t="inlineStr">
+        <is>
+          <t>PLURAL in EN.</t>
+        </is>
+      </c>
       <c r="H219" s="6" t="inlineStr"/>
       <c r="I219" s="6" t="inlineStr"/>
     </row>
@@ -9280,7 +9284,7 @@
       </c>
       <c r="G255" s="7" t="inlineStr">
         <is>
-          <t>After 5 wrong PINs: 30 s cooldown.</t>
+          <t>After 5 wrong PINs: 30 s cooldown. PLURAL in EN.</t>
         </is>
       </c>
       <c r="H255" s="6" t="inlineStr"/>

--- a/docs/copy/izzah-copy-id-en.xlsx
+++ b/docs/copy/izzah-copy-id-en.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Glossary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Copy'!$A$1:$I$279</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Copy'!$A$1:$I$281</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Religious'!$A$1:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Glossary'!$A$1:$E$13</definedName>
   </definedNames>
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I279"/>
+  <dimension ref="A1:I281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1039,37 +1039,37 @@
       <c r="I11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>onboarding_progress</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Onboarding (all)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>{step}/6</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>{step}/6</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Placeholder only.</t>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>pin_delete_cd</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>PIN pad</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Hapus</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Delete</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Content description for the backspace key on the PIN pad (accessibility).</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr"/>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>niat_title</t>
+          <t>onboarding_progress</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>1 · Niat</t>
+          <t>Onboarding (all)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1096,15 +1096,19 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Apa yang membuatmu ingin berubah?</t>
+          <t>{step}/6</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>What makes you want to change?</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr"/>
+          <t>{step}/6</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Placeholder only.</t>
+        </is>
+      </c>
       <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" s="6" t="inlineStr"/>
     </row>
@@ -1114,7 +1118,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>niat_subtitle</t>
+          <t>niat_title</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1129,12 +1133,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Pilih yang paling dekat di hati. Ini akan kami ingatkan saat kamu goyah.</t>
+          <t>Apa yang membuatmu ingin berubah?</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Pick what's closest to your heart. We'll remind you of it when you feel shaky.</t>
+          <t>What makes you want to change?</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -1147,7 +1151,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>niat_opt_allah</t>
+          <t>niat_subtitle</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1162,12 +1166,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Dekat dengan Allah</t>
+          <t>Pilih yang paling dekat di hati. Ini akan kami ingatkan saat kamu goyah.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Closer to Allah</t>
+          <t>Pick what's closest to your heart. We'll remind you of it when you feel shaky.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -1180,7 +1184,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>niat_opt_family</t>
+          <t>niat_opt_allah</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1195,12 +1199,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Untuk keluarga</t>
+          <t>Dekat dengan Allah</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>For my family</t>
+          <t>Closer to Allah</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
@@ -1213,7 +1217,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>niat_opt_spouse</t>
+          <t>niat_opt_family</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1228,12 +1232,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Pasangan / calon</t>
+          <t>Untuk keluarga</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>My spouse / future spouse</t>
+          <t>For my family</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr"/>
@@ -1246,7 +1250,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>niat_opt_focus</t>
+          <t>niat_opt_spouse</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1261,12 +1265,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Fokus &amp; produktif</t>
+          <t>Pasangan / calon</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Focus &amp; productivity</t>
+          <t>My spouse / future spouse</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
@@ -1279,7 +1283,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>niat_opt_peace</t>
+          <t>niat_opt_focus</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1294,12 +1298,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Ketenangan pikiran</t>
+          <t>Fokus &amp; produktif</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Peace of mind</t>
+          <t>Focus &amp; productivity</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr"/>
@@ -1312,7 +1316,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>niat_opt_selfrespect</t>
+          <t>niat_opt_peace</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1327,12 +1331,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Harga diri</t>
+          <t>Ketenangan pikiran</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Self-respect</t>
+          <t>Peace of mind</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
@@ -1345,7 +1349,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>niat_note</t>
+          <t>niat_opt_selfrespect</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1360,12 +1364,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Tersimpan hanya di HP-mu.</t>
+          <t>Harga diri</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Saved only on your phone.</t>
+          <t>Self-respect</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
@@ -1378,12 +1382,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>target_title</t>
+          <t>niat_note</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>2 · Target</t>
+          <t>1 · Niat</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1393,12 +1397,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Pilih target pertamamu</t>
+          <t>Tersimpan hanya di HP-mu.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Choose your first goal</t>
+          <t>Saved only on your phone.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
@@ -1411,7 +1415,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>target_subtitle</t>
+          <t>target_title</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1426,12 +1430,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Kami menghitung hari yang kamu jaga. Terpeleset tidak menghapus hitungan.</t>
+          <t>Pilih target pertamamu</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>We count the days you keep. A slip doesn't erase the count.</t>
+          <t>Choose your first goal</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
@@ -1444,7 +1448,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>target_7_title</t>
+          <t>target_subtitle</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1459,12 +1463,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Satu minggu</t>
+          <t>Kami menghitung hari yang kamu jaga. Terpeleset tidak menghapus hitungan.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>One week</t>
+          <t>We count the days you keep. A slip doesn't erase the count.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
@@ -1477,7 +1481,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>target_7_desc</t>
+          <t>target_7_title</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1492,12 +1496,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Langkah pertama</t>
+          <t>Satu minggu</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>A first step</t>
+          <t>One week</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
@@ -1510,7 +1514,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>target_30_title</t>
+          <t>target_7_desc</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1525,12 +1529,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Satu bulan</t>
+          <t>Langkah pertama</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>One month</t>
+          <t>A first step</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
@@ -1543,7 +1547,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>target_30_desc</t>
+          <t>target_30_title</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1558,12 +1562,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Membangun kebiasaan</t>
+          <t>Satu bulan</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Building a habit</t>
+          <t>One month</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
@@ -1576,7 +1580,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>target_40_title</t>
+          <t>target_30_desc</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1591,12 +1595,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Empat puluh hari</t>
+          <t>Membangun kebiasaan</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Forty days</t>
+          <t>Building a habit</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>target_40_desc</t>
+          <t>target_40_title</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1624,12 +1628,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Waktu yang sering disebut untuk perubahan diri</t>
+          <t>Empat puluh hari</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>A span often linked to real self-change</t>
+          <t>Forty days</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
@@ -1642,7 +1646,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>target_90_title</t>
+          <t>target_40_desc</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1657,12 +1661,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Tiga bulan</t>
+          <t>Waktu yang sering disebut untuk perubahan diri</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Three months</t>
+          <t>A span often linked to real self-change</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
@@ -1675,7 +1679,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>target_90_desc</t>
+          <t>target_90_title</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1690,19 +1694,15 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Disarankan · otak mulai pulih</t>
+          <t>Tiga bulan</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Recommended · the brain begins to recover</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>This is a health claim, so consider softening it, e.g. 'Recommended · time for real change'.</t>
-        </is>
-      </c>
+          <t>Three months</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="6" t="inlineStr"/>
       <c r="I31" s="6" t="inlineStr"/>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>rawan_title</t>
+          <t>target_90_desc</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>3 · Jam rawan</t>
+          <t>2 · Target</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1727,15 +1727,19 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Kapan biasanya paling berat?</t>
+          <t>Disarankan · otak mulai pulih</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>When is it usually hardest?</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr"/>
+          <t>Recommended · the brain begins to recover</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>This is a health claim, so consider softening it, e.g. 'Recommended · time for real change'.</t>
+        </is>
+      </c>
       <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" s="6" t="inlineStr"/>
     </row>
@@ -1745,7 +1749,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>rawan_subtitle</t>
+          <t>rawan_title</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1760,12 +1764,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Kami akan lebih dekat di waktu-waktu itu: pengingat, dan pagar untuk aplikasi.</t>
+          <t>Kapan biasanya paling berat?</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>We'll stay closer at those times, with reminders and a fence around certain apps.</t>
+          <t>When is it usually hardest?</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
@@ -1778,7 +1782,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>rawan_opt_late</t>
+          <t>rawan_subtitle</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1793,12 +1797,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Larut malam</t>
+          <t>Kami akan lebih dekat di waktu-waktu itu: pengingat, dan pagar untuk aplikasi.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Late at night</t>
+          <t>We'll stay closer at those times, with reminders and a fence around certain apps.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
@@ -1811,7 +1815,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>rawan_opt_dawn</t>
+          <t>rawan_opt_late</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -1826,12 +1830,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Dini hari</t>
+          <t>Larut malam</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Before dawn</t>
+          <t>Late at night</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
@@ -1844,7 +1848,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>rawan_opt_afternoon</t>
+          <t>rawan_opt_dawn</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1859,12 +1863,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Siang, sendirian</t>
+          <t>Dini hari</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Afternoons, alone</t>
+          <t>Before dawn</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
@@ -1877,7 +1881,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>rawan_opt_social</t>
+          <t>rawan_opt_afternoon</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -1892,12 +1896,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Setelah buka medsos</t>
+          <t>Siang, sendirian</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>After social media</t>
+          <t>Afternoons, alone</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
@@ -1910,7 +1914,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>rawan_opt_stress</t>
+          <t>rawan_opt_social</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1925,12 +1929,12 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Saat stres</t>
+          <t>Setelah buka medsos</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>When stressed</t>
+          <t>After social media</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
@@ -1943,7 +1947,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>rawan_opt_weekend</t>
+          <t>rawan_opt_stress</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -1958,12 +1962,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Akhir pekan</t>
+          <t>Saat stres</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Weekends</t>
+          <t>When stressed</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
@@ -1976,12 +1980,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>izin_title</t>
+          <t>rawan_opt_weekend</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>4 · Izin</t>
+          <t>3 · Jam rawan</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1991,12 +1995,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Izinkan Izzah menjaga waktu rawanmu</t>
+          <t>Akhir pekan</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Let Izzah guard your hard hours</t>
+          <t>Weekends</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
@@ -2004,72 +2008,72 @@
       <c r="I40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="n">
+      <c r="A41" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>izin_subtitle</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>izin_title</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>4 · Izin</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>ANDROID</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>Dengan izin akses penggunaan, Izzah bisa memberi jeda pada aplikasi yang kamu pilih.</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>With usage access, Izzah can put a pause in front of the apps you choose.</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>Original: 'Dengan izin Screen Time…'. Screen Time is iOS-only.</t>
-        </is>
-      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Izinkan Izzah menjaga waktu rawanmu</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Let Izzah guard your hard hours</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>izin_promise_1</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>izin_subtitle</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>4 · Izin</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>Riwayat browsing tidak pernah kami lihat atau simpan.</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>We never see or store your browsing history.</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>ANDROID</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Dengan izin akses penggunaan, Izzah bisa memberi jeda pada aplikasi yang kamu pilih.</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>With usage access, Izzah can put a pause in front of the apps you choose.</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>Original: 'Dengan izin Screen Time…'. Screen Time is iOS-only.</t>
+        </is>
+      </c>
       <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" s="6" t="inlineStr"/>
     </row>
@@ -2079,7 +2083,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>izin_promise_2</t>
+          <t>izin_promise_1</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -2094,12 +2098,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Kamu sendiri yang memilih aplikasi dan jamnya.</t>
+          <t>Riwayat browsing tidak pernah kami lihat atau simpan.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>You choose the apps and the hours yourself.</t>
+          <t>We never see or store your browsing history.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr"/>
@@ -2112,7 +2116,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>izin_promise_3</t>
+          <t>izin_promise_2</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -2127,12 +2131,12 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Bisa dimatikan kapan saja dari Pengaturan.</t>
+          <t>Kamu sendiri yang memilih aplikasi dan jamnya.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>You can turn it off anytime in Settings.</t>
+          <t>You choose the apps and the hours yourself.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
@@ -2140,109 +2144,105 @@
       <c r="I44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="n">
+      <c r="A45" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>izin_cta</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>izin_promise_3</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>4 · Izin</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>ANDROID</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>Berikan izin</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>Grant access</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>Original: 'Izinkan Screen Time'. On Android it opens 2 system settings in turn.</t>
-        </is>
-      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Bisa dimatikan kapan saja dari Pengaturan.</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>You can turn it off anytime in Settings.</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>izin_skip</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>izin_cta</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>4 · Izin</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>Nanti saja</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>Maybe later</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>ANDROID</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>Berikan izin</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Grant access</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>Original: 'Izinkan Screen Time'. On Android it opens 2 system settings in turn.</t>
+        </is>
+      </c>
       <c r="H46" s="6" t="inlineStr"/>
       <c r="I46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="n">
+      <c r="A47" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>izin_perm_usage_title</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>izin_skip</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>4 · Izin</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>Akses penggunaan</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>Usage access</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>Replaces the iOS system alert. Status row #1.</t>
-        </is>
-      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Nanti saja</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Maybe later</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" s="6" t="inlineStr"/>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>izin_perm_usage_desc</t>
+          <t>izin_perm_usage_title</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
@@ -2267,15 +2267,19 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Supaya Izzah tahu kapan aplikasi pilihanmu dibuka.</t>
+          <t>Akses penggunaan</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>So Izzah knows when an app you chose is opened.</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr"/>
+          <t>Usage access</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Replaces the iOS system alert. Status row #1.</t>
+        </is>
+      </c>
       <c r="H48" s="6" t="inlineStr"/>
       <c r="I48" s="6" t="inlineStr"/>
     </row>
@@ -2285,7 +2289,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>izin_perm_overlay_title</t>
+          <t>izin_perm_usage_desc</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -2300,19 +2304,15 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Tampil di atas aplikasi lain</t>
+          <t>Supaya Izzah tahu kapan aplikasi pilihanmu dibuka.</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Display over other apps</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>Status row #2.</t>
-        </is>
-      </c>
+          <t>So Izzah knows when an app you chose is opened.</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" s="6" t="inlineStr"/>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>izin_perm_overlay_desc</t>
+          <t>izin_perm_overlay_title</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
@@ -2337,15 +2337,19 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Supaya layar jeda bisa muncul.</t>
+          <t>Tampil di atas aplikasi lain</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>So the pause screen can appear.</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr"/>
+          <t>Display over other apps</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Status row #2.</t>
+        </is>
+      </c>
       <c r="H50" s="6" t="inlineStr"/>
       <c r="I50" s="6" t="inlineStr"/>
     </row>
@@ -2355,7 +2359,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>izin_perm_on</t>
+          <t>izin_perm_overlay_desc</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -2370,12 +2374,12 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Supaya layar jeda bisa muncul.</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>So the pause screen can appear.</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr"/>
@@ -2388,7 +2392,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>izin_perm_off</t>
+          <t>izin_perm_on</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -2403,12 +2407,12 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Belum</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Not yet</t>
+          <t>On</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr"/>
@@ -2416,35 +2420,35 @@
       <c r="I52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>pin_create_title</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>5 · PIN</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>Buat PIN 4 angka</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>Create a 4-digit PIN</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr"/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>izin_perm_off</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>4 · Izin</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr"/>
       <c r="H53" s="6" t="inlineStr"/>
       <c r="I53" s="6" t="inlineStr"/>
     </row>
@@ -2454,7 +2458,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>pin_create_subtitle</t>
+          <t>pin_create_title</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -2469,12 +2473,12 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Supaya hanya kamu yang bisa membuka Izzah.</t>
+          <t>Buat PIN 4 angka</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>So only you can open Izzah.</t>
+          <t>Create a 4-digit PIN</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
@@ -2482,39 +2486,35 @@
       <c r="I54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="n">
+      <c r="A55" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>pin_confirm_title</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>pin_create_subtitle</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>5 · PIN</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>Ketik ulang PIN-mu</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Enter your PIN again</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>Proposed confirmation step (not in design), so a typo doesn't lock the user out.</t>
-        </is>
-      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Supaya hanya kamu yang bisa membuka Izzah.</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>So only you can open Izzah.</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="6" t="inlineStr"/>
       <c r="I55" s="6" t="inlineStr"/>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>pin_mismatch</t>
+          <t>pin_confirm_title</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
@@ -2539,122 +2539,126 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>PIN tidak sama. Coba lagi.</t>
+          <t>Ketik ulang PIN-mu</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>PINs don't match. Try again.</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr"/>
+          <t>Enter your PIN again</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Proposed confirmation step (not in design), so a typo doesn't lock the user out.</t>
+        </is>
+      </c>
       <c r="H56" s="6" t="inlineStr"/>
       <c r="I56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="n">
+      <c r="A57" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>pin_biometric_toggle</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>pin_mismatch</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>5 · PIN</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>ANDROID</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>Buka juga dengan sidik jari atau wajah</t>
-        </is>
-      </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>Also unlock with fingerprint or face</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>Original: 'Buka juga dengan Face ID'.</t>
-        </is>
-      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>PIN tidak sama. Coba lagi.</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>PINs don't match. Try again.</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr"/>
       <c r="H57" s="6" t="inlineStr"/>
       <c r="I57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="n">
+      <c r="A58" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>keypad_delete_cd</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>5 · PIN / Unlock</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>Hapus angka</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>Delete digit</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>Content description for ⌫.</t>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>pin_biometric_toggle</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>5 · PIN</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>ANDROID</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>Buka juga dengan sidik jari atau wajah</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Also unlock with fingerprint or face</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>Original: 'Buka juga dengan Face ID'.</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>notif_title</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>6 · Notifikasi</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>Pengingat yang tidak membuka rahasiamu</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>Reminders that keep your secret</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr"/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>keypad_delete_cd</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>5 · PIN / Unlock</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Hapus angka</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Delete digit</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Content description for ⌫.</t>
+        </is>
+      </c>
       <c r="H59" s="6" t="inlineStr"/>
       <c r="I59" s="6" t="inlineStr"/>
     </row>
@@ -2664,7 +2668,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>notif_subtitle</t>
+          <t>notif_title</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2679,12 +2683,12 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Isi notifikasi selalu netral. Orang di sebelahmu tidak akan tahu.</t>
+          <t>Pengingat yang tidak membuka rahasiamu</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Notifications are always neutral. The person next to you won't know.</t>
+          <t>Reminders that keep your secret</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr"/>
@@ -2697,7 +2701,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>notif_preview_time</t>
+          <t>notif_subtitle</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -2712,12 +2716,12 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>sekarang</t>
+          <t>Isi notifikasi selalu netral. Orang di sebelahmu tidak akan tahu.</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>now</t>
+          <t>Notifications are always neutral. The person next to you won't know.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr"/>
@@ -2730,7 +2734,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>notif_preview_body</t>
+          <t>notif_preview_time</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -2745,12 +2749,12 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Waktunya Ashar. Sejenak untuk dirimu.</t>
+          <t>sekarang</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Time for Asr. A moment for yourself.</t>
+          <t>now</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr"/>
@@ -2763,7 +2767,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>notif_opt_prayer</t>
+          <t>notif_preview_body</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -2778,12 +2782,12 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Pengingat sholat</t>
+          <t>Waktunya Ashar. Sejenak untuk dirimu.</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Prayer reminders</t>
+          <t>Time for Asr. A moment for yourself.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr"/>
@@ -2796,7 +2800,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>notif_opt_prayer_desc</t>
+          <t>notif_opt_prayer</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -2811,12 +2815,12 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Lima waktu, isi netral</t>
+          <t>Pengingat sholat</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>All five prayers, neutral wording</t>
+          <t>Prayer reminders</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr"/>
@@ -2829,7 +2833,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>notif_opt_dzikir</t>
+          <t>notif_opt_prayer_desc</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -2844,12 +2848,12 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Dzikir pagi &amp; petang</t>
+          <t>Lima waktu, isi netral</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Morning &amp; evening dhikr</t>
+          <t>All five prayers, neutral wording</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr"/>
@@ -2862,7 +2866,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>notif_opt_dzikir_desc</t>
+          <t>notif_opt_dzikir</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -2877,12 +2881,12 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Setelah Subuh dan Ashar</t>
+          <t>Dzikir pagi &amp; petang</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>After Fajr and Asr</t>
+          <t>Morning &amp; evening dhikr</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr"/>
@@ -2895,7 +2899,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>notif_opt_checkin</t>
+          <t>notif_opt_dzikir_desc</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -2910,12 +2914,12 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Check-in malam</t>
+          <t>Setelah Subuh dan Ashar</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Evening check-in</t>
+          <t>After Fajr and Asr</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
@@ -2928,7 +2932,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>notif_opt_checkin_desc</t>
+          <t>notif_opt_checkin</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -2943,19 +2947,15 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Pukul {time}, sebelum jam rawan</t>
+          <t>Check-in malam</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>At {time}, before the hard hours</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>{time} = 21.30 (ID) / 9:30 PM (EN). Format with the locale, never hardcode it.</t>
-        </is>
-      </c>
+          <t>Evening check-in</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="6" t="inlineStr"/>
       <c r="I68" s="6" t="inlineStr"/>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>notif_cta</t>
+          <t>notif_opt_checkin_desc</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -2980,15 +2980,19 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Izinkan notifikasi</t>
+          <t>Pukul {time}, sebelum jam rawan</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Allow notifications</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr"/>
+          <t>At {time}, before the hard hours</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>{time} = 21.30 (ID) / 9:30 PM (EN). Format with the locale, never hardcode it.</t>
+        </is>
+      </c>
       <c r="H69" s="6" t="inlineStr"/>
       <c r="I69" s="6" t="inlineStr"/>
     </row>
@@ -2998,12 +3002,12 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>done_day_label</t>
+          <t>notif_cta</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Selesai</t>
+          <t>6 · Notifikasi</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -3013,12 +3017,12 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Hari pertama · {hijri}</t>
+          <t>Izinkan notifikasi</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Day one · {hijri}</t>
+          <t>Allow notifications</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr"/>
@@ -3031,7 +3035,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>done_journey</t>
+          <t>done_day_label</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -3046,12 +3050,12 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Perjalanan {target} hari dimulai hari ini.</t>
+          <t>Hari pertama · {hijri}</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Your {target}-day journey starts today.</t>
+          <t>Day one · {hijri}</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr"/>
@@ -3064,7 +3068,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>done_hint</t>
+          <t>done_journey</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -3079,12 +3083,12 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Kalau dorongan datang, tombol Jeda selalu ada di tengah bawah.</t>
+          <t>Perjalanan {target} hari dimulai hari ini.</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>If an urge comes, the Pause button is always at the bottom center.</t>
+          <t>Your {target}-day journey starts today.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr"/>
@@ -3097,7 +3101,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>done_cta</t>
+          <t>done_hint</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -3112,12 +3116,12 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Masuk ke Beranda</t>
+          <t>Kalau dorongan datang, tombol Jeda selalu ada di tengah bawah.</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Go to Home</t>
+          <t>If an urge comes, the Pause button is always at the bottom center.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr"/>
@@ -3130,12 +3134,12 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>tab_home</t>
+          <t>done_cta</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Tab bar</t>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3145,12 +3149,12 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Beranda</t>
+          <t>Masuk ke Beranda</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Go to Home</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr"/>
@@ -3163,7 +3167,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>tab_progress</t>
+          <t>tab_home</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -3178,12 +3182,12 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Progres</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr"/>
@@ -3196,7 +3200,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>tab_jeda</t>
+          <t>tab_progress</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -3211,19 +3215,15 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Jeda</t>
+          <t>Progres</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Pause</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>Center button. Option: keep 'Jeda' in EN as a brand word.</t>
-        </is>
-      </c>
+          <t>Progress</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr"/>
       <c r="H76" s="6" t="inlineStr"/>
       <c r="I76" s="6" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>tab_protect</t>
+          <t>tab_jeda</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -3248,15 +3248,19 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Lindungi</t>
+          <t>Jeda</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Protect</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr"/>
+          <t>Pause</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Center button. Option: keep 'Jeda' in EN as a brand word.</t>
+        </is>
+      </c>
       <c r="H77" s="6" t="inlineStr"/>
       <c r="I77" s="6" t="inlineStr"/>
     </row>
@@ -3266,7 +3270,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>tab_settings</t>
+          <t>tab_protect</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -3281,12 +3285,12 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Lindungi</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr"/>
@@ -3299,12 +3303,12 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>home_greeting</t>
+          <t>tab_settings</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Beranda</t>
+          <t>Tab bar</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -3314,19 +3318,15 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Assalamu’alaikum</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Assalamu’alaikum</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>Kept as-is in EN.</t>
-        </is>
-      </c>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="6" t="inlineStr"/>
       <c r="I79" s="6" t="inlineStr"/>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>home_date_line</t>
+          <t>home_greeting</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>{weekday} · {hijri}</t>
+          <t>Assalamu’alaikum</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>{weekday} · {hijri}</t>
+          <t>Assalamu’alaikum</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Example: 'Selasa · 13 Rabiul Akhir 1448 H' / 'Tuesday · 13 Rabi' al-Thani 1448 AH'.</t>
+          <t>Kept as-is in EN.</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>home_hero_label</t>
+          <t>home_date_line</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -3388,17 +3388,17 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Kamu sudah terjaga</t>
+          <t>{weekday} · {hijri}</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>You've kept</t>
+          <t>{weekday} · {hijri}</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Rendered UPPERCASE. Reads with the big number: 'YOU'VE KEPT 42 days'.</t>
+          <t>Example: 'Selasa · 13 Rabiul Akhir 1448 H' / 'Tuesday · 13 Rabi' al-Thani 1448 AH'.</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr"/>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>home_hero_unit</t>
+          <t>home_hero_label</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>hari</t>
+          <t>Kamu sudah terjaga</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>You've kept</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>PLURAL in EN (1 day, 2 days). ID has no plural.</t>
+          <t>Rendered UPPERCASE. Reads with the big number: 'YOU'VE KEPT 42 days'.</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr"/>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>home_today_clock</t>
+          <t>home_hero_unit</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -3462,15 +3462,19 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>hari ini · {time}</t>
+          <t>hari</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>today · {time}</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr"/>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>PLURAL in EN (1 day, 2 days). ID has no plural.</t>
+        </is>
+      </c>
       <c r="H83" s="6" t="inlineStr"/>
       <c r="I83" s="6" t="inlineStr"/>
     </row>
@@ -3480,7 +3484,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>home_shortcut_dzikir</t>
+          <t>home_today_clock</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -3495,12 +3499,12 @@
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Dzikir</t>
+          <t>hari ini · {time}</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Dhikr</t>
+          <t>today · {time}</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr"/>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>home_shortcut_sholat</t>
+          <t>home_shortcut_dzikir</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -3528,12 +3532,12 @@
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Sholat</t>
+          <t>Dzikir</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Prayer</t>
+          <t>Dhikr</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr"/>
@@ -3546,7 +3550,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>home_shortcut_jurnal</t>
+          <t>home_shortcut_sholat</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -3561,12 +3565,12 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Jurnal</t>
+          <t>Sholat</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Journal</t>
+          <t>Prayer</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr"/>
@@ -3579,7 +3583,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>home_shortcut_doa</t>
+          <t>home_shortcut_jurnal</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -3594,12 +3598,12 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Doa</t>
+          <t>Jurnal</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Dua</t>
+          <t>Journal</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr"/>
@@ -3612,7 +3616,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>home_bars_caption</t>
+          <t>home_shortcut_doa</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -3627,12 +3631,12 @@
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>{kept} dari {target} hari menuju target pertamamu</t>
+          <t>Doa</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>{kept} of {target} days toward your first goal</t>
+          <t>Dua</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr"/>
@@ -3645,7 +3649,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>home_bars_hint</t>
+          <t>home_bars_caption</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -3660,12 +3664,12 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Ketuk batang untuk detail · lihat semua →</t>
+          <t>{kept} dari {target} hari menuju target pertamamu</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Tap a bar for details · see all →</t>
+          <t>{kept} of {target} days toward your first goal</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr"/>
@@ -3678,7 +3682,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>home_prayer_card</t>
+          <t>home_bars_hint</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -3693,19 +3697,15 @@
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Sholat hari ini · {done}/5</t>
+          <t>Ketuk batang untuk detail · lihat semua →</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Today's prayers · {done}/5</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>Rendered UPPERCASE.</t>
-        </is>
-      </c>
+          <t>Tap a bar for details · see all →</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr"/>
       <c r="H90" s="6" t="inlineStr"/>
       <c r="I90" s="6" t="inlineStr"/>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>home_next_prayer</t>
+          <t>home_prayer_card</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -3730,15 +3730,19 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>{prayer} · {time}</t>
+          <t>Sholat hari ini · {done}/5</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>{prayer} · {time}</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr"/>
+          <t>Today's prayers · {done}/5</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Rendered UPPERCASE.</t>
+        </is>
+      </c>
       <c r="H91" s="6" t="inlineStr"/>
       <c r="I91" s="6" t="inlineStr"/>
     </row>
@@ -3748,7 +3752,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>home_prayers_complete</t>
+          <t>home_next_prayer</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -3763,12 +3767,12 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Alhamdulillah, lengkap</t>
+          <t>{prayer} · {time}</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Alhamdulillah, all done</t>
+          <t>{prayer} · {time}</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr"/>
@@ -3781,7 +3785,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>home_dzikir_tag</t>
+          <t>home_prayers_complete</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -3796,12 +3800,12 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Al-Ma’tsurat · 7 mnt</t>
+          <t>Alhamdulillah, lengkap</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Al-Ma’thurat · 7 min</t>
+          <t>Alhamdulillah, all done</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr"/>
@@ -3814,7 +3818,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>home_dzikir_card</t>
+          <t>home_dzikir_tag</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -3829,89 +3833,89 @@
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Dzikir petang hari ini</t>
+          <t>Al-Ma’tsurat · 7 mnt</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Today's evening dhikr</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>Becomes 'Dzikir pagi hari ini' / 'Today's morning dhikr' before Asr (proposed).</t>
-        </is>
-      </c>
+          <t>Al-Ma’thurat · 7 min</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr"/>
       <c r="H94" s="6" t="inlineStr"/>
       <c r="I94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="7" t="n">
+      <c r="A95" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>home_dzikir_card_morning</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>home_dzikir_card</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>Beranda</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>Dzikir pagi hari ini</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Today's morning dhikr</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>Morning variant (proposed).</t>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Dzikir petang hari ini</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Today's evening dhikr</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Becomes 'Dzikir pagi hari ini' / 'Today's morning dhikr' before Asr (proposed).</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
       <c r="I95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n">
+      <c r="A96" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>home_slip_prompt</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>home_dzikir_card_morning</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>Beranda</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>Tadi sempat terpeleset? Pintu taubat selalu terbuka.</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>Slipped earlier? The door of repentance is always open.</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>Dzikir pagi hari ini</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>Today's morning dhikr</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>Morning variant (proposed).</t>
+        </is>
+      </c>
       <c r="H96" s="6" t="inlineStr"/>
       <c r="I96" s="6" t="inlineStr"/>
     </row>
@@ -3921,7 +3925,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>home_slip_cta</t>
+          <t>home_slip_prompt</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -3936,12 +3940,12 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Mulai lagi →</t>
+          <t>Tadi sempat terpeleset? Pintu taubat selalu terbuka.</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Begin again →</t>
+          <t>Slipped earlier? The door of repentance is always open.</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr"/>
@@ -3949,74 +3953,70 @@
       <c r="I97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="7" t="n">
+      <c r="A98" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>avatar_cd</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>home_slip_cta</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>Beranda</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>Buka pengaturan</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>Open settings</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>Content description for the avatar.</t>
-        </is>
-      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Mulai lagi →</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Begin again →</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr"/>
       <c r="H98" s="6" t="inlineStr"/>
       <c r="I98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n">
+      <c r="A99" s="7" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>day_title</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>Detail hari</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>Hari ke-{n}</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>Day {n}</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>Rendered UPPERCASE in the sheet.</t>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>avatar_cd</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Beranda</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>Buka pengaturan</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Open settings</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Content description for the avatar.</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -4028,12 +4028,12 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>day_status_kept</t>
+          <t>day_title</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Detail hari / Progres</t>
+          <t>Detail hari</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -4043,15 +4043,19 @@
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Terjaga</t>
+          <t>Hari ke-{n}</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Kept</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr"/>
+          <t>Day {n}</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>Rendered UPPERCASE in the sheet.</t>
+        </is>
+      </c>
       <c r="H100" s="6" t="inlineStr"/>
       <c r="I100" s="6" t="inlineStr"/>
     </row>
@@ -4061,7 +4065,7 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>day_status_slip</t>
+          <t>day_status_kept</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -4076,19 +4080,15 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Terpeleset</t>
+          <t>Terjaga</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Slipped</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>Never use red or 'reset' language for this state.</t>
-        </is>
-      </c>
+          <t>Kept</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr"/>
       <c r="H101" s="6" t="inlineStr"/>
       <c r="I101" s="6" t="inlineStr"/>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>day_status_today</t>
+          <t>day_status_slip</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -4113,15 +4113,19 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Hari ini</t>
+          <t>Terpeleset</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Today</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr"/>
+          <t>Slipped</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Never use red or 'reset' language for this state.</t>
+        </is>
+      </c>
       <c r="H102" s="6" t="inlineStr"/>
       <c r="I102" s="6" t="inlineStr"/>
     </row>
@@ -4131,12 +4135,12 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>day_checkin_yes</t>
+          <t>day_status_today</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Detail hari</t>
+          <t>Detail hari / Progres</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -4146,12 +4150,12 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Check-in · tercatat</t>
+          <t>Hari ini</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Check-in · logged</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr"/>
@@ -4164,7 +4168,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>day_checkin_no</t>
+          <t>day_checkin_yes</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -4179,12 +4183,12 @@
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Tidak ada check-in</t>
+          <t>Check-in · tercatat</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>No check-in</t>
+          <t>Check-in · logged</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr"/>
@@ -4197,7 +4201,7 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>day_note_slip</t>
+          <t>day_checkin_no</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -4212,19 +4216,15 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Terpeleset malam itu, lalu kamu menekan “Mulai lagi” keesokan paginya.</t>
+          <t>Tidak ada check-in</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>You slipped that night, then tapped “Begin again” the next morning.</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>Auto note for a slip day with no journal entry.</t>
-        </is>
-      </c>
+          <t>No check-in</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr"/>
       <c r="H105" s="6" t="inlineStr"/>
       <c r="I105" s="6" t="inlineStr"/>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>day_note_today</t>
+          <t>day_note_slip</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -4249,85 +4249,89 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Hari ini masih berjalan.</t>
+          <t>Terpeleset malam itu, lalu kamu menekan “Mulai lagi” keesokan paginya.</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Today is still in progress.</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr"/>
+          <t>You slipped that night, then tapped “Begin again” the next morning.</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>Auto note for a slip day with no journal entry.</t>
+        </is>
+      </c>
       <c r="H106" s="6" t="inlineStr"/>
       <c r="I106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="7" t="n">
+      <c r="A107" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>day_note_empty</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>day_note_today</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>Detail hari</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Tidak ada catatan.</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>No note.</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>Kept day with no journal entry.</t>
-        </is>
-      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>Hari ini masih berjalan.</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Today is still in progress.</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr"/>
       <c r="H107" s="6" t="inlineStr"/>
       <c r="I107" s="6" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n">
+      <c r="A108" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>common_close</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>day_note_empty</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
         <is>
           <t>Detail hari</t>
         </is>
       </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>Tutup</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr"/>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>Tidak ada catatan.</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>No note.</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>Kept day with no journal entry.</t>
+        </is>
+      </c>
       <c r="H108" s="6" t="inlineStr"/>
       <c r="I108" s="6" t="inlineStr"/>
     </row>
@@ -4337,12 +4341,12 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>jeda_header</t>
+          <t>common_close</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Jeda</t>
+          <t>Detail hari</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -4352,19 +4356,15 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Jeda · {seconds} detik</t>
+          <t>Tutup</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Pause · {seconds} seconds</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>Rendered UPPERCASE, countdown 60→0. PLURAL in EN.</t>
-        </is>
-      </c>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr"/>
       <c r="H109" s="6" t="inlineStr"/>
       <c r="I109" s="6" t="inlineStr"/>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>jeda_reminder</t>
+          <t>jeda_header</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -4389,15 +4389,19 @@
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Ingat {kept} hari yang sudah kamu jaga. Ini juga akan lewat.</t>
+          <t>Jeda · {seconds} detik</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Remember the {kept} days you've kept. This too will pass.</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="inlineStr"/>
+          <t>Pause · {seconds} seconds</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>Rendered UPPERCASE, countdown 60→0. PLURAL in EN.</t>
+        </is>
+      </c>
       <c r="H110" s="6" t="inlineStr"/>
       <c r="I110" s="6" t="inlineStr"/>
     </row>
@@ -4407,7 +4411,7 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>jeda_inhale</t>
+          <t>jeda_reminder</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
@@ -4422,12 +4426,12 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Tarik napas…</t>
+          <t>Ingat {kept} hari yang sudah kamu jaga. Ini juga akan lewat.</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Breathe in…</t>
+          <t>Remember the {kept} days you've kept. This too will pass.</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr"/>
@@ -4440,7 +4444,7 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>jeda_exhale</t>
+          <t>jeda_inhale</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -4455,12 +4459,12 @@
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Hembuskan…</t>
+          <t>Tarik napas…</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Breathe out…</t>
+          <t>Breathe in…</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr"/>
@@ -4473,7 +4477,7 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>jeda_translit</t>
+          <t>jeda_exhale</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
@@ -4488,12 +4492,12 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>Astaghfirullāh al-‘aẓīm · napas ke-{n}</t>
+          <t>Hembuskan…</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>Astaghfirullāh al-‘aẓīm · breath {n}</t>
+          <t>Breathe out…</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr"/>
@@ -4506,7 +4510,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>jeda_calmer</t>
+          <t>jeda_translit</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -4521,12 +4525,12 @@
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Aku sudah lebih tenang</t>
+          <t>Astaghfirullāh al-‘aẓīm · napas ke-{n}</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>I feel calmer now</t>
+          <t>Astaghfirullāh al-‘aẓīm · breath {n}</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr"/>
@@ -4539,7 +4543,7 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>jeda_read_doa</t>
+          <t>jeda_calmer</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -4554,12 +4558,12 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>Baca doa perlindungan</t>
+          <t>Aku sudah lebih tenang</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>Read a dua for protection</t>
+          <t>I feel calmer now</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr"/>
@@ -4572,12 +4576,12 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>progress_title</t>
+          <t>jeda_read_doa</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Progres</t>
+          <t>Jeda</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -4587,12 +4591,12 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Progres</t>
+          <t>Baca doa perlindungan</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Read a dua for protection</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr"/>
@@ -4605,7 +4609,7 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>progress_of_target</t>
+          <t>progress_title</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
@@ -4620,12 +4624,12 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>/ {target} hari</t>
+          <t>Progres</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>/ {target} days</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr"/>
@@ -4638,7 +4642,7 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>progress_summary</t>
+          <t>progress_of_target</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -4653,85 +4657,85 @@
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Hari ke-{day} sejak mulai · {slips} hari terpeleset, semuanya kamu lanjutkan.</t>
+          <t>/ {target} hari</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>Day {day} since you started · {slips} slips, and you kept going after every one.</t>
-        </is>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>PLURAL in EN for {slips}. When slips = 0, use the next row.</t>
-        </is>
-      </c>
+          <t>/ {target} days</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr"/>
       <c r="H118" s="6" t="inlineStr"/>
       <c r="I118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="7" t="n">
+      <c r="A119" s="5" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>progress_summary_noslip</t>
-        </is>
-      </c>
-      <c r="C119" s="7" t="inlineStr">
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>progress_summary</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
         <is>
           <t>Progres</t>
         </is>
       </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t>Hari ke-{day} sejak mulai.</t>
-        </is>
-      </c>
-      <c r="F119" s="7" t="inlineStr">
-        <is>
-          <t>Day {day} since you started.</t>
-        </is>
-      </c>
-      <c r="G119" s="7" t="inlineStr"/>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>Hari ke-{day} sejak mulai · {slips} hari terpeleset, semuanya kamu lanjutkan.</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Day {day} since you started · {slips} slips, and you kept going after every one.</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>PLURAL in EN for {slips}. When slips = 0, use the next row.</t>
+        </is>
+      </c>
       <c r="H119" s="6" t="inlineStr"/>
       <c r="I119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n">
+      <c r="A120" s="7" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>progress_legend_future</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>progress_summary_noslip</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
         <is>
           <t>Progres</t>
         </is>
       </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>Belum dijalani</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>Not yet</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="inlineStr"/>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>Hari ke-{day} sejak mulai.</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>Day {day} since you started.</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr"/>
       <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" s="6" t="inlineStr"/>
     </row>
@@ -4741,7 +4745,7 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>progress_bar_caption</t>
+          <t>progress_legend_future</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
@@ -4756,12 +4760,12 @@
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>Makin tinggi batang, makin banyak sholat dan check-in di hari itu.</t>
+          <t>Belum dijalani</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>The taller the bar, the more prayers and check-ins that day.</t>
+          <t>Not yet</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr"/>
@@ -4774,7 +4778,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>progress_sel_title</t>
+          <t>progress_bar_caption</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -4789,12 +4793,12 @@
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Hari ke-{n} · {date}</t>
+          <t>Makin tinggi batang, makin banyak sholat dan check-in di hari itu.</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>Day {n} · {date}</t>
+          <t>The taller the bar, the more prayers and check-ins that day.</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr"/>
@@ -4807,7 +4811,7 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>progress_sel_sub</t>
+          <t>progress_sel_title</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
@@ -4822,12 +4826,12 @@
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>{hijri} · sholat {done}/5</t>
+          <t>Hari ke-{n} · {date}</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>{hijri} · prayers {done}/5</t>
+          <t>Day {n} · {date}</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr"/>
@@ -4840,7 +4844,7 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>progress_stat_prayer</t>
+          <t>progress_sel_sub</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -4855,12 +4859,12 @@
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>sholat terjaga</t>
+          <t>{hijri} · sholat {done}/5</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>prayers kept</t>
+          <t>{hijri} · prayers {done}/5</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr"/>
@@ -4873,7 +4877,7 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>progress_stat_checkin</t>
+          <t>progress_stat_prayer</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
@@ -4888,12 +4892,12 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>hari check-in</t>
+          <t>sholat terjaga</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>check-in days</t>
+          <t>prayers kept</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr"/>
@@ -4906,7 +4910,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>progress_stat_jeda</t>
+          <t>progress_stat_checkin</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -4921,12 +4925,12 @@
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>jeda berhasil</t>
+          <t>hari check-in</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>pauses completed</t>
+          <t>check-in days</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr"/>
@@ -4939,7 +4943,7 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>progress_insight_title</t>
+          <t>progress_stat_jeda</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
@@ -4954,12 +4958,12 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>Pola yang terlihat</t>
+          <t>jeda berhasil</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>A pattern we noticed</t>
+          <t>pauses completed</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr"/>
@@ -4972,7 +4976,7 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>progress_insight_body</t>
+          <t>progress_insight_title</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
@@ -4987,19 +4991,15 @@
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Kamu paling sering butuh jeda antara pukul {start} dan {end}. Mau diingatkan dzikir sebelum tidur?</t>
+          <t>Pola yang terlihat</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>You most often need a pause between {start} and {end}. Want a dhikr reminder before bed?</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>Show only when there is enough jeda data (proposed: ≥5 pauses).</t>
-        </is>
-      </c>
+          <t>A pattern we noticed</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr"/>
       <c r="H128" s="6" t="inlineStr"/>
       <c r="I128" s="6" t="inlineStr"/>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>progress_remind_cta</t>
+          <t>progress_insight_body</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
@@ -5024,15 +5024,19 @@
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>Ingatkan jam {time}</t>
+          <t>Kamu paling sering butuh jeda antara pukul {start} dan {end}. Mau diingatkan dzikir sebelum tidur?</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>Remind me at {time}</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="inlineStr"/>
+          <t>You most often need a pause between {start} and {end}. Want a dhikr reminder before bed?</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>Show only when there is enough jeda data (proposed: ≥5 pauses).</t>
+        </is>
+      </c>
       <c r="H129" s="6" t="inlineStr"/>
       <c r="I129" s="6" t="inlineStr"/>
     </row>
@@ -5042,7 +5046,7 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>progress_remind_on</t>
+          <t>progress_remind_cta</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
@@ -5057,12 +5061,12 @@
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>✓ Diingatkan jam {time}</t>
+          <t>Ingatkan jam {time}</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>✓ Reminder set for {time}</t>
+          <t>Remind me at {time}</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr"/>
@@ -5075,12 +5079,12 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>sholat_title</t>
+          <t>progress_remind_on</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Sholat</t>
+          <t>Progres</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
@@ -5090,12 +5094,12 @@
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>Sholat hari ini</t>
+          <t>✓ Diingatkan jam {time}</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>Today's prayers</t>
+          <t>✓ Reminder set for {time}</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr"/>
@@ -5108,7 +5112,7 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>sholat_of_five</t>
+          <t>sholat_title</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -5123,12 +5127,12 @@
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>/ 5</t>
+          <t>Sholat hari ini</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>/ 5</t>
+          <t>Today's prayers</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr"/>
@@ -5141,7 +5145,7 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>sholat_location</t>
+          <t>sholat_of_five</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
@@ -5156,12 +5160,12 @@
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>{city} · {hijri}</t>
+          <t>/ 5</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>{city} · {hijri}</t>
+          <t>/ 5</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr"/>
@@ -5174,7 +5178,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>sholat_footer</t>
+          <t>sholat_location</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -5189,12 +5193,12 @@
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Check-in setelah sholat ikut membuat batang hari ini lebih tinggi.</t>
+          <t>{city} · {hijri}</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Checking in after each prayer makes today's bar taller.</t>
+          <t>{city} · {hijri}</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr"/>
@@ -5202,39 +5206,35 @@
       <c r="I134" s="6" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="7" t="n">
+      <c r="A135" s="5" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="7" t="inlineStr">
-        <is>
-          <t>sholat_location_pick</t>
-        </is>
-      </c>
-      <c r="C135" s="7" t="inlineStr">
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>sholat_footer</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
         <is>
           <t>Sholat</t>
         </is>
       </c>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>Pilih kota</t>
-        </is>
-      </c>
-      <c r="F135" s="7" t="inlineStr">
-        <is>
-          <t>Choose city</t>
-        </is>
-      </c>
-      <c r="G135" s="7" t="inlineStr">
-        <is>
-          <t>Fallback when location is off or denied.</t>
-        </is>
-      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>Check-in setelah sholat ikut membuat batang hari ini lebih tinggi.</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Checking in after each prayer makes today's bar taller.</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr"/>
       <c r="H135" s="6" t="inlineStr"/>
       <c r="I135" s="6" t="inlineStr"/>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>sholat_use_location</t>
+          <t>sholat_location_pick</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
@@ -5259,48 +5259,52 @@
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>Pakai lokasi sekarang</t>
+          <t>Pilih kota</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Use current location</t>
-        </is>
-      </c>
-      <c r="G136" s="7" t="inlineStr"/>
+          <t>Choose city</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>Fallback when location is off or denied.</t>
+        </is>
+      </c>
       <c r="H136" s="6" t="inlineStr"/>
       <c r="I136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n">
+      <c r="A137" s="7" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>prayer_fajr</t>
-        </is>
-      </c>
-      <c r="C137" s="5" t="inlineStr">
-        <is>
-          <t>Prayer names</t>
-        </is>
-      </c>
-      <c r="D137" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>Subuh</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>Fajr</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="inlineStr"/>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>sholat_use_location</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>Sholat</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>Pakai lokasi sekarang</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>Use current location</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr"/>
       <c r="H137" s="6" t="inlineStr"/>
       <c r="I137" s="6" t="inlineStr"/>
     </row>
@@ -5310,7 +5314,7 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>prayer_dhuhr</t>
+          <t>prayer_fajr</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
@@ -5325,12 +5329,12 @@
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Dzuhur</t>
+          <t>Subuh</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>Dhuhr</t>
+          <t>Fajr</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr"/>
@@ -5343,7 +5347,7 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>prayer_asr</t>
+          <t>prayer_dhuhr</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
@@ -5358,12 +5362,12 @@
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>Ashar</t>
+          <t>Dzuhur</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>Asr</t>
+          <t>Dhuhr</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr"/>
@@ -5376,7 +5380,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>prayer_maghrib</t>
+          <t>prayer_asr</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
@@ -5391,12 +5395,12 @@
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Maghrib</t>
+          <t>Ashar</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>Maghrib</t>
+          <t>Asr</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr"/>
@@ -5409,7 +5413,7 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>prayer_isha</t>
+          <t>prayer_maghrib</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
@@ -5424,12 +5428,12 @@
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>Isya</t>
+          <t>Maghrib</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>Isha</t>
+          <t>Maghrib</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr"/>
@@ -5442,12 +5446,12 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>dzikir_title</t>
+          <t>prayer_isha</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Dzikir</t>
+          <t>Prayer names</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
@@ -5457,12 +5461,12 @@
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>Dzikir setelah sholat</t>
+          <t>Isya</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>Dhikr after prayer</t>
+          <t>Isha</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr"/>
@@ -5475,7 +5479,7 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>dzikir_hint</t>
+          <t>dzikir_title</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
@@ -5490,12 +5494,12 @@
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>dari 33 · ketuk</t>
+          <t>Dzikir setelah sholat</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>of 33 · tap</t>
+          <t>Dhikr after prayer</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr"/>
@@ -5508,7 +5512,7 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>dzikir_done</t>
+          <t>dzikir_hint</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
@@ -5523,12 +5527,12 @@
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>selesai · 99</t>
+          <t>dari 33 · ketuk</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>done · 99</t>
+          <t>of 33 · tap</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr"/>
@@ -5541,7 +5545,7 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>dzikir_footer</t>
+          <t>dzikir_done</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
@@ -5556,12 +5560,12 @@
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>Getar halus setiap 33. Bisa juga pakai tombol volume.</t>
+          <t>selesai · 99</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>A gentle vibration every 33. You can also use the volume buttons.</t>
+          <t>done · 99</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr"/>
@@ -5569,72 +5573,72 @@
       <c r="I145" s="6" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="7" t="n">
+      <c r="A146" s="5" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="7" t="inlineStr">
-        <is>
-          <t>dzikir_reset_cd</t>
-        </is>
-      </c>
-      <c r="C146" s="7" t="inlineStr">
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>dzikir_footer</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
         <is>
           <t>Dzikir</t>
         </is>
       </c>
-      <c r="D146" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="inlineStr">
-        <is>
-          <t>Ulangi dari awal</t>
-        </is>
-      </c>
-      <c r="F146" s="7" t="inlineStr">
-        <is>
-          <t>Start over</t>
-        </is>
-      </c>
-      <c r="G146" s="7" t="inlineStr">
-        <is>
-          <t>Content description for ↺.</t>
-        </is>
-      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>Getar halus setiap 33. Bisa juga pakai tombol volume.</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>A gentle vibration every 33. You can also use the volume buttons.</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr"/>
       <c r="H146" s="6" t="inlineStr"/>
       <c r="I146" s="6" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="n">
+      <c r="A147" s="7" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="5" t="inlineStr">
-        <is>
-          <t>doa_title</t>
-        </is>
-      </c>
-      <c r="C147" s="5" t="inlineStr">
-        <is>
-          <t>Doa</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E147" s="5" t="inlineStr">
-        <is>
-          <t>Doa saat goyah</t>
-        </is>
-      </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>Duas for shaky moments</t>
-        </is>
-      </c>
-      <c r="G147" s="5" t="inlineStr"/>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>dzikir_reset_cd</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>Dzikir</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>Ulangi dari awal</t>
+        </is>
+      </c>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>Start over</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>Content description for ↺.</t>
+        </is>
+      </c>
       <c r="H147" s="6" t="inlineStr"/>
       <c r="I147" s="6" t="inlineStr"/>
     </row>
@@ -5644,7 +5648,7 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>doa_subtitle</t>
+          <t>doa_title</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
@@ -5659,12 +5663,12 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Baca pelan-pelan. Tidak perlu hafal, cukup hadirkan hati.</t>
+          <t>Doa saat goyah</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>Read slowly. No need to memorize. Just bring your heart.</t>
+          <t>Duas for shaky moments</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr"/>
@@ -5677,12 +5681,12 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>jurnal_title</t>
+          <t>doa_subtitle</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Jurnal</t>
+          <t>Doa</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -5692,12 +5696,12 @@
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>Jurnal</t>
+          <t>Baca pelan-pelan. Tidak perlu hafal, cukup hadirkan hati.</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>Journal</t>
+          <t>Read slowly. No need to memorize. Just bring your heart.</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr"/>
@@ -5710,7 +5714,7 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>jurnal_question</t>
+          <t>jurnal_title</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
@@ -5725,12 +5729,12 @@
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>Bagaimana hatimu hari ini?</t>
+          <t>Jurnal</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>How is your heart today?</t>
+          <t>Journal</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr"/>
@@ -5743,7 +5747,7 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>mood_strong</t>
+          <t>jurnal_question</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
@@ -5758,12 +5762,12 @@
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>Kuat</t>
+          <t>Bagaimana hatimu hari ini?</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>How is your heart today?</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr"/>
@@ -5776,7 +5780,7 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>mood_okay</t>
+          <t>mood_strong</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
@@ -5791,12 +5795,12 @@
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Biasa</t>
+          <t>Kuat</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>Okay</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr"/>
@@ -5809,7 +5813,7 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>mood_shaky</t>
+          <t>mood_okay</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
@@ -5824,12 +5828,12 @@
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>Goyah</t>
+          <t>Biasa</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>Shaky</t>
+          <t>Okay</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr"/>
@@ -5842,7 +5846,7 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>mood_heavy</t>
+          <t>mood_shaky</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
@@ -5857,12 +5861,12 @@
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Berat</t>
+          <t>Goyah</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Shaky</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr"/>
@@ -5875,7 +5879,7 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>jurnal_placeholder</t>
+          <t>mood_heavy</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
@@ -5890,12 +5894,12 @@
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>Tulis sedikit. Apa yang membantu, apa yang berat…</t>
+          <t>Berat</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>Write a little. What helped, what felt heavy…</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr"/>
@@ -5908,7 +5912,7 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>jurnal_locked_note</t>
+          <t>jurnal_placeholder</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
@@ -5923,12 +5927,12 @@
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Terkunci dengan PIN. Hanya kamu yang bisa membaca.</t>
+          <t>Tulis sedikit. Apa yang membantu, apa yang berat…</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>Locked with your PIN. Only you can read it.</t>
+          <t>Write a little. What helped, what felt heavy…</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr"/>
@@ -5941,7 +5945,7 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>common_save</t>
+          <t>jurnal_locked_note</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
@@ -5956,12 +5960,12 @@
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>Simpan</t>
+          <t>Terkunci dengan PIN. Hanya kamu yang bisa membaca.</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Locked with your PIN. Only you can read it.</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr"/>
@@ -5974,7 +5978,7 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>jurnal_saved_toast</t>
+          <t>common_save</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
@@ -5989,12 +5993,12 @@
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>Tersimpan. Terima kasih sudah jujur pada dirimu.</t>
+          <t>Simpan</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>Saved. Thank you for being honest with yourself.</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr"/>
@@ -6007,7 +6011,7 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>jurnal_earlier</t>
+          <t>jurnal_saved_toast</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
@@ -6022,12 +6026,12 @@
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>Sebelumnya</t>
+          <t>Tersimpan. Terima kasih sudah jujur pada dirimu.</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>Earlier</t>
+          <t>Saved. Thank you for being honest with yourself.</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr"/>
@@ -6040,7 +6044,7 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>jurnal_entry_meta</t>
+          <t>jurnal_earlier</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
@@ -6055,12 +6059,12 @@
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>{weekday} · {mood}</t>
+          <t>Sebelumnya</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>{weekday} · {mood}</t>
+          <t>Earlier</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr"/>
@@ -6068,72 +6072,72 @@
       <c r="I160" s="6" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="7" t="n">
+      <c r="A161" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="B161" s="7" t="inlineStr">
-        <is>
-          <t>jurnal_empty</t>
-        </is>
-      </c>
-      <c r="C161" s="7" t="inlineStr">
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>jurnal_entry_meta</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
         <is>
           <t>Jurnal</t>
         </is>
       </c>
-      <c r="D161" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E161" s="7" t="inlineStr">
-        <is>
-          <t>Belum ada catatan. Tulisan pertamamu akan muncul di sini.</t>
-        </is>
-      </c>
-      <c r="F161" s="7" t="inlineStr">
-        <is>
-          <t>No entries yet. Your first one will show up here.</t>
-        </is>
-      </c>
-      <c r="G161" s="7" t="inlineStr">
-        <is>
-          <t>Empty state (design shows sample entries only).</t>
-        </is>
-      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>{weekday} · {mood}</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>{weekday} · {mood}</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr"/>
       <c r="H161" s="6" t="inlineStr"/>
       <c r="I161" s="6" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="n">
+      <c r="A162" s="7" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="5" t="inlineStr">
-        <is>
-          <t>mulai_title</t>
-        </is>
-      </c>
-      <c r="C162" s="5" t="inlineStr">
-        <is>
-          <t>Mulai lagi</t>
-        </is>
-      </c>
-      <c r="D162" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="inlineStr">
-        <is>
-          <t>Terpeleset bukan akhir perjalanan.</t>
-        </is>
-      </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>A slip is not the end of the journey.</t>
-        </is>
-      </c>
-      <c r="G162" s="5" t="inlineStr"/>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>jurnal_empty</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>Jurnal</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>Belum ada catatan. Tulisan pertamamu akan muncul di sini.</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>No entries yet. Your first one will show up here.</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>Empty state (design shows sample entries only).</t>
+        </is>
+      </c>
       <c r="H162" s="6" t="inlineStr"/>
       <c r="I162" s="6" t="inlineStr"/>
     </row>
@@ -6143,7 +6147,7 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>mulai_body</t>
+          <t>mulai_title</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
@@ -6158,12 +6162,12 @@
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>{kept} hari yang kamu jaga tetap tercatat. Hari ini cukup jadi satu titik redup di antaranya.</t>
+          <t>Terpeleset bukan akhir perjalanan.</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>The {kept} days you've kept still count. Today is just one dim dot among them.</t>
+          <t>A slip is not the end of the journey.</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr"/>
@@ -6176,7 +6180,7 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>mulai_step_1</t>
+          <t>mulai_body</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
@@ -6191,12 +6195,12 @@
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Istighfar</t>
+          <t>{kept} hari yang kamu jaga tetap tercatat. Hari ini cukup jadi satu titik redup di antaranya.</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>Istighfar</t>
+          <t>The {kept} days you've kept still count. Today is just one dim dot among them.</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr"/>
@@ -6209,7 +6213,7 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>mulai_step_1_desc</t>
+          <t>mulai_step_1</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
@@ -6224,12 +6228,12 @@
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>Astaghfirullāh, 3×</t>
+          <t>Istighfar</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>Astaghfirullāh, 3×</t>
+          <t>Istighfar</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr"/>
@@ -6242,7 +6246,7 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>mulai_step_2</t>
+          <t>mulai_step_1_desc</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
@@ -6257,12 +6261,12 @@
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Wudhu &amp; sholat taubat</t>
+          <t>Astaghfirullāh, 3×</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>Wudu &amp; the prayer of repentance</t>
+          <t>Astaghfirullāh, 3×</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr"/>
@@ -6275,7 +6279,7 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>mulai_step_2_desc</t>
+          <t>mulai_step_2</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
@@ -6290,12 +6294,12 @@
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>2 rakaat, kapan pun kamu siap</t>
+          <t>Wudhu &amp; sholat taubat</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>2 rak‘ahs, whenever you're ready</t>
+          <t>Wudu &amp; the prayer of repentance</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr"/>
@@ -6308,7 +6312,7 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>mulai_step_3</t>
+          <t>mulai_step_2_desc</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
@@ -6323,12 +6327,12 @@
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>Satu langkah kecil</t>
+          <t>2 rakaat, kapan pun kamu siap</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>One small step</t>
+          <t>2 rak‘ahs, whenever you're ready</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr"/>
@@ -6341,7 +6345,7 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>mulai_step_3_desc</t>
+          <t>mulai_step_3</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
@@ -6356,12 +6360,12 @@
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>Hapus satu pemicu, misalnya satu aplikasi</t>
+          <t>Satu langkah kecil</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>Remove one trigger, like a single app</t>
+          <t>One small step</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr"/>
@@ -6374,7 +6378,7 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>mulai_triggers_title</t>
+          <t>mulai_step_3_desc</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
@@ -6389,12 +6393,12 @@
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>Apa pemicunya? (hanya untukmu)</t>
+          <t>Hapus satu pemicu, misalnya satu aplikasi</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>What triggered it? (just for you)</t>
+          <t>Remove one trigger, like a single app</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr"/>
@@ -6407,7 +6411,7 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>trigger_alone_night</t>
+          <t>mulai_triggers_title</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
@@ -6422,12 +6426,12 @@
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>Sendirian malam</t>
+          <t>Apa pemicunya? (hanya untukmu)</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>Alone at night</t>
+          <t>What triggered it? (just for you)</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr"/>
@@ -6440,7 +6444,7 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>trigger_bored</t>
+          <t>trigger_alone_night</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
@@ -6455,12 +6459,12 @@
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Bosan</t>
+          <t>Sendirian malam</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>Bored</t>
+          <t>Alone at night</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr"/>
@@ -6473,7 +6477,7 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>trigger_work_stress</t>
+          <t>trigger_bored</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
@@ -6488,12 +6492,12 @@
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>Stres kerja</t>
+          <t>Bosan</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>Work stress</t>
+          <t>Bored</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr"/>
@@ -6506,7 +6510,7 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>trigger_social</t>
+          <t>trigger_work_stress</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
@@ -6521,12 +6525,12 @@
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Media sosial</t>
+          <t>Stres kerja</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>Social media</t>
+          <t>Work stress</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr"/>
@@ -6539,7 +6543,7 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>trigger_tired</t>
+          <t>trigger_social</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
@@ -6554,12 +6558,12 @@
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>Lelah</t>
+          <t>Media sosial</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>Tired</t>
+          <t>Social media</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr"/>
@@ -6572,7 +6576,7 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>trigger_no_sleep</t>
+          <t>trigger_tired</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
@@ -6587,12 +6591,12 @@
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Sulit tidur</t>
+          <t>Lelah</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>Couldn't sleep</t>
+          <t>Tired</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr"/>
@@ -6605,7 +6609,7 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>mulai_cta</t>
+          <t>trigger_no_sleep</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
@@ -6620,12 +6624,12 @@
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>Mulai lagi hari ini</t>
+          <t>Sulit tidur</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>Begin again today</t>
+          <t>Couldn't sleep</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr"/>
@@ -6633,72 +6637,72 @@
       <c r="I177" s="6" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="7" t="n">
+      <c r="A178" s="5" t="n">
         <v>177</v>
       </c>
-      <c r="B178" s="7" t="inlineStr">
-        <is>
-          <t>mulai_close_cd</t>
-        </is>
-      </c>
-      <c r="C178" s="7" t="inlineStr">
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>mulai_cta</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
         <is>
           <t>Mulai lagi</t>
         </is>
       </c>
-      <c r="D178" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr">
-        <is>
-          <t>Tutup</t>
-        </is>
-      </c>
-      <c r="F178" s="7" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="G178" s="7" t="inlineStr">
-        <is>
-          <t>Content description for ✕.</t>
-        </is>
-      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>Mulai lagi hari ini</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>Begin again today</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="inlineStr"/>
       <c r="H178" s="6" t="inlineStr"/>
       <c r="I178" s="6" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="n">
+      <c r="A179" s="7" t="n">
         <v>178</v>
       </c>
-      <c r="B179" s="5" t="inlineStr">
-        <is>
-          <t>protect_title</t>
-        </is>
-      </c>
-      <c r="C179" s="5" t="inlineStr">
-        <is>
-          <t>Lindungi</t>
-        </is>
-      </c>
-      <c r="D179" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E179" s="5" t="inlineStr">
-        <is>
-          <t>Lindungi</t>
-        </is>
-      </c>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>Protect</t>
-        </is>
-      </c>
-      <c r="G179" s="5" t="inlineStr"/>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>mulai_close_cd</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>Mulai lagi</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>Tutup</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>Content description for ✕.</t>
+        </is>
+      </c>
       <c r="H179" s="6" t="inlineStr"/>
       <c r="I179" s="6" t="inlineStr"/>
     </row>
@@ -6708,7 +6712,7 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>protect_desc</t>
+          <t>protect_title</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
@@ -6723,12 +6727,12 @@
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Aplikasi tertentu dikunci di jam-jam rawan. Bukan hukuman, hanya pagar kecil supaya kamu tidak berjuang sendirian.</t>
+          <t>Lindungi</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>Chosen apps are locked during your hard hours. Not a punishment, just a small fence so you don't fight alone.</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr"/>
@@ -6741,7 +6745,7 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>protect_schedule</t>
+          <t>protect_desc</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
@@ -6756,12 +6760,12 @@
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>Jadwal</t>
+          <t>Aplikasi tertentu dikunci di jam-jam rawan. Bukan hukuman, hanya pagar kecil supaya kamu tidak berjuang sendirian.</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Chosen apps are locked during your hard hours. Not a punishment, just a small fence so you don't fight alone.</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr"/>
@@ -6774,7 +6778,7 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>slot_tag_risky</t>
+          <t>protect_schedule</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
@@ -6789,12 +6793,12 @@
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Rawan</t>
+          <t>Jadwal</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>High-risk</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr"/>
@@ -6807,7 +6811,7 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>slot_tag_optional</t>
+          <t>slot_tag_risky</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
@@ -6822,12 +6826,12 @@
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>Opsional</t>
+          <t>Rawan</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>High-risk</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr"/>
@@ -6840,7 +6844,7 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>slot_tag_auto</t>
+          <t>slot_tag_optional</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
@@ -6855,12 +6859,12 @@
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Otomatis</t>
+          <t>Opsional</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr"/>
@@ -6873,7 +6877,7 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>slot_1_desc</t>
+          <t>slot_tag_auto</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
@@ -6888,12 +6892,12 @@
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>Setiap hari · dari pola jedamu</t>
+          <t>Otomatis</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>Every day · based on your pauses</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr"/>
@@ -6906,7 +6910,7 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>slot_2_desc</t>
+          <t>slot_1_desc</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
@@ -6921,12 +6925,12 @@
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Senin–Jumat · jam sepi di kantor</t>
+          <t>Setiap hari · dari pola jedamu</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>Mon–Fri · quiet hours at work</t>
+          <t>Every day · based on your pauses</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr"/>
@@ -6939,7 +6943,7 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>slot_3_title</t>
+          <t>slot_2_desc</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
@@ -6954,19 +6958,15 @@
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>Saat sendirian di rumah</t>
+          <t>Senin–Jumat · jam sepi di kantor</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>When alone at home</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr">
-        <is>
-          <t>Needs location permission + geofencing. Proposal: leave out of v1.</t>
-        </is>
-      </c>
+          <t>Mon–Fri · quiet hours at work</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr"/>
       <c r="H187" s="6" t="inlineStr"/>
       <c r="I187" s="6" t="inlineStr"/>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>slot_3_desc</t>
+          <t>slot_3_title</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
@@ -6991,15 +6991,19 @@
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Saat lokasi Rumah &amp; tidak ada jadwal</t>
+          <t>Saat sendirian di rumah</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>When you're at Home &amp; nothing is scheduled</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr"/>
+          <t>When alone at home</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr">
+        <is>
+          <t>Needs location permission + geofencing. Proposal: leave out of v1.</t>
+        </is>
+      </c>
       <c r="H188" s="6" t="inlineStr"/>
       <c r="I188" s="6" t="inlineStr"/>
     </row>
@@ -7009,7 +7013,7 @@
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>protect_locked_apps</t>
+          <t>slot_3_desc</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
@@ -7024,89 +7028,89 @@
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>Yang dikunci · {n} aplikasi</t>
+          <t>Saat lokasi Rumah &amp; tidak ada jadwal</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>Locked · {n} apps</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr">
-        <is>
-          <t>PLURAL in EN (1 app).</t>
-        </is>
-      </c>
+          <t>When you're at Home &amp; nothing is scheduled</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr"/>
       <c r="H189" s="6" t="inlineStr"/>
       <c r="I189" s="6" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="7" t="n">
+      <c r="A190" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="B190" s="7" t="inlineStr">
-        <is>
-          <t>protect_add_app</t>
-        </is>
-      </c>
-      <c r="C190" s="7" t="inlineStr">
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>protect_locked_apps</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
         <is>
           <t>Lindungi</t>
         </is>
       </c>
-      <c r="D190" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E190" s="7" t="inlineStr">
-        <is>
-          <t>+ Tambah aplikasi</t>
-        </is>
-      </c>
-      <c r="F190" s="7" t="inlineStr">
-        <is>
-          <t>+ Add app</t>
-        </is>
-      </c>
-      <c r="G190" s="7" t="inlineStr">
-        <is>
-          <t>Opens the installed-app picker (replaces iOS FamilyActivityPicker).</t>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="inlineStr">
+        <is>
+          <t>Yang dikunci · {n} aplikasi</t>
+        </is>
+      </c>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>Locked · {n} apps</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t>PLURAL in EN (1 app).</t>
         </is>
       </c>
       <c r="H190" s="6" t="inlineStr"/>
       <c r="I190" s="6" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="5" t="n">
+      <c r="A191" s="7" t="n">
         <v>190</v>
       </c>
-      <c r="B191" s="5" t="inlineStr">
-        <is>
-          <t>protect_when_opened</t>
-        </is>
-      </c>
-      <c r="C191" s="5" t="inlineStr">
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>protect_add_app</t>
+        </is>
+      </c>
+      <c r="C191" s="7" t="inlineStr">
         <is>
           <t>Lindungi</t>
         </is>
       </c>
-      <c r="D191" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E191" s="5" t="inlineStr">
-        <is>
-          <t>Saat dibuka</t>
-        </is>
-      </c>
-      <c r="F191" s="5" t="inlineStr">
-        <is>
-          <t>When opened</t>
-        </is>
-      </c>
-      <c r="G191" s="5" t="inlineStr"/>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>+ Tambah aplikasi</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>+ Add app</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>Opens the installed-app picker (replaces iOS FamilyActivityPicker).</t>
+        </is>
+      </c>
       <c r="H191" s="6" t="inlineStr"/>
       <c r="I191" s="6" t="inlineStr"/>
     </row>
@@ -7116,7 +7120,7 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>mode_gentle</t>
+          <t>protect_when_opened</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
@@ -7131,12 +7135,12 @@
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Pengingat lembut</t>
+          <t>Saat dibuka</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>Gentle reminder</t>
+          <t>When opened</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr"/>
@@ -7149,7 +7153,7 @@
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>mode_gentle_desc</t>
+          <t>mode_gentle</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
@@ -7164,12 +7168,12 @@
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>Muncul pesan, tetap bisa lanjut</t>
+          <t>Pengingat lembut</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>A message appears, you can still continue</t>
+          <t>Gentle reminder</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr"/>
@@ -7182,7 +7186,7 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>mode_pause</t>
+          <t>mode_gentle_desc</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
@@ -7197,12 +7201,12 @@
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Jeda 60 detik dulu</t>
+          <t>Muncul pesan, tetap bisa lanjut</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>60-second pause first</t>
+          <t>A message appears, you can still continue</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr"/>
@@ -7215,7 +7219,7 @@
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>mode_pause_desc</t>
+          <t>mode_pause</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
@@ -7230,12 +7234,12 @@
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>Napas dulu, lalu boleh buka 5 menit</t>
+          <t>Jeda 60 detik dulu</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>Breathe first, then it opens for 5 minutes</t>
+          <t>60-second pause first</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr"/>
@@ -7248,7 +7252,7 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>mode_full</t>
+          <t>mode_pause_desc</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
@@ -7263,12 +7267,12 @@
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Kunci penuh</t>
+          <t>Napas dulu, lalu boleh buka 5 menit</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>Full lock</t>
+          <t>Breathe first, then it opens for 5 minutes</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr"/>
@@ -7281,7 +7285,7 @@
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>mode_full_desc</t>
+          <t>mode_full</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
@@ -7296,12 +7300,12 @@
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>Tidak bisa dibuka sampai jadwal selesai</t>
+          <t>Kunci penuh</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>Can't be opened until the schedule ends</t>
+          <t>Full lock</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr"/>
@@ -7314,7 +7318,7 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>protect_preview_shield</t>
+          <t>mode_full_desc</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
@@ -7329,12 +7333,12 @@
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>Lihat tampilan saat terkunci</t>
+          <t>Tidak bisa dibuka sampai jadwal selesai</t>
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>Preview the locked screen</t>
+          <t>Can't be opened until the schedule ends</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr"/>
@@ -7347,12 +7351,12 @@
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>shield_label</t>
+          <t>protect_preview_shield</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>Layar terkunci</t>
+          <t>Lindungi</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
@@ -7362,19 +7366,15 @@
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>Waktu terjaga · sampai {time}</t>
+          <t>Lihat tampilan saat terkunci</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>Guarded hours · until {time}</t>
-        </is>
-      </c>
-      <c r="G199" s="5" t="inlineStr">
-        <is>
-          <t>Rendered UPPERCASE.</t>
-        </is>
-      </c>
+          <t>Preview the locked screen</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="inlineStr"/>
       <c r="H199" s="6" t="inlineStr"/>
       <c r="I199" s="6" t="inlineStr"/>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>shield_title</t>
+          <t>shield_label</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
@@ -7399,89 +7399,93 @@
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Sudah larut. Istirahat dulu, yuk.</t>
+          <t>Waktu terjaga · sampai {time}</t>
         </is>
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
-          <t>It's late. Time to rest, okay?</t>
+          <t>Guarded hours · until {time}</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>Fits a late-night slot only. A daytime variant is proposed below.</t>
+          <t>Rendered UPPERCASE.</t>
         </is>
       </c>
       <c r="H200" s="6" t="inlineStr"/>
       <c r="I200" s="6" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="7" t="n">
+      <c r="A201" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="B201" s="7" t="inlineStr">
-        <is>
-          <t>shield_title_day</t>
-        </is>
-      </c>
-      <c r="C201" s="7" t="inlineStr">
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>shield_title</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
         <is>
           <t>Layar terkunci</t>
         </is>
       </c>
-      <c r="D201" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E201" s="7" t="inlineStr">
-        <is>
-          <t>Sebentar dulu. Tarik napas, yuk.</t>
-        </is>
-      </c>
-      <c r="F201" s="7" t="inlineStr">
-        <is>
-          <t>Hold on a moment. Let's take a breath.</t>
-        </is>
-      </c>
-      <c r="G201" s="7" t="inlineStr">
-        <is>
-          <t>For daytime slots (e.g. 13.00–15.00).</t>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="inlineStr">
+        <is>
+          <t>Sudah larut. Istirahat dulu, yuk.</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>It's late. Time to rest, okay?</t>
+        </is>
+      </c>
+      <c r="G201" s="5" t="inlineStr">
+        <is>
+          <t>Fits a late-night slot only. A daytime variant is proposed below.</t>
         </is>
       </c>
       <c r="H201" s="6" t="inlineStr"/>
       <c r="I201" s="6" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="5" t="n">
+      <c r="A202" s="7" t="n">
         <v>201</v>
       </c>
-      <c r="B202" s="5" t="inlineStr">
-        <is>
-          <t>shield_body</t>
-        </is>
-      </c>
-      <c r="C202" s="5" t="inlineStr">
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>shield_title_day</t>
+        </is>
+      </c>
+      <c r="C202" s="7" t="inlineStr">
         <is>
           <t>Layar terkunci</t>
         </is>
       </c>
-      <c r="D202" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E202" s="5" t="inlineStr">
-        <is>
-          <t>Kamu sendiri yang memasang pagar ini, di saat kamu sedang kuat.</t>
-        </is>
-      </c>
-      <c r="F202" s="5" t="inlineStr">
-        <is>
-          <t>You put up this fence yourself, at a moment you were strong.</t>
-        </is>
-      </c>
-      <c r="G202" s="5" t="inlineStr"/>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>Sebentar dulu. Tarik napas, yuk.</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>Hold on a moment. Let's take a breath.</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>For daytime slots (e.g. 13.00–15.00).</t>
+        </is>
+      </c>
       <c r="H202" s="6" t="inlineStr"/>
       <c r="I202" s="6" t="inlineStr"/>
     </row>
@@ -7491,7 +7495,7 @@
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>shield_take_jeda</t>
+          <t>shield_body</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
@@ -7506,12 +7510,12 @@
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>Ambil jeda 60 detik</t>
+          <t>Kamu sendiri yang memasang pagar ini, di saat kamu sedang kuat.</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>Take a 60-second pause</t>
+          <t>You put up this fence yourself, at a moment you were strong.</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr"/>
@@ -7524,7 +7528,7 @@
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>shield_close_app</t>
+          <t>shield_take_jeda</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
@@ -7539,12 +7543,12 @@
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>Tutup aplikasi</t>
+          <t>Ambil jeda 60 detik</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>Close the app</t>
+          <t>Take a 60-second pause</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr"/>
@@ -7552,72 +7556,72 @@
       <c r="I204" s="6" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="7" t="n">
+      <c r="A205" s="5" t="n">
         <v>204</v>
       </c>
-      <c r="B205" s="7" t="inlineStr">
-        <is>
-          <t>shield_continue</t>
-        </is>
-      </c>
-      <c r="C205" s="7" t="inlineStr">
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>shield_close_app</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
         <is>
           <t>Layar terkunci</t>
         </is>
       </c>
-      <c r="D205" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E205" s="7" t="inlineStr">
-        <is>
-          <t>Tetap lanjutkan</t>
-        </is>
-      </c>
-      <c r="F205" s="7" t="inlineStr">
-        <is>
-          <t>Continue anyway</t>
-        </is>
-      </c>
-      <c r="G205" s="7" t="inlineStr">
-        <is>
-          <t>Needed for 'Pengingat lembut' mode, where the design has no continue button.</t>
-        </is>
-      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>Tutup aplikasi</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>Close the app</t>
+        </is>
+      </c>
+      <c r="G205" s="5" t="inlineStr"/>
       <c r="H205" s="6" t="inlineStr"/>
       <c r="I205" s="6" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="5" t="n">
+      <c r="A206" s="7" t="n">
         <v>205</v>
       </c>
-      <c r="B206" s="5" t="inlineStr">
-        <is>
-          <t>shield_note_gentle</t>
-        </is>
-      </c>
-      <c r="C206" s="5" t="inlineStr">
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>shield_continue</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr">
         <is>
           <t>Layar terkunci</t>
         </is>
       </c>
-      <c r="D206" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E206" s="5" t="inlineStr">
-        <is>
-          <t>Kamu tetap bisa melanjutkan jika memang perlu</t>
-        </is>
-      </c>
-      <c r="F206" s="5" t="inlineStr">
-        <is>
-          <t>You can still continue if you really need to</t>
-        </is>
-      </c>
-      <c r="G206" s="5" t="inlineStr"/>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>Tetap lanjutkan</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>Continue anyway</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>Needed for 'Pengingat lembut' mode, where the design has no continue button.</t>
+        </is>
+      </c>
       <c r="H206" s="6" t="inlineStr"/>
       <c r="I206" s="6" t="inlineStr"/>
     </row>
@@ -7627,7 +7631,7 @@
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>shield_note_pause</t>
+          <t>shield_note_gentle</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
@@ -7642,12 +7646,12 @@
       </c>
       <c r="E207" s="5" t="inlineStr">
         <is>
-          <t>Setelah jeda, aplikasi terbuka 5 menit</t>
+          <t>Kamu tetap bisa melanjutkan jika memang perlu</t>
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>After the pause, the app opens for 5 minutes</t>
+          <t>You can still continue if you really need to</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr"/>
@@ -7660,7 +7664,7 @@
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>shield_note_full</t>
+          <t>shield_note_pause</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
@@ -7675,12 +7679,12 @@
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>Terbuka lagi pukul {time}</t>
+          <t>Setelah jeda, aplikasi terbuka 5 menit</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>Opens again at {time}</t>
+          <t>After the pause, the app opens for 5 minutes</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr"/>
@@ -7693,12 +7697,12 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>settings_title</t>
+          <t>shield_note_full</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Layar terkunci</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
@@ -7708,12 +7712,12 @@
       </c>
       <c r="E209" s="5" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Terbuka lagi pukul {time}</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Opens again at {time}</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr"/>
@@ -7726,7 +7730,7 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>settings_profile_title</t>
+          <t>settings_title</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
@@ -7741,12 +7745,12 @@
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>Akun anonim</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>Anonymous account</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr"/>
@@ -7759,7 +7763,7 @@
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>settings_profile_sub</t>
+          <t>settings_profile_title</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
@@ -7774,12 +7778,12 @@
       </c>
       <c r="E211" s="5" t="inlineStr">
         <is>
-          <t>Tanpa email · data hanya di HP ini</t>
+          <t>Akun anonim</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>No email · data stays on this phone</t>
+          <t>Anonymous account</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr"/>
@@ -7792,7 +7796,7 @@
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>settings_group_privacy</t>
+          <t>settings_profile_sub</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
@@ -7807,12 +7811,12 @@
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>Privasi</t>
+          <t>Tanpa email · data hanya di HP ini</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>Privacy</t>
+          <t>No email · data stays on this phone</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr"/>
@@ -7820,72 +7824,72 @@
       <c r="I212" s="6" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="8" t="n">
+      <c r="A213" s="5" t="n">
         <v>212</v>
       </c>
-      <c r="B213" s="8" t="inlineStr">
-        <is>
-          <t>settings_pin_lock</t>
-        </is>
-      </c>
-      <c r="C213" s="8" t="inlineStr">
+      <c r="B213" s="5" t="inlineStr">
+        <is>
+          <t>settings_group_privacy</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D213" s="8" t="inlineStr">
-        <is>
-          <t>ANDROID</t>
-        </is>
-      </c>
-      <c r="E213" s="8" t="inlineStr">
-        <is>
-          <t>Kunci dengan PIN &amp; sidik jari</t>
-        </is>
-      </c>
-      <c r="F213" s="8" t="inlineStr">
-        <is>
-          <t>Lock with PIN &amp; fingerprint</t>
-        </is>
-      </c>
-      <c r="G213" s="8" t="inlineStr">
-        <is>
-          <t>Original: '…&amp; Face ID'.</t>
-        </is>
-      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="inlineStr">
+        <is>
+          <t>Privasi</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr"/>
       <c r="H213" s="6" t="inlineStr"/>
       <c r="I213" s="6" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="n">
+      <c r="A214" s="8" t="n">
         <v>213</v>
       </c>
-      <c r="B214" s="5" t="inlineStr">
-        <is>
-          <t>settings_disguise</t>
-        </is>
-      </c>
-      <c r="C214" s="5" t="inlineStr">
+      <c r="B214" s="8" t="inlineStr">
+        <is>
+          <t>settings_pin_lock</t>
+        </is>
+      </c>
+      <c r="C214" s="8" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D214" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E214" s="5" t="inlineStr">
-        <is>
-          <t>Ikon &amp; nama samaran</t>
-        </is>
-      </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>Disguised icon &amp; name</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr"/>
+      <c r="D214" s="8" t="inlineStr">
+        <is>
+          <t>ANDROID</t>
+        </is>
+      </c>
+      <c r="E214" s="8" t="inlineStr">
+        <is>
+          <t>Kunci dengan PIN &amp; sidik jari</t>
+        </is>
+      </c>
+      <c r="F214" s="8" t="inlineStr">
+        <is>
+          <t>Lock with PIN &amp; fingerprint</t>
+        </is>
+      </c>
+      <c r="G214" s="8" t="inlineStr">
+        <is>
+          <t>Original: '…&amp; Face ID'.</t>
+        </is>
+      </c>
       <c r="H214" s="6" t="inlineStr"/>
       <c r="I214" s="6" t="inlineStr"/>
     </row>
@@ -7895,7 +7899,7 @@
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>settings_hide_search</t>
+          <t>settings_disguise</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
@@ -7910,89 +7914,89 @@
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>Sembunyikan dari pencarian HP</t>
+          <t>Ikon &amp; nama samaran</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>Hide from phone search</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr">
-        <is>
-          <t>Android has no reliable API for this. Proposal: remove it, or replace it with 'Sembunyikan isi di layar Recent' / 'Hide content in Recents' (FLAG_SECURE).</t>
-        </is>
-      </c>
+          <t>Disguised icon &amp; name</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr"/>
       <c r="H215" s="6" t="inlineStr"/>
       <c r="I215" s="6" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="7" t="n">
+      <c r="A216" s="5" t="n">
         <v>215</v>
       </c>
-      <c r="B216" s="7" t="inlineStr">
-        <is>
-          <t>settings_hide_recents</t>
-        </is>
-      </c>
-      <c r="C216" s="7" t="inlineStr">
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>settings_hide_search</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D216" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E216" s="7" t="inlineStr">
-        <is>
-          <t>Sembunyikan isi di layar Recent</t>
-        </is>
-      </c>
-      <c r="F216" s="7" t="inlineStr">
-        <is>
-          <t>Hide content in Recents</t>
-        </is>
-      </c>
-      <c r="G216" s="7" t="inlineStr">
-        <is>
-          <t>Android replacement for the row above (FLAG_SECURE also blocks screenshots).</t>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="inlineStr">
+        <is>
+          <t>Sembunyikan dari pencarian HP</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>Hide from phone search</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr">
+        <is>
+          <t>Android has no reliable API for this. Proposal: remove it, or replace it with 'Sembunyikan isi di layar Recent' / 'Hide content in Recents' (FLAG_SECURE).</t>
         </is>
       </c>
       <c r="H216" s="6" t="inlineStr"/>
       <c r="I216" s="6" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="n">
+      <c r="A217" s="7" t="n">
         <v>216</v>
       </c>
-      <c r="B217" s="5" t="inlineStr">
-        <is>
-          <t>settings_group_journey</t>
-        </is>
-      </c>
-      <c r="C217" s="5" t="inlineStr">
+      <c r="B217" s="7" t="inlineStr">
+        <is>
+          <t>settings_hide_recents</t>
+        </is>
+      </c>
+      <c r="C217" s="7" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D217" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E217" s="5" t="inlineStr">
-        <is>
-          <t>Perjalanan</t>
-        </is>
-      </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>Journey</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr"/>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="inlineStr">
+        <is>
+          <t>Sembunyikan isi di layar Recent</t>
+        </is>
+      </c>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>Hide content in Recents</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>Android replacement for the row above (FLAG_SECURE also blocks screenshots).</t>
+        </is>
+      </c>
       <c r="H217" s="6" t="inlineStr"/>
       <c r="I217" s="6" t="inlineStr"/>
     </row>
@@ -8002,7 +8006,7 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>settings_target</t>
+          <t>settings_group_journey</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
@@ -8017,12 +8021,12 @@
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Perjalanan</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Journey</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr"/>
@@ -8035,7 +8039,7 @@
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>settings_target_value</t>
+          <t>settings_target</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
@@ -8050,19 +8054,15 @@
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>{n} hari</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>{n} days</t>
-        </is>
-      </c>
-      <c r="G219" s="5" t="inlineStr">
-        <is>
-          <t>PLURAL in EN.</t>
-        </is>
-      </c>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="inlineStr"/>
       <c r="H219" s="6" t="inlineStr"/>
       <c r="I219" s="6" t="inlineStr"/>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>settings_reminders</t>
+          <t>settings_target_value</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
@@ -8087,15 +8087,19 @@
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>Pengingat sholat &amp; dzikir</t>
+          <t>{n} hari</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>Prayer &amp; dhikr reminders</t>
-        </is>
-      </c>
-      <c r="G220" s="5" t="inlineStr"/>
+          <t>{n} days</t>
+        </is>
+      </c>
+      <c r="G220" s="5" t="inlineStr">
+        <is>
+          <t>PLURAL in EN.</t>
+        </is>
+      </c>
       <c r="H220" s="6" t="inlineStr"/>
       <c r="I220" s="6" t="inlineStr"/>
     </row>
@@ -8105,7 +8109,7 @@
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>settings_schedule</t>
+          <t>settings_reminders</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
@@ -8120,12 +8124,12 @@
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>Jadwal waktu terjaga</t>
+          <t>Pengingat sholat &amp; dzikir</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>Guarded-hours schedule</t>
+          <t>Prayer &amp; dhikr reminders</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr"/>
@@ -8138,7 +8142,7 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>settings_group_data</t>
+          <t>settings_schedule</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
@@ -8153,12 +8157,12 @@
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>Data &amp; bantuan</t>
+          <t>Jadwal waktu terjaga</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Data &amp; help</t>
+          <t>Guarded-hours schedule</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr"/>
@@ -8171,7 +8175,7 @@
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>settings_export_delete</t>
+          <t>settings_group_data</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
@@ -8186,12 +8190,12 @@
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>Ekspor &amp; hapus data</t>
+          <t>Data &amp; bantuan</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>Export &amp; delete data</t>
+          <t>Data &amp; help</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr"/>
@@ -8204,7 +8208,7 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>settings_counselor</t>
+          <t>settings_export_delete</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
@@ -8219,19 +8223,15 @@
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>Bicara dengan konselor</t>
+          <t>Ekspor &amp; hapus data</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>Talk to a counselor</t>
-        </is>
-      </c>
-      <c r="G224" s="5" t="inlineStr">
-        <is>
-          <t>Where does it go? Needs a real contact or link before release.</t>
-        </is>
-      </c>
+          <t>Export &amp; delete data</t>
+        </is>
+      </c>
+      <c r="G224" s="5" t="inlineStr"/>
       <c r="H224" s="6" t="inlineStr"/>
       <c r="I224" s="6" t="inlineStr"/>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>settings_about</t>
+          <t>settings_counselor</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
@@ -8256,15 +8256,19 @@
       </c>
       <c r="E225" s="5" t="inlineStr">
         <is>
-          <t>Tentang Izzah</t>
+          <t>Bicara dengan konselor</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>About Izzah</t>
-        </is>
-      </c>
-      <c r="G225" s="5" t="inlineStr"/>
+          <t>Talk to a counselor</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="inlineStr">
+        <is>
+          <t>Where does it go? Needs a real contact or link before release.</t>
+        </is>
+      </c>
       <c r="H225" s="6" t="inlineStr"/>
       <c r="I225" s="6" t="inlineStr"/>
     </row>
@@ -8274,7 +8278,7 @@
       </c>
       <c r="B226" s="7" t="inlineStr">
         <is>
-          <t>settings_language</t>
+          <t>counselor_placeholder</t>
         </is>
       </c>
       <c r="C226" s="7" t="inlineStr">
@@ -8289,52 +8293,52 @@
       </c>
       <c r="E226" s="7" t="inlineStr">
         <is>
-          <t>Bahasa</t>
+          <t>Segera hadir. Kami sedang menyiapkan kontak konselor yang tepercaya.</t>
         </is>
       </c>
       <c r="F226" s="7" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Coming soon. We're preparing a trusted counselor contact.</t>
         </is>
       </c>
       <c r="G226" s="7" t="inlineStr">
         <is>
-          <t>Language picker row, under Privasi or a new 'Umum' group.</t>
+          <t>Shown in the counselor sheet until a real contact or link exists.</t>
         </is>
       </c>
       <c r="H226" s="6" t="inlineStr"/>
       <c r="I226" s="6" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="7" t="n">
+      <c r="A227" s="5" t="n">
         <v>226</v>
       </c>
-      <c r="B227" s="7" t="inlineStr">
-        <is>
-          <t>language_system</t>
-        </is>
-      </c>
-      <c r="C227" s="7" t="inlineStr">
+      <c r="B227" s="5" t="inlineStr">
+        <is>
+          <t>settings_about</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D227" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E227" s="7" t="inlineStr">
-        <is>
-          <t>Ikuti sistem</t>
-        </is>
-      </c>
-      <c r="F227" s="7" t="inlineStr">
-        <is>
-          <t>System default</t>
-        </is>
-      </c>
-      <c r="G227" s="7" t="inlineStr"/>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="inlineStr">
+        <is>
+          <t>Tentang Izzah</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="inlineStr">
+        <is>
+          <t>About Izzah</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="inlineStr"/>
       <c r="H227" s="6" t="inlineStr"/>
       <c r="I227" s="6" t="inlineStr"/>
     </row>
@@ -8344,7 +8348,7 @@
       </c>
       <c r="B228" s="7" t="inlineStr">
         <is>
-          <t>language_id</t>
+          <t>settings_language</t>
         </is>
       </c>
       <c r="C228" s="7" t="inlineStr">
@@ -8359,17 +8363,17 @@
       </c>
       <c r="E228" s="7" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>Bahasa</t>
         </is>
       </c>
       <c r="F228" s="7" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="G228" s="7" t="inlineStr">
         <is>
-          <t>Always shown in its own language.</t>
+          <t>Language picker row, under Privasi or a new 'Umum' group.</t>
         </is>
       </c>
       <c r="H228" s="6" t="inlineStr"/>
@@ -8381,7 +8385,7 @@
       </c>
       <c r="B229" s="7" t="inlineStr">
         <is>
-          <t>language_en</t>
+          <t>language_system</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
@@ -8396,85 +8400,89 @@
       </c>
       <c r="E229" s="7" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Ikuti sistem</t>
         </is>
       </c>
       <c r="F229" s="7" t="inlineStr">
         <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G229" s="7" t="inlineStr">
-        <is>
-          <t>Always shown in its own language.</t>
-        </is>
-      </c>
+          <t>System default</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr"/>
       <c r="H229" s="6" t="inlineStr"/>
       <c r="I229" s="6" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="5" t="n">
+      <c r="A230" s="7" t="n">
         <v>229</v>
       </c>
-      <c r="B230" s="5" t="inlineStr">
-        <is>
-          <t>disguise_title</t>
-        </is>
-      </c>
-      <c r="C230" s="5" t="inlineStr">
-        <is>
-          <t>Ikon samaran</t>
-        </is>
-      </c>
-      <c r="D230" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E230" s="5" t="inlineStr">
-        <is>
-          <t>Ikon samaran</t>
-        </is>
-      </c>
-      <c r="F230" s="5" t="inlineStr">
-        <is>
-          <t>Disguised icon</t>
-        </is>
-      </c>
-      <c r="G230" s="5" t="inlineStr"/>
+      <c r="B230" s="7" t="inlineStr">
+        <is>
+          <t>language_id</t>
+        </is>
+      </c>
+      <c r="C230" s="7" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E230" s="7" t="inlineStr">
+        <is>
+          <t>Bahasa Indonesia</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>Bahasa Indonesia</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t>Always shown in its own language.</t>
+        </is>
+      </c>
       <c r="H230" s="6" t="inlineStr"/>
       <c r="I230" s="6" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="5" t="n">
+      <c r="A231" s="7" t="n">
         <v>230</v>
       </c>
-      <c r="B231" s="5" t="inlineStr">
-        <is>
-          <t>disguise_desc</t>
-        </is>
-      </c>
-      <c r="C231" s="5" t="inlineStr">
-        <is>
-          <t>Ikon samaran</t>
-        </is>
-      </c>
-      <c r="D231" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E231" s="5" t="inlineStr">
-        <is>
-          <t>Ganti ikon dan nama di layar HP supaya tidak menarik perhatian.</t>
-        </is>
-      </c>
-      <c r="F231" s="5" t="inlineStr">
-        <is>
-          <t>Change the icon and name on your home screen so it doesn't draw attention.</t>
-        </is>
-      </c>
-      <c r="G231" s="5" t="inlineStr"/>
+      <c r="B231" s="7" t="inlineStr">
+        <is>
+          <t>language_en</t>
+        </is>
+      </c>
+      <c r="C231" s="7" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="D231" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E231" s="7" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="F231" s="7" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>Always shown in its own language.</t>
+        </is>
+      </c>
       <c r="H231" s="6" t="inlineStr"/>
       <c r="I231" s="6" t="inlineStr"/>
     </row>
@@ -8484,7 +8492,7 @@
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>disguise_izzah</t>
+          <t>disguise_title</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
@@ -8499,12 +8507,12 @@
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>Izzah</t>
+          <t>Ikon samaran</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>Izzah</t>
+          <t>Disguised icon</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr"/>
@@ -8517,7 +8525,7 @@
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>disguise_steps</t>
+          <t>disguise_desc</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
@@ -8532,19 +8540,15 @@
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>Langkah</t>
+          <t>Ganti ikon dan nama di layar HP supaya tidak menarik perhatian.</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G233" s="5" t="inlineStr">
-        <is>
-          <t>This becomes the launcher label, so it's localized too.</t>
-        </is>
-      </c>
+          <t>Change the icon and name on your home screen so it doesn't draw attention.</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="inlineStr"/>
       <c r="H233" s="6" t="inlineStr"/>
       <c r="I233" s="6" t="inlineStr"/>
     </row>
@@ -8554,7 +8558,7 @@
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>disguise_focus</t>
+          <t>disguise_izzah</t>
         </is>
       </c>
       <c r="C234" s="5" t="inlineStr">
@@ -8569,12 +8573,12 @@
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>Fokus</t>
+          <t>Izzah</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>Focus</t>
+          <t>Izzah</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr"/>
@@ -8587,7 +8591,7 @@
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>disguise_notes</t>
+          <t>disguise_steps</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
@@ -8602,52 +8606,52 @@
       </c>
       <c r="E235" s="5" t="inlineStr">
         <is>
-          <t>Catatan</t>
+          <t>Langkah</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="G235" s="5" t="inlineStr"/>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G235" s="5" t="inlineStr">
+        <is>
+          <t>This becomes the launcher label, so it's localized too.</t>
+        </is>
+      </c>
       <c r="H235" s="6" t="inlineStr"/>
       <c r="I235" s="6" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="8" t="n">
+      <c r="A236" s="5" t="n">
         <v>235</v>
       </c>
-      <c r="B236" s="8" t="inlineStr">
-        <is>
-          <t>disguise_footer</t>
-        </is>
-      </c>
-      <c r="C236" s="8" t="inlineStr">
+      <c r="B236" s="5" t="inlineStr">
+        <is>
+          <t>disguise_focus</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="inlineStr">
         <is>
           <t>Ikon samaran</t>
         </is>
       </c>
-      <c r="D236" s="8" t="inlineStr">
-        <is>
-          <t>ANDROID</t>
-        </is>
-      </c>
-      <c r="E236" s="8" t="inlineStr">
-        <is>
-          <t>Nama di notifikasi tetap “Izzah”, tapi isinya selalu netral.</t>
-        </is>
-      </c>
-      <c r="F236" s="8" t="inlineStr">
-        <is>
-          <t>Notifications still show “Izzah”, but their content is always neutral.</t>
-        </is>
-      </c>
-      <c r="G236" s="8" t="inlineStr">
-        <is>
-          <t>Original: 'Notifikasi akan memakai nama yang sama.' Android always shows the application label in notifications; an activity-alias can't change it.</t>
-        </is>
-      </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="inlineStr">
+        <is>
+          <t>Fokus</t>
+        </is>
+      </c>
+      <c r="F236" s="5" t="inlineStr">
+        <is>
+          <t>Focus</t>
+        </is>
+      </c>
+      <c r="G236" s="5" t="inlineStr"/>
       <c r="H236" s="6" t="inlineStr"/>
       <c r="I236" s="6" t="inlineStr"/>
     </row>
@@ -8657,12 +8661,12 @@
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>data_title</t>
+          <t>disguise_notes</t>
         </is>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>Datamu</t>
+          <t>Ikon samaran</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
@@ -8672,12 +8676,12 @@
       </c>
       <c r="E237" s="5" t="inlineStr">
         <is>
-          <t>Datamu</t>
+          <t>Catatan</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>Your data</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr"/>
@@ -8685,35 +8689,39 @@
       <c r="I237" s="6" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="n">
+      <c r="A238" s="8" t="n">
         <v>237</v>
       </c>
-      <c r="B238" s="5" t="inlineStr">
-        <is>
-          <t>data_desc</t>
-        </is>
-      </c>
-      <c r="C238" s="5" t="inlineStr">
-        <is>
-          <t>Datamu</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E238" s="5" t="inlineStr">
-        <is>
-          <t>Semua tersimpan di HP ini. Tidak ada di server kami.</t>
-        </is>
-      </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>Everything is stored on this phone. Nothing is on our servers.</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr"/>
+      <c r="B238" s="8" t="inlineStr">
+        <is>
+          <t>disguise_footer</t>
+        </is>
+      </c>
+      <c r="C238" s="8" t="inlineStr">
+        <is>
+          <t>Ikon samaran</t>
+        </is>
+      </c>
+      <c r="D238" s="8" t="inlineStr">
+        <is>
+          <t>ANDROID</t>
+        </is>
+      </c>
+      <c r="E238" s="8" t="inlineStr">
+        <is>
+          <t>Nama di notifikasi tetap “Izzah”, tapi isinya selalu netral.</t>
+        </is>
+      </c>
+      <c r="F238" s="8" t="inlineStr">
+        <is>
+          <t>Notifications still show “Izzah”, but their content is always neutral.</t>
+        </is>
+      </c>
+      <c r="G238" s="8" t="inlineStr">
+        <is>
+          <t>Original: 'Notifikasi akan memakai nama yang sama.' Android always shows the application label in notifications; an activity-alias can't change it.</t>
+        </is>
+      </c>
       <c r="H238" s="6" t="inlineStr"/>
       <c r="I238" s="6" t="inlineStr"/>
     </row>
@@ -8723,7 +8731,7 @@
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
-          <t>data_export_title</t>
+          <t>data_title</t>
         </is>
       </c>
       <c r="C239" s="5" t="inlineStr">
@@ -8738,12 +8746,12 @@
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
-          <t>Ekspor cadangan</t>
+          <t>Datamu</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>Export a backup</t>
+          <t>Your data</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr"/>
@@ -8756,7 +8764,7 @@
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>data_export_desc</t>
+          <t>data_desc</t>
         </is>
       </c>
       <c r="C240" s="5" t="inlineStr">
@@ -8771,12 +8779,12 @@
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>File terenkripsi dengan PIN-mu. Pakai saat pindah HP.</t>
+          <t>Semua tersimpan di HP ini. Tidak ada di server kami.</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>A file encrypted with your PIN. Use it when you switch phones.</t>
+          <t>Everything is stored on this phone. Nothing is on our servers.</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr"/>
@@ -8789,7 +8797,7 @@
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>data_export_cta</t>
+          <t>data_export_title</t>
         </is>
       </c>
       <c r="C241" s="5" t="inlineStr">
@@ -8804,12 +8812,12 @@
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>Buat file cadangan</t>
+          <t>Ekspor cadangan</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>Create backup file</t>
+          <t>Export a backup</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr"/>
@@ -8817,72 +8825,68 @@
       <c r="I241" s="6" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="7" t="n">
+      <c r="A242" s="5" t="n">
         <v>241</v>
       </c>
-      <c r="B242" s="7" t="inlineStr">
-        <is>
-          <t>data_import_wrong_pin</t>
-        </is>
-      </c>
-      <c r="C242" s="7" t="inlineStr">
+      <c r="B242" s="5" t="inlineStr">
+        <is>
+          <t>data_export_desc</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="inlineStr">
         <is>
           <t>Datamu</t>
         </is>
       </c>
-      <c r="D242" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E242" s="7" t="inlineStr">
-        <is>
-          <t>PIN cadangan tidak cocok.</t>
-        </is>
-      </c>
-      <c r="F242" s="7" t="inlineStr">
-        <is>
-          <t>The backup PIN doesn't match.</t>
-        </is>
-      </c>
-      <c r="G242" s="7" t="inlineStr"/>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E242" s="5" t="inlineStr">
+        <is>
+          <t>File terenkripsi dengan PIN-mu. Pakai saat pindah HP.</t>
+        </is>
+      </c>
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>A file encrypted with your PIN. Use it when you switch phones.</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr"/>
       <c r="H242" s="6" t="inlineStr"/>
       <c r="I242" s="6" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="7" t="n">
+      <c r="A243" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="B243" s="7" t="inlineStr">
-        <is>
-          <t>data_export_done</t>
-        </is>
-      </c>
-      <c r="C243" s="7" t="inlineStr">
+      <c r="B243" s="5" t="inlineStr">
+        <is>
+          <t>data_export_cta</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="inlineStr">
         <is>
           <t>Datamu</t>
         </is>
       </c>
-      <c r="D243" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E243" s="7" t="inlineStr">
-        <is>
-          <t>Cadangan tersimpan.</t>
-        </is>
-      </c>
-      <c r="F243" s="7" t="inlineStr">
-        <is>
-          <t>Backup saved.</t>
-        </is>
-      </c>
-      <c r="G243" s="7" t="inlineStr">
-        <is>
-          <t>Toast after the system save dialog.</t>
-        </is>
-      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="inlineStr">
+        <is>
+          <t>Buat file cadangan</t>
+        </is>
+      </c>
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>Create backup file</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr"/>
       <c r="H243" s="6" t="inlineStr"/>
       <c r="I243" s="6" t="inlineStr"/>
     </row>
@@ -8892,7 +8896,7 @@
       </c>
       <c r="B244" s="7" t="inlineStr">
         <is>
-          <t>data_import_cta</t>
+          <t>data_import_wrong_pin</t>
         </is>
       </c>
       <c r="C244" s="7" t="inlineStr">
@@ -8907,85 +8911,89 @@
       </c>
       <c r="E244" s="7" t="inlineStr">
         <is>
-          <t>Pulihkan dari cadangan</t>
+          <t>PIN cadangan tidak cocok.</t>
         </is>
       </c>
       <c r="F244" s="7" t="inlineStr">
         <is>
-          <t>Restore from backup</t>
-        </is>
-      </c>
-      <c r="G244" s="7" t="inlineStr">
-        <is>
-          <t>Without this, the export is useless on a new phone. Proposed for v1.</t>
-        </is>
-      </c>
+          <t>The backup PIN doesn't match.</t>
+        </is>
+      </c>
+      <c r="G244" s="7" t="inlineStr"/>
       <c r="H244" s="6" t="inlineStr"/>
       <c r="I244" s="6" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="5" t="n">
+      <c r="A245" s="7" t="n">
         <v>244</v>
       </c>
-      <c r="B245" s="5" t="inlineStr">
-        <is>
-          <t>data_delete_title</t>
-        </is>
-      </c>
-      <c r="C245" s="5" t="inlineStr">
+      <c r="B245" s="7" t="inlineStr">
+        <is>
+          <t>data_export_done</t>
+        </is>
+      </c>
+      <c r="C245" s="7" t="inlineStr">
         <is>
           <t>Datamu</t>
         </is>
       </c>
-      <c r="D245" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E245" s="5" t="inlineStr">
-        <is>
-          <t>Hapus semua data</t>
-        </is>
-      </c>
-      <c r="F245" s="5" t="inlineStr">
-        <is>
-          <t>Delete all data</t>
-        </is>
-      </c>
-      <c r="G245" s="5" t="inlineStr"/>
+      <c r="D245" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E245" s="7" t="inlineStr">
+        <is>
+          <t>Cadangan tersimpan.</t>
+        </is>
+      </c>
+      <c r="F245" s="7" t="inlineStr">
+        <is>
+          <t>Backup saved.</t>
+        </is>
+      </c>
+      <c r="G245" s="7" t="inlineStr">
+        <is>
+          <t>Toast after the system save dialog.</t>
+        </is>
+      </c>
       <c r="H245" s="6" t="inlineStr"/>
       <c r="I245" s="6" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="5" t="n">
+      <c r="A246" s="7" t="n">
         <v>245</v>
       </c>
-      <c r="B246" s="5" t="inlineStr">
-        <is>
-          <t>data_delete_desc</t>
-        </is>
-      </c>
-      <c r="C246" s="5" t="inlineStr">
+      <c r="B246" s="7" t="inlineStr">
+        <is>
+          <t>data_import_cta</t>
+        </is>
+      </c>
+      <c r="C246" s="7" t="inlineStr">
         <is>
           <t>Datamu</t>
         </is>
       </c>
-      <c r="D246" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E246" s="5" t="inlineStr">
-        <is>
-          <t>Progres, jurnal, dan pengaturan akan hilang permanen.</t>
-        </is>
-      </c>
-      <c r="F246" s="5" t="inlineStr">
-        <is>
-          <t>Your progress, journal and settings will be permanently erased.</t>
-        </is>
-      </c>
-      <c r="G246" s="5" t="inlineStr"/>
+      <c r="D246" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E246" s="7" t="inlineStr">
+        <is>
+          <t>Pulihkan dari cadangan</t>
+        </is>
+      </c>
+      <c r="F246" s="7" t="inlineStr">
+        <is>
+          <t>Restore from backup</t>
+        </is>
+      </c>
+      <c r="G246" s="7" t="inlineStr">
+        <is>
+          <t>Without this, the export is useless on a new phone. Proposed for v1.</t>
+        </is>
+      </c>
       <c r="H246" s="6" t="inlineStr"/>
       <c r="I246" s="6" t="inlineStr"/>
     </row>
@@ -8995,7 +9003,7 @@
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>data_delete_cta</t>
+          <t>data_delete_title</t>
         </is>
       </c>
       <c r="C247" s="5" t="inlineStr">
@@ -9010,12 +9018,12 @@
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>Hapus data</t>
+          <t>Hapus semua data</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>Delete data</t>
+          <t>Delete all data</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr"/>
@@ -9028,12 +9036,12 @@
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>delete_sheet_title</t>
+          <t>data_delete_desc</t>
         </is>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>Hapus (sheet)</t>
+          <t>Datamu</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
@@ -9043,12 +9051,12 @@
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>Yakin hapus semua?</t>
+          <t>Progres, jurnal, dan pengaturan akan hilang permanen.</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>Delete everything?</t>
+          <t>Your progress, journal and settings will be permanently erased.</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr"/>
@@ -9061,12 +9069,12 @@
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>delete_sheet_body</t>
+          <t>data_delete_cta</t>
         </is>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>Hapus (sheet)</t>
+          <t>Datamu</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
@@ -9076,12 +9084,12 @@
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>Ini tidak bisa dibatalkan. Kalau hanya ingin istirahat, kamu bisa menjeda pengingat saja.</t>
+          <t>Hapus data</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>This can't be undone. If you just need a break, you can pause the reminders instead.</t>
+          <t>Delete data</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr"/>
@@ -9094,7 +9102,7 @@
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>delete_sheet_confirm</t>
+          <t>delete_sheet_title</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
@@ -9109,12 +9117,12 @@
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>Ya, hapus semuanya</t>
+          <t>Yakin hapus semua?</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>Yes, delete everything</t>
+          <t>Delete everything?</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr"/>
@@ -9127,7 +9135,7 @@
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>common_cancel</t>
+          <t>delete_sheet_body</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
@@ -9142,12 +9150,12 @@
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>Batal</t>
+          <t>Ini tidak bisa dibatalkan. Kalau hanya ingin istirahat, kamu bisa menjeda pengingat saja.</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>This can't be undone. If you just need a break, you can pause the reminders instead.</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr"/>
@@ -9160,12 +9168,12 @@
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>unlock_title</t>
+          <t>delete_sheet_confirm</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>Buka dengan PIN</t>
+          <t>Hapus (sheet)</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
@@ -9175,12 +9183,12 @@
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>Masukkan PIN</t>
+          <t>Ya, hapus semuanya</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>Enter your PIN</t>
+          <t>Yes, delete everything</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr"/>
@@ -9193,12 +9201,12 @@
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>unlock_subtitle</t>
+          <t>common_cancel</t>
         </is>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>Buka dengan PIN</t>
+          <t>Hapus (sheet)</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
@@ -9208,12 +9216,12 @@
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>Assalamu’alaikum. Selamat datang kembali.</t>
+          <t>Batal</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>Assalamu’alaikum. Welcome back.</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr"/>
@@ -9221,72 +9229,68 @@
       <c r="I253" s="6" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="7" t="n">
+      <c r="A254" s="5" t="n">
         <v>253</v>
       </c>
-      <c r="B254" s="7" t="inlineStr">
-        <is>
-          <t>unlock_wrong</t>
-        </is>
-      </c>
-      <c r="C254" s="7" t="inlineStr">
+      <c r="B254" s="5" t="inlineStr">
+        <is>
+          <t>unlock_title</t>
+        </is>
+      </c>
+      <c r="C254" s="5" t="inlineStr">
         <is>
           <t>Buka dengan PIN</t>
         </is>
       </c>
-      <c r="D254" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E254" s="7" t="inlineStr">
-        <is>
-          <t>PIN salah. Coba lagi.</t>
-        </is>
-      </c>
-      <c r="F254" s="7" t="inlineStr">
-        <is>
-          <t>Wrong PIN. Try again.</t>
-        </is>
-      </c>
-      <c r="G254" s="7" t="inlineStr"/>
+      <c r="D254" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E254" s="5" t="inlineStr">
+        <is>
+          <t>Masukkan PIN</t>
+        </is>
+      </c>
+      <c r="F254" s="5" t="inlineStr">
+        <is>
+          <t>Enter your PIN</t>
+        </is>
+      </c>
+      <c r="G254" s="5" t="inlineStr"/>
       <c r="H254" s="6" t="inlineStr"/>
       <c r="I254" s="6" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="7" t="n">
+      <c r="A255" s="5" t="n">
         <v>254</v>
       </c>
-      <c r="B255" s="7" t="inlineStr">
-        <is>
-          <t>unlock_cooldown</t>
-        </is>
-      </c>
-      <c r="C255" s="7" t="inlineStr">
+      <c r="B255" s="5" t="inlineStr">
+        <is>
+          <t>unlock_subtitle</t>
+        </is>
+      </c>
+      <c r="C255" s="5" t="inlineStr">
         <is>
           <t>Buka dengan PIN</t>
         </is>
       </c>
-      <c r="D255" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E255" s="7" t="inlineStr">
-        <is>
-          <t>Terlalu banyak percobaan. Coba lagi dalam {seconds} detik.</t>
-        </is>
-      </c>
-      <c r="F255" s="7" t="inlineStr">
-        <is>
-          <t>Too many tries. Try again in {seconds} seconds.</t>
-        </is>
-      </c>
-      <c r="G255" s="7" t="inlineStr">
-        <is>
-          <t>After 5 wrong PINs: 30 s cooldown. PLURAL in EN.</t>
-        </is>
-      </c>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="inlineStr">
+        <is>
+          <t>Assalamu’alaikum. Selamat datang kembali.</t>
+        </is>
+      </c>
+      <c r="F255" s="5" t="inlineStr">
+        <is>
+          <t>Assalamu’alaikum. Welcome back.</t>
+        </is>
+      </c>
+      <c r="G255" s="5" t="inlineStr"/>
       <c r="H255" s="6" t="inlineStr"/>
       <c r="I255" s="6" t="inlineStr"/>
     </row>
@@ -9296,7 +9300,7 @@
       </c>
       <c r="B256" s="7" t="inlineStr">
         <is>
-          <t>unlock_forgot</t>
+          <t>unlock_wrong</t>
         </is>
       </c>
       <c r="C256" s="7" t="inlineStr">
@@ -9311,12 +9315,12 @@
       </c>
       <c r="E256" s="7" t="inlineStr">
         <is>
-          <t>Lupa PIN?</t>
+          <t>PIN salah. Coba lagi.</t>
         </is>
       </c>
       <c r="F256" s="7" t="inlineStr">
         <is>
-          <t>Forgot your PIN?</t>
+          <t>Wrong PIN. Try again.</t>
         </is>
       </c>
       <c r="G256" s="7" t="inlineStr"/>
@@ -9329,7 +9333,7 @@
       </c>
       <c r="B257" s="7" t="inlineStr">
         <is>
-          <t>unlock_forgot_body</t>
+          <t>unlock_cooldown</t>
         </is>
       </c>
       <c r="C257" s="7" t="inlineStr">
@@ -9344,17 +9348,17 @@
       </c>
       <c r="E257" s="7" t="inlineStr">
         <is>
-          <t>Karena akunmu anonim, PIN tidak bisa dipulihkan. Kamu bisa menghapus data dan mulai dari awal, atau memulihkan dari file cadangan.</t>
+          <t>Terlalu banyak percobaan. Coba lagi dalam {seconds} detik.</t>
         </is>
       </c>
       <c r="F257" s="7" t="inlineStr">
         <is>
-          <t>Your account is anonymous, so the PIN can't be recovered. You can delete your data and start fresh, or restore from a backup file.</t>
+          <t>Too many tries. Try again in {seconds} seconds.</t>
         </is>
       </c>
       <c r="G257" s="7" t="inlineStr">
         <is>
-          <t>Bottom sheet. Buttons reuse delete_sheet_confirm + data_import_cta + common_cancel.</t>
+          <t>After 5 wrong PINs: 30 s cooldown. PLURAL in EN.</t>
         </is>
       </c>
       <c r="H257" s="6" t="inlineStr"/>
@@ -9366,7 +9370,7 @@
       </c>
       <c r="B258" s="7" t="inlineStr">
         <is>
-          <t>biometric_title</t>
+          <t>unlock_forgot</t>
         </is>
       </c>
       <c r="C258" s="7" t="inlineStr">
@@ -9381,19 +9385,15 @@
       </c>
       <c r="E258" s="7" t="inlineStr">
         <is>
-          <t>Buka Izzah</t>
+          <t>Lupa PIN?</t>
         </is>
       </c>
       <c r="F258" s="7" t="inlineStr">
         <is>
-          <t>Unlock Izzah</t>
-        </is>
-      </c>
-      <c r="G258" s="7" t="inlineStr">
-        <is>
-          <t>Title of the system BiometricPrompt. Shows the disguise name if a disguise is active.</t>
-        </is>
-      </c>
+          <t>Forgot your PIN?</t>
+        </is>
+      </c>
+      <c r="G258" s="7" t="inlineStr"/>
       <c r="H258" s="6" t="inlineStr"/>
       <c r="I258" s="6" t="inlineStr"/>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="B259" s="7" t="inlineStr">
         <is>
-          <t>biometric_use_pin</t>
+          <t>unlock_forgot_body</t>
         </is>
       </c>
       <c r="C259" s="7" t="inlineStr">
@@ -9418,50 +9418,54 @@
       </c>
       <c r="E259" s="7" t="inlineStr">
         <is>
-          <t>Pakai PIN</t>
+          <t>Karena akunmu anonim, PIN tidak bisa dipulihkan. Kamu bisa menghapus data dan mulai dari awal, atau memulihkan dari file cadangan.</t>
         </is>
       </c>
       <c r="F259" s="7" t="inlineStr">
         <is>
-          <t>Use PIN</t>
-        </is>
-      </c>
-      <c r="G259" s="7" t="inlineStr"/>
+          <t>Your account is anonymous, so the PIN can't be recovered. You can delete your data and start fresh, or restore from a backup file.</t>
+        </is>
+      </c>
+      <c r="G259" s="7" t="inlineStr">
+        <is>
+          <t>Bottom sheet. Buttons reuse delete_sheet_confirm + data_import_cta + common_cancel.</t>
+        </is>
+      </c>
       <c r="H259" s="6" t="inlineStr"/>
       <c r="I259" s="6" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="5" t="n">
+      <c r="A260" s="7" t="n">
         <v>259</v>
       </c>
-      <c r="B260" s="5" t="inlineStr">
-        <is>
-          <t>notif_prayer_body</t>
-        </is>
-      </c>
-      <c r="C260" s="5" t="inlineStr">
-        <is>
-          <t>Notifikasi (sistem)</t>
-        </is>
-      </c>
-      <c r="D260" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E260" s="5" t="inlineStr">
-        <is>
-          <t>Waktunya {prayer}. Sejenak untuk dirimu.</t>
-        </is>
-      </c>
-      <c r="F260" s="5" t="inlineStr">
-        <is>
-          <t>Time for {prayer}. A moment for yourself.</t>
-        </is>
-      </c>
-      <c r="G260" s="5" t="inlineStr">
-        <is>
-          <t>RULE: no notification may mention porn, relapse or addiction.</t>
+      <c r="B260" s="7" t="inlineStr">
+        <is>
+          <t>biometric_title</t>
+        </is>
+      </c>
+      <c r="C260" s="7" t="inlineStr">
+        <is>
+          <t>Buka dengan PIN</t>
+        </is>
+      </c>
+      <c r="D260" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E260" s="7" t="inlineStr">
+        <is>
+          <t>Buka Izzah</t>
+        </is>
+      </c>
+      <c r="F260" s="7" t="inlineStr">
+        <is>
+          <t>Unlock Izzah</t>
+        </is>
+      </c>
+      <c r="G260" s="7" t="inlineStr">
+        <is>
+          <t>Title of the system BiometricPrompt. Shows the disguise name if a disguise is active.</t>
         </is>
       </c>
       <c r="H260" s="6" t="inlineStr"/>
@@ -9473,12 +9477,12 @@
       </c>
       <c r="B261" s="7" t="inlineStr">
         <is>
-          <t>notif_dzikir_morning</t>
+          <t>biometric_use_pin</t>
         </is>
       </c>
       <c r="C261" s="7" t="inlineStr">
         <is>
-          <t>Notifikasi (sistem)</t>
+          <t>Buka dengan PIN</t>
         </is>
       </c>
       <c r="D261" s="7" t="inlineStr">
@@ -9488,12 +9492,12 @@
       </c>
       <c r="E261" s="7" t="inlineStr">
         <is>
-          <t>Pagi yang baru. Ada waktu sebentar untuk dirimu?</t>
+          <t>Pakai PIN</t>
         </is>
       </c>
       <c r="F261" s="7" t="inlineStr">
         <is>
-          <t>A fresh morning. Got a minute for yourself?</t>
+          <t>Use PIN</t>
         </is>
       </c>
       <c r="G261" s="7" t="inlineStr"/>
@@ -9501,35 +9505,39 @@
       <c r="I261" s="6" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="7" t="n">
+      <c r="A262" s="5" t="n">
         <v>261</v>
       </c>
-      <c r="B262" s="7" t="inlineStr">
-        <is>
-          <t>notif_dzikir_evening</t>
-        </is>
-      </c>
-      <c r="C262" s="7" t="inlineStr">
+      <c r="B262" s="5" t="inlineStr">
+        <is>
+          <t>notif_prayer_body</t>
+        </is>
+      </c>
+      <c r="C262" s="5" t="inlineStr">
         <is>
           <t>Notifikasi (sistem)</t>
         </is>
       </c>
-      <c r="D262" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E262" s="7" t="inlineStr">
-        <is>
-          <t>Sore menjelang. Sejenak untuk menenangkan hati.</t>
-        </is>
-      </c>
-      <c r="F262" s="7" t="inlineStr">
-        <is>
-          <t>Evening is here. A moment to settle your heart.</t>
-        </is>
-      </c>
-      <c r="G262" s="7" t="inlineStr"/>
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="inlineStr">
+        <is>
+          <t>Waktunya {prayer}. Sejenak untuk dirimu.</t>
+        </is>
+      </c>
+      <c r="F262" s="5" t="inlineStr">
+        <is>
+          <t>Time for {prayer}. A moment for yourself.</t>
+        </is>
+      </c>
+      <c r="G262" s="5" t="inlineStr">
+        <is>
+          <t>RULE: no notification may mention porn, relapse or addiction.</t>
+        </is>
+      </c>
       <c r="H262" s="6" t="inlineStr"/>
       <c r="I262" s="6" t="inlineStr"/>
     </row>
@@ -9539,7 +9547,7 @@
       </c>
       <c r="B263" s="7" t="inlineStr">
         <is>
-          <t>notif_checkin</t>
+          <t>notif_dzikir_morning</t>
         </is>
       </c>
       <c r="C263" s="7" t="inlineStr">
@@ -9554,12 +9562,12 @@
       </c>
       <c r="E263" s="7" t="inlineStr">
         <is>
-          <t>Bagaimana harimu? Catat sebentar sebelum istirahat.</t>
+          <t>Pagi yang baru. Ada waktu sebentar untuk dirimu?</t>
         </is>
       </c>
       <c r="F263" s="7" t="inlineStr">
         <is>
-          <t>How was your day? A quick note before you rest.</t>
+          <t>A fresh morning. Got a minute for yourself?</t>
         </is>
       </c>
       <c r="G263" s="7" t="inlineStr"/>
@@ -9572,7 +9580,7 @@
       </c>
       <c r="B264" s="7" t="inlineStr">
         <is>
-          <t>notif_channel_reminders</t>
+          <t>notif_dzikir_evening</t>
         </is>
       </c>
       <c r="C264" s="7" t="inlineStr">
@@ -9587,19 +9595,15 @@
       </c>
       <c r="E264" s="7" t="inlineStr">
         <is>
-          <t>Pengingat</t>
+          <t>Sore menjelang. Sejenak untuk menenangkan hati.</t>
         </is>
       </c>
       <c r="F264" s="7" t="inlineStr">
         <is>
-          <t>Reminders</t>
-        </is>
-      </c>
-      <c r="G264" s="7" t="inlineStr">
-        <is>
-          <t>Android notification channel name (visible in system settings).</t>
-        </is>
-      </c>
+          <t>Evening is here. A moment to settle your heart.</t>
+        </is>
+      </c>
+      <c r="G264" s="7" t="inlineStr"/>
       <c r="H264" s="6" t="inlineStr"/>
       <c r="I264" s="6" t="inlineStr"/>
     </row>
@@ -9609,7 +9613,7 @@
       </c>
       <c r="B265" s="7" t="inlineStr">
         <is>
-          <t>notif_channel_protect</t>
+          <t>notif_checkin</t>
         </is>
       </c>
       <c r="C265" s="7" t="inlineStr">
@@ -9624,19 +9628,15 @@
       </c>
       <c r="E265" s="7" t="inlineStr">
         <is>
-          <t>Penjagaan aktif</t>
+          <t>Bagaimana harimu? Catat sebentar sebelum istirahat.</t>
         </is>
       </c>
       <c r="F265" s="7" t="inlineStr">
         <is>
-          <t>Protection running</t>
-        </is>
-      </c>
-      <c r="G265" s="7" t="inlineStr">
-        <is>
-          <t>Foreground service channel for the blocker.</t>
-        </is>
-      </c>
+          <t>How was your day? A quick note before you rest.</t>
+        </is>
+      </c>
+      <c r="G265" s="7" t="inlineStr"/>
       <c r="H265" s="6" t="inlineStr"/>
       <c r="I265" s="6" t="inlineStr"/>
     </row>
@@ -9646,7 +9646,7 @@
       </c>
       <c r="B266" s="7" t="inlineStr">
         <is>
-          <t>notif_protect_ongoing</t>
+          <t>notif_channel_reminders</t>
         </is>
       </c>
       <c r="C266" s="7" t="inlineStr">
@@ -9661,89 +9661,93 @@
       </c>
       <c r="E266" s="7" t="inlineStr">
         <is>
-          <t>Berjalan di latar belakang.</t>
+          <t>Pengingat</t>
         </is>
       </c>
       <c r="F266" s="7" t="inlineStr">
         <is>
-          <t>Running in the background.</t>
+          <t>Reminders</t>
         </is>
       </c>
       <c r="G266" s="7" t="inlineStr">
         <is>
-          <t>Persistent foreground-service notification. Must stay neutral.</t>
+          <t>Android notification channel name (visible in system settings).</t>
         </is>
       </c>
       <c r="H266" s="6" t="inlineStr"/>
       <c r="I266" s="6" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="5" t="n">
+      <c r="A267" s="7" t="n">
         <v>266</v>
       </c>
-      <c r="B267" s="5" t="inlineStr">
-        <is>
-          <t>hijri_month_1</t>
-        </is>
-      </c>
-      <c r="C267" s="5" t="inlineStr">
-        <is>
-          <t>Hijri calendar</t>
-        </is>
-      </c>
-      <c r="D267" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E267" s="5" t="inlineStr">
-        <is>
-          <t>Muharram</t>
-        </is>
-      </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>Muharram</t>
-        </is>
-      </c>
-      <c r="G267" s="5" t="inlineStr">
-        <is>
-          <t>Used by {hijri}.</t>
+      <c r="B267" s="7" t="inlineStr">
+        <is>
+          <t>notif_channel_protect</t>
+        </is>
+      </c>
+      <c r="C267" s="7" t="inlineStr">
+        <is>
+          <t>Notifikasi (sistem)</t>
+        </is>
+      </c>
+      <c r="D267" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E267" s="7" t="inlineStr">
+        <is>
+          <t>Penjagaan aktif</t>
+        </is>
+      </c>
+      <c r="F267" s="7" t="inlineStr">
+        <is>
+          <t>Protection running</t>
+        </is>
+      </c>
+      <c r="G267" s="7" t="inlineStr">
+        <is>
+          <t>Foreground service channel for the blocker.</t>
         </is>
       </c>
       <c r="H267" s="6" t="inlineStr"/>
       <c r="I267" s="6" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="n">
+      <c r="A268" s="7" t="n">
         <v>267</v>
       </c>
-      <c r="B268" s="5" t="inlineStr">
-        <is>
-          <t>hijri_month_2</t>
-        </is>
-      </c>
-      <c r="C268" s="5" t="inlineStr">
-        <is>
-          <t>Hijri calendar</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E268" s="5" t="inlineStr">
-        <is>
-          <t>Safar</t>
-        </is>
-      </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>Safar</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="inlineStr"/>
+      <c r="B268" s="7" t="inlineStr">
+        <is>
+          <t>notif_protect_ongoing</t>
+        </is>
+      </c>
+      <c r="C268" s="7" t="inlineStr">
+        <is>
+          <t>Notifikasi (sistem)</t>
+        </is>
+      </c>
+      <c r="D268" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E268" s="7" t="inlineStr">
+        <is>
+          <t>Berjalan di latar belakang.</t>
+        </is>
+      </c>
+      <c r="F268" s="7" t="inlineStr">
+        <is>
+          <t>Running in the background.</t>
+        </is>
+      </c>
+      <c r="G268" s="7" t="inlineStr">
+        <is>
+          <t>Persistent foreground-service notification. Must stay neutral.</t>
+        </is>
+      </c>
       <c r="H268" s="6" t="inlineStr"/>
       <c r="I268" s="6" t="inlineStr"/>
     </row>
@@ -9753,7 +9757,7 @@
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_3</t>
+          <t>hijri_month_1</t>
         </is>
       </c>
       <c r="C269" s="5" t="inlineStr">
@@ -9768,15 +9772,19 @@
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>Rabiul Awal</t>
+          <t>Muharram</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>Rabi‘ al-Awwal</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr"/>
+          <t>Muharram</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr">
+        <is>
+          <t>Used by {hijri}.</t>
+        </is>
+      </c>
       <c r="H269" s="6" t="inlineStr"/>
       <c r="I269" s="6" t="inlineStr"/>
     </row>
@@ -9786,7 +9794,7 @@
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_4</t>
+          <t>hijri_month_2</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
@@ -9801,12 +9809,12 @@
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>Rabiul Akhir</t>
+          <t>Safar</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>Rabi‘ al-Thani</t>
+          <t>Safar</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr"/>
@@ -9819,7 +9827,7 @@
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_5</t>
+          <t>hijri_month_3</t>
         </is>
       </c>
       <c r="C271" s="5" t="inlineStr">
@@ -9834,12 +9842,12 @@
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>Jumadil Awal</t>
+          <t>Rabiul Awal</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>Jumada al-Ula</t>
+          <t>Rabi‘ al-Awwal</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr"/>
@@ -9852,7 +9860,7 @@
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_6</t>
+          <t>hijri_month_4</t>
         </is>
       </c>
       <c r="C272" s="5" t="inlineStr">
@@ -9867,12 +9875,12 @@
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>Jumadil Akhir</t>
+          <t>Rabiul Akhir</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>Jumada al-Akhirah</t>
+          <t>Rabi‘ al-Thani</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr"/>
@@ -9885,7 +9893,7 @@
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_7</t>
+          <t>hijri_month_5</t>
         </is>
       </c>
       <c r="C273" s="5" t="inlineStr">
@@ -9900,12 +9908,12 @@
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>Rajab</t>
+          <t>Jumadil Awal</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>Rajab</t>
+          <t>Jumada al-Ula</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr"/>
@@ -9918,7 +9926,7 @@
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_8</t>
+          <t>hijri_month_6</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
@@ -9933,12 +9941,12 @@
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>Sya’ban</t>
+          <t>Jumadil Akhir</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>Sha‘ban</t>
+          <t>Jumada al-Akhirah</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr"/>
@@ -9951,7 +9959,7 @@
       </c>
       <c r="B275" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_9</t>
+          <t>hijri_month_7</t>
         </is>
       </c>
       <c r="C275" s="5" t="inlineStr">
@@ -9966,12 +9974,12 @@
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
-          <t>Ramadhan</t>
+          <t>Rajab</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>Ramadan</t>
+          <t>Rajab</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr"/>
@@ -9984,7 +9992,7 @@
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_10</t>
+          <t>hijri_month_8</t>
         </is>
       </c>
       <c r="C276" s="5" t="inlineStr">
@@ -9999,12 +10007,12 @@
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>Syawal</t>
+          <t>Sya’ban</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>Shawwal</t>
+          <t>Sha‘ban</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr"/>
@@ -10017,7 +10025,7 @@
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_11</t>
+          <t>hijri_month_9</t>
         </is>
       </c>
       <c r="C277" s="5" t="inlineStr">
@@ -10032,12 +10040,12 @@
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>Dzulqa’dah</t>
+          <t>Ramadhan</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>Dhu al-Qa‘dah</t>
+          <t>Ramadan</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr"/>
@@ -10050,7 +10058,7 @@
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_12</t>
+          <t>hijri_month_10</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
@@ -10065,12 +10073,12 @@
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>Dzulhijjah</t>
+          <t>Syawal</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>Dhu al-Hijjah</t>
+          <t>Shawwal</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr"/>
@@ -10083,7 +10091,7 @@
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>hijri_suffix</t>
+          <t>hijri_month_11</t>
         </is>
       </c>
       <c r="C279" s="5" t="inlineStr">
@@ -10098,22 +10106,88 @@
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>{day} {month} {year} H</t>
+          <t>Dzulqa’dah</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>{day} {month} {year} AH</t>
+          <t>Dhu al-Qa‘dah</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr"/>
       <c r="H279" s="6" t="inlineStr"/>
       <c r="I279" s="6" t="inlineStr"/>
     </row>
+    <row r="280">
+      <c r="A280" s="5" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="5" t="inlineStr">
+        <is>
+          <t>hijri_month_12</t>
+        </is>
+      </c>
+      <c r="C280" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D280" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="inlineStr">
+        <is>
+          <t>Dzulhijjah</t>
+        </is>
+      </c>
+      <c r="F280" s="5" t="inlineStr">
+        <is>
+          <t>Dhu al-Hijjah</t>
+        </is>
+      </c>
+      <c r="G280" s="5" t="inlineStr"/>
+      <c r="H280" s="6" t="inlineStr"/>
+      <c r="I280" s="6" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="5" t="inlineStr">
+        <is>
+          <t>hijri_suffix</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="inlineStr">
+        <is>
+          <t>{day} {month} {year} H</t>
+        </is>
+      </c>
+      <c r="F281" s="5" t="inlineStr">
+        <is>
+          <t>{day} {month} {year} AH</t>
+        </is>
+      </c>
+      <c r="G281" s="5" t="inlineStr"/>
+      <c r="H281" s="6" t="inlineStr"/>
+      <c r="I281" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I279"/>
+  <autoFilter ref="A1:I281"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H279" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H281" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,Revisi,Hapus"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/copy/izzah-copy-id-en.xlsx
+++ b/docs/copy/izzah-copy-id-en.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Glossary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Copy'!$A$1:$I$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Copy'!$A$1:$I$280</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Religious'!$A$1:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Glossary'!$A$1:$E$13</definedName>
   </definedNames>
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I281"/>
+  <dimension ref="A1:I280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1039,37 +1039,37 @@
       <c r="I11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>pin_delete_cd</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>PIN pad</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Hapus</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Delete</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Content description for the backspace key on the PIN pad (accessibility).</t>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>onboarding_progress</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Onboarding (all)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>{step}/6</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>{step}/6</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Placeholder only.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr"/>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>onboarding_progress</t>
+          <t>niat_title</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Onboarding (all)</t>
+          <t>1 · Niat</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1096,19 +1096,15 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>{step}/6</t>
+          <t>Apa yang membuatmu ingin berubah?</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>{step}/6</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Placeholder only.</t>
-        </is>
-      </c>
+          <t>What makes you want to change?</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" s="6" t="inlineStr"/>
     </row>
@@ -1118,7 +1114,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>niat_title</t>
+          <t>niat_subtitle</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1133,12 +1129,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Apa yang membuatmu ingin berubah?</t>
+          <t>Pilih yang paling dekat di hati. Ini akan kami ingatkan saat kamu goyah.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>What makes you want to change?</t>
+          <t>Pick what's closest to your heart. We'll remind you of it when you feel shaky.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -1151,7 +1147,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>niat_subtitle</t>
+          <t>niat_opt_allah</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1166,12 +1162,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Pilih yang paling dekat di hati. Ini akan kami ingatkan saat kamu goyah.</t>
+          <t>Dekat dengan Allah</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Pick what's closest to your heart. We'll remind you of it when you feel shaky.</t>
+          <t>Closer to Allah</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -1184,7 +1180,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>niat_opt_allah</t>
+          <t>niat_opt_family</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1199,12 +1195,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Dekat dengan Allah</t>
+          <t>Untuk keluarga</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Closer to Allah</t>
+          <t>For my family</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
@@ -1217,7 +1213,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>niat_opt_family</t>
+          <t>niat_opt_spouse</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1232,12 +1228,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Untuk keluarga</t>
+          <t>Pasangan / calon</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>For my family</t>
+          <t>My spouse / future spouse</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr"/>
@@ -1250,7 +1246,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>niat_opt_spouse</t>
+          <t>niat_opt_focus</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1265,12 +1261,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Pasangan / calon</t>
+          <t>Fokus &amp; produktif</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>My spouse / future spouse</t>
+          <t>Focus &amp; productivity</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
@@ -1283,7 +1279,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>niat_opt_focus</t>
+          <t>niat_opt_peace</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1298,12 +1294,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Fokus &amp; produktif</t>
+          <t>Ketenangan pikiran</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Focus &amp; productivity</t>
+          <t>Peace of mind</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr"/>
@@ -1316,7 +1312,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>niat_opt_peace</t>
+          <t>niat_opt_selfrespect</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1331,12 +1327,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Ketenangan pikiran</t>
+          <t>Harga diri</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Peace of mind</t>
+          <t>Self-respect</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
@@ -1349,7 +1345,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>niat_opt_selfrespect</t>
+          <t>niat_note</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1364,12 +1360,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Harga diri</t>
+          <t>Tersimpan hanya di HP-mu.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Self-respect</t>
+          <t>Saved only on your phone.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
@@ -1382,12 +1378,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>niat_note</t>
+          <t>target_title</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>1 · Niat</t>
+          <t>2 · Target</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1397,12 +1393,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Tersimpan hanya di HP-mu.</t>
+          <t>Pilih target pertamamu</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Saved only on your phone.</t>
+          <t>Choose your first goal</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
@@ -1415,7 +1411,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>target_title</t>
+          <t>target_subtitle</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1430,12 +1426,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Pilih target pertamamu</t>
+          <t>Kami menghitung hari yang kamu jaga. Terpeleset tidak menghapus hitungan.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Choose your first goal</t>
+          <t>We count the days you keep. A slip doesn't erase the count.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
@@ -1448,7 +1444,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>target_subtitle</t>
+          <t>target_7_title</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1463,12 +1459,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Kami menghitung hari yang kamu jaga. Terpeleset tidak menghapus hitungan.</t>
+          <t>Satu minggu</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>We count the days you keep. A slip doesn't erase the count.</t>
+          <t>One week</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
@@ -1481,7 +1477,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>target_7_title</t>
+          <t>target_7_desc</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1496,12 +1492,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Satu minggu</t>
+          <t>Langkah pertama</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>One week</t>
+          <t>A first step</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
@@ -1514,7 +1510,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>target_7_desc</t>
+          <t>target_30_title</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1529,12 +1525,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Langkah pertama</t>
+          <t>Satu bulan</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>A first step</t>
+          <t>One month</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
@@ -1547,7 +1543,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>target_30_title</t>
+          <t>target_30_desc</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1562,12 +1558,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Satu bulan</t>
+          <t>Membangun kebiasaan</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>One month</t>
+          <t>Building a habit</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
@@ -1580,7 +1576,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>target_30_desc</t>
+          <t>target_40_title</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1595,12 +1591,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Membangun kebiasaan</t>
+          <t>Empat puluh hari</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Building a habit</t>
+          <t>Forty days</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
@@ -1613,7 +1609,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>target_40_title</t>
+          <t>target_40_desc</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1628,12 +1624,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Empat puluh hari</t>
+          <t>Waktu yang sering disebut untuk perubahan diri</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Forty days</t>
+          <t>A span often linked to real self-change</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
@@ -1646,7 +1642,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>target_40_desc</t>
+          <t>target_90_title</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1661,12 +1657,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Waktu yang sering disebut untuk perubahan diri</t>
+          <t>Tiga bulan</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>A span often linked to real self-change</t>
+          <t>Three months</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
@@ -1679,7 +1675,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>target_90_title</t>
+          <t>target_90_desc</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1694,15 +1690,19 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Tiga bulan</t>
+          <t>Disarankan · otak mulai pulih</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Three months</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr"/>
+          <t>Recommended · the brain begins to recover</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>This is a health claim, so consider softening it, e.g. 'Recommended · time for real change'.</t>
+        </is>
+      </c>
       <c r="H31" s="6" t="inlineStr"/>
       <c r="I31" s="6" t="inlineStr"/>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>target_90_desc</t>
+          <t>rawan_title</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>2 · Target</t>
+          <t>3 · Jam rawan</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1727,19 +1727,15 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Disarankan · otak mulai pulih</t>
+          <t>Kapan biasanya paling berat?</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Recommended · the brain begins to recover</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>This is a health claim, so consider softening it, e.g. 'Recommended · time for real change'.</t>
-        </is>
-      </c>
+          <t>When is it usually hardest?</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" s="6" t="inlineStr"/>
     </row>
@@ -1749,7 +1745,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>rawan_title</t>
+          <t>rawan_subtitle</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1764,12 +1760,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Kapan biasanya paling berat?</t>
+          <t>Kami akan lebih dekat di waktu-waktu itu: pengingat, dan pagar untuk aplikasi.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>When is it usually hardest?</t>
+          <t>We'll stay closer at those times, with reminders and a fence around certain apps.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
@@ -1782,7 +1778,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>rawan_subtitle</t>
+          <t>rawan_opt_late</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1797,12 +1793,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Kami akan lebih dekat di waktu-waktu itu: pengingat, dan pagar untuk aplikasi.</t>
+          <t>Larut malam</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>We'll stay closer at those times, with reminders and a fence around certain apps.</t>
+          <t>Late at night</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
@@ -1815,7 +1811,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>rawan_opt_late</t>
+          <t>rawan_opt_dawn</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -1830,12 +1826,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Larut malam</t>
+          <t>Dini hari</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Late at night</t>
+          <t>Before dawn</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
@@ -1848,7 +1844,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>rawan_opt_dawn</t>
+          <t>rawan_opt_afternoon</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1863,12 +1859,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Dini hari</t>
+          <t>Siang, sendirian</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Before dawn</t>
+          <t>Afternoons, alone</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
@@ -1881,7 +1877,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>rawan_opt_afternoon</t>
+          <t>rawan_opt_social</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -1896,12 +1892,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Siang, sendirian</t>
+          <t>Setelah buka medsos</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Afternoons, alone</t>
+          <t>After social media</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
@@ -1914,7 +1910,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>rawan_opt_social</t>
+          <t>rawan_opt_stress</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1929,12 +1925,12 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Setelah buka medsos</t>
+          <t>Saat stres</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>After social media</t>
+          <t>When stressed</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
@@ -1947,7 +1943,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>rawan_opt_stress</t>
+          <t>rawan_opt_weekend</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -1962,12 +1958,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Saat stres</t>
+          <t>Akhir pekan</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>When stressed</t>
+          <t>Weekends</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
@@ -1980,12 +1976,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>rawan_opt_weekend</t>
+          <t>izin_title</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>3 · Jam rawan</t>
+          <t>4 · Izin</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1995,12 +1991,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Akhir pekan</t>
+          <t>Izinkan Izzah menjaga waktu rawanmu</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Weekends</t>
+          <t>Let Izzah guard your hard hours</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
@@ -2008,72 +2004,72 @@
       <c r="I40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>izin_title</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>izin_subtitle</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>4 · Izin</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>Izinkan Izzah menjaga waktu rawanmu</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Let Izzah guard your hard hours</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>ANDROID</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Dengan izin akses penggunaan, Izzah bisa memberi jeda pada aplikasi yang kamu pilih.</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>With usage access, Izzah can put a pause in front of the apps you choose.</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>Original: 'Dengan izin Screen Time…'. Screen Time is iOS-only.</t>
+        </is>
+      </c>
       <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n">
+      <c r="A42" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>izin_subtitle</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>izin_promise_1</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>4 · Izin</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>ANDROID</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>Dengan izin akses penggunaan, Izzah bisa memberi jeda pada aplikasi yang kamu pilih.</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>With usage access, Izzah can put a pause in front of the apps you choose.</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>Original: 'Dengan izin Screen Time…'. Screen Time is iOS-only.</t>
-        </is>
-      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Riwayat browsing tidak pernah kami lihat atau simpan.</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>We never see or store your browsing history.</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" s="6" t="inlineStr"/>
     </row>
@@ -2083,7 +2079,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>izin_promise_1</t>
+          <t>izin_promise_2</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -2098,12 +2094,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Riwayat browsing tidak pernah kami lihat atau simpan.</t>
+          <t>Kamu sendiri yang memilih aplikasi dan jamnya.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>We never see or store your browsing history.</t>
+          <t>You choose the apps and the hours yourself.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr"/>
@@ -2116,7 +2112,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>izin_promise_2</t>
+          <t>izin_promise_3</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -2131,12 +2127,12 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Kamu sendiri yang memilih aplikasi dan jamnya.</t>
+          <t>Bisa dimatikan kapan saja dari Pengaturan.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>You choose the apps and the hours yourself.</t>
+          <t>You can turn it off anytime in Settings.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
@@ -2144,105 +2140,109 @@
       <c r="I44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>izin_promise_3</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>izin_cta</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>4 · Izin</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>Bisa dimatikan kapan saja dari Pengaturan.</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>You can turn it off anytime in Settings.</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>ANDROID</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Berikan izin</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Grant access</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>Original: 'Izinkan Screen Time'. On Android it opens 2 system settings in turn.</t>
+        </is>
+      </c>
       <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="n">
+      <c r="A46" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>izin_cta</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>izin_skip</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>4 · Izin</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>ANDROID</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>Berikan izin</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>Grant access</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>Original: 'Izinkan Screen Time'. On Android it opens 2 system settings in turn.</t>
-        </is>
-      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Nanti saja</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Maybe later</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="6" t="inlineStr"/>
       <c r="I46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>izin_skip</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>izin_perm_usage_title</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>4 · Izin</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>Nanti saja</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Maybe later</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Akses penggunaan</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>Usage access</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Replaces the iOS system alert. Status row #1.</t>
+        </is>
+      </c>
       <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" s="6" t="inlineStr"/>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>izin_perm_usage_title</t>
+          <t>izin_perm_usage_desc</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
@@ -2267,19 +2267,15 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Akses penggunaan</t>
+          <t>Supaya Izzah tahu kapan aplikasi pilihanmu dibuka.</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Usage access</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>Replaces the iOS system alert. Status row #1.</t>
-        </is>
-      </c>
+          <t>So Izzah knows when an app you chose is opened.</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr"/>
       <c r="H48" s="6" t="inlineStr"/>
       <c r="I48" s="6" t="inlineStr"/>
     </row>
@@ -2289,7 +2285,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>izin_perm_usage_desc</t>
+          <t>izin_perm_overlay_title</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -2304,15 +2300,19 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Supaya Izzah tahu kapan aplikasi pilihanmu dibuka.</t>
+          <t>Tampil di atas aplikasi lain</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>So Izzah knows when an app you chose is opened.</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr"/>
+          <t>Display over other apps</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Status row #2.</t>
+        </is>
+      </c>
       <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" s="6" t="inlineStr"/>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>izin_perm_overlay_title</t>
+          <t>izin_perm_overlay_desc</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
@@ -2337,19 +2337,15 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Tampil di atas aplikasi lain</t>
+          <t>Supaya layar jeda bisa muncul.</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Display over other apps</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>Status row #2.</t>
-        </is>
-      </c>
+          <t>So the pause screen can appear.</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr"/>
       <c r="H50" s="6" t="inlineStr"/>
       <c r="I50" s="6" t="inlineStr"/>
     </row>
@@ -2359,7 +2355,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>izin_perm_overlay_desc</t>
+          <t>izin_perm_on</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -2374,12 +2370,12 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Supaya layar jeda bisa muncul.</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>So the pause screen can appear.</t>
+          <t>On</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr"/>
@@ -2392,7 +2388,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>izin_perm_on</t>
+          <t>izin_perm_off</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -2407,12 +2403,12 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Belum</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Not yet</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr"/>
@@ -2420,35 +2416,35 @@
       <c r="I52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="n">
+      <c r="A53" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>izin_perm_off</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>4 · Izin</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Not yet</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr"/>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>pin_create_title</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>5 · PIN</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Buat PIN 4 angka</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Create a 4-digit PIN</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="6" t="inlineStr"/>
       <c r="I53" s="6" t="inlineStr"/>
     </row>
@@ -2458,7 +2454,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>pin_create_title</t>
+          <t>pin_create_subtitle</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -2473,12 +2469,12 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Buat PIN 4 angka</t>
+          <t>Supaya hanya kamu yang bisa membuka Izzah.</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Create a 4-digit PIN</t>
+          <t>So only you can open Izzah.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
@@ -2486,35 +2482,39 @@
       <c r="I54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>pin_create_subtitle</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>pin_confirm_title</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>5 · PIN</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>Supaya hanya kamu yang bisa membuka Izzah.</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>So only you can open Izzah.</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr"/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Ketik ulang PIN-mu</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Enter your PIN again</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Proposed confirmation step (not in design), so a typo doesn't lock the user out.</t>
+        </is>
+      </c>
       <c r="H55" s="6" t="inlineStr"/>
       <c r="I55" s="6" t="inlineStr"/>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>pin_confirm_title</t>
+          <t>pin_mismatch</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
@@ -2539,126 +2539,122 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Ketik ulang PIN-mu</t>
+          <t>PIN tidak sama. Coba lagi.</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Enter your PIN again</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>Proposed confirmation step (not in design), so a typo doesn't lock the user out.</t>
-        </is>
-      </c>
+          <t>PINs don't match. Try again.</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr"/>
       <c r="H56" s="6" t="inlineStr"/>
       <c r="I56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="n">
+      <c r="A57" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>pin_mismatch</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>pin_biometric_toggle</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>5 · PIN</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>PIN tidak sama. Coba lagi.</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>PINs don't match. Try again.</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>ANDROID</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>Buka juga dengan sidik jari atau wajah</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Also unlock with fingerprint or face</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>Original: 'Buka juga dengan Face ID'.</t>
+        </is>
+      </c>
       <c r="H57" s="6" t="inlineStr"/>
       <c r="I57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="n">
+      <c r="A58" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>pin_biometric_toggle</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>5 · PIN</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>ANDROID</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>Buka juga dengan sidik jari atau wajah</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>Also unlock with fingerprint or face</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>Original: 'Buka juga dengan Face ID'.</t>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>keypad_delete_cd</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>5 · PIN / Unlock</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Hapus angka</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Delete digit</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Content description for ⌫.</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="n">
+      <c r="A59" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>keypad_delete_cd</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>5 · PIN / Unlock</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>Hapus angka</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>Delete digit</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>Content description for ⌫.</t>
-        </is>
-      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>notif_title</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>6 · Notifikasi</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Pengingat yang tidak membuka rahasiamu</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Reminders that keep your secret</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="6" t="inlineStr"/>
       <c r="I59" s="6" t="inlineStr"/>
     </row>
@@ -2668,7 +2664,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>notif_title</t>
+          <t>notif_subtitle</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2683,12 +2679,12 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Pengingat yang tidak membuka rahasiamu</t>
+          <t>Isi notifikasi selalu netral. Orang di sebelahmu tidak akan tahu.</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Reminders that keep your secret</t>
+          <t>Notifications are always neutral. The person next to you won't know.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr"/>
@@ -2701,7 +2697,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>notif_subtitle</t>
+          <t>notif_preview_time</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -2716,12 +2712,12 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Isi notifikasi selalu netral. Orang di sebelahmu tidak akan tahu.</t>
+          <t>sekarang</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Notifications are always neutral. The person next to you won't know.</t>
+          <t>now</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr"/>
@@ -2734,7 +2730,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>notif_preview_time</t>
+          <t>notif_preview_body</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -2749,12 +2745,12 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>sekarang</t>
+          <t>Waktunya Ashar. Sejenak untuk dirimu.</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>now</t>
+          <t>Time for Asr. A moment for yourself.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr"/>
@@ -2767,7 +2763,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>notif_preview_body</t>
+          <t>notif_opt_prayer</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -2782,12 +2778,12 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Waktunya Ashar. Sejenak untuk dirimu.</t>
+          <t>Pengingat sholat</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Time for Asr. A moment for yourself.</t>
+          <t>Prayer reminders</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr"/>
@@ -2800,7 +2796,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>notif_opt_prayer</t>
+          <t>notif_opt_prayer_desc</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -2815,12 +2811,12 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Pengingat sholat</t>
+          <t>Lima waktu, isi netral</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Prayer reminders</t>
+          <t>All five prayers, neutral wording</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr"/>
@@ -2833,7 +2829,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>notif_opt_prayer_desc</t>
+          <t>notif_opt_dzikir</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -2848,12 +2844,12 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Lima waktu, isi netral</t>
+          <t>Dzikir pagi &amp; petang</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>All five prayers, neutral wording</t>
+          <t>Morning &amp; evening dhikr</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr"/>
@@ -2866,7 +2862,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>notif_opt_dzikir</t>
+          <t>notif_opt_dzikir_desc</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -2881,12 +2877,12 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Dzikir pagi &amp; petang</t>
+          <t>Setelah Subuh dan Ashar</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Morning &amp; evening dhikr</t>
+          <t>After Fajr and Asr</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr"/>
@@ -2899,7 +2895,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>notif_opt_dzikir_desc</t>
+          <t>notif_opt_checkin</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -2914,12 +2910,12 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Setelah Subuh dan Ashar</t>
+          <t>Check-in malam</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>After Fajr and Asr</t>
+          <t>Evening check-in</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
@@ -2932,7 +2928,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>notif_opt_checkin</t>
+          <t>notif_opt_checkin_desc</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -2947,15 +2943,19 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Check-in malam</t>
+          <t>Pukul {time}, sebelum jam rawan</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Evening check-in</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr"/>
+          <t>At {time}, before the hard hours</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>{time} = 21.30 (ID) / 9:30 PM (EN). Format with the locale, never hardcode it.</t>
+        </is>
+      </c>
       <c r="H68" s="6" t="inlineStr"/>
       <c r="I68" s="6" t="inlineStr"/>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>notif_opt_checkin_desc</t>
+          <t>notif_cta</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -2980,19 +2980,15 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Pukul {time}, sebelum jam rawan</t>
+          <t>Izinkan notifikasi</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>At {time}, before the hard hours</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>{time} = 21.30 (ID) / 9:30 PM (EN). Format with the locale, never hardcode it.</t>
-        </is>
-      </c>
+          <t>Allow notifications</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="6" t="inlineStr"/>
       <c r="I69" s="6" t="inlineStr"/>
     </row>
@@ -3002,12 +2998,12 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>notif_cta</t>
+          <t>done_day_label</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>6 · Notifikasi</t>
+          <t>Selesai</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -3017,12 +3013,12 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Izinkan notifikasi</t>
+          <t>Hari pertama · {hijri}</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Allow notifications</t>
+          <t>Day one · {hijri}</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr"/>
@@ -3035,7 +3031,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>done_day_label</t>
+          <t>done_journey</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -3050,12 +3046,12 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Hari pertama · {hijri}</t>
+          <t>Perjalanan {target} hari dimulai hari ini.</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Day one · {hijri}</t>
+          <t>Your {target}-day journey starts today.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr"/>
@@ -3068,7 +3064,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>done_journey</t>
+          <t>done_hint</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -3083,12 +3079,12 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Perjalanan {target} hari dimulai hari ini.</t>
+          <t>Kalau dorongan datang, tombol Jeda selalu ada di tengah bawah.</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Your {target}-day journey starts today.</t>
+          <t>If an urge comes, the Pause button is always at the bottom center.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr"/>
@@ -3101,7 +3097,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>done_hint</t>
+          <t>done_cta</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -3116,12 +3112,12 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Kalau dorongan datang, tombol Jeda selalu ada di tengah bawah.</t>
+          <t>Masuk ke Beranda</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>If an urge comes, the Pause button is always at the bottom center.</t>
+          <t>Go to Home</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr"/>
@@ -3134,12 +3130,12 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>done_cta</t>
+          <t>tab_home</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Selesai</t>
+          <t>Tab bar</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3149,12 +3145,12 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Masuk ke Beranda</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Go to Home</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr"/>
@@ -3167,7 +3163,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>tab_home</t>
+          <t>tab_progress</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -3182,12 +3178,12 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Beranda</t>
+          <t>Progres</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr"/>
@@ -3200,7 +3196,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>tab_progress</t>
+          <t>tab_jeda</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -3215,15 +3211,19 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Progres</t>
+          <t>Jeda</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Progress</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr"/>
+          <t>Pause</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Center button. Option: keep 'Jeda' in EN as a brand word.</t>
+        </is>
+      </c>
       <c r="H76" s="6" t="inlineStr"/>
       <c r="I76" s="6" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>tab_jeda</t>
+          <t>tab_protect</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -3248,19 +3248,15 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Jeda</t>
+          <t>Lindungi</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Pause</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>Center button. Option: keep 'Jeda' in EN as a brand word.</t>
-        </is>
-      </c>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr"/>
       <c r="H77" s="6" t="inlineStr"/>
       <c r="I77" s="6" t="inlineStr"/>
     </row>
@@ -3270,7 +3266,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>tab_protect</t>
+          <t>tab_settings</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -3285,12 +3281,12 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Lindungi</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr"/>
@@ -3303,12 +3299,12 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>tab_settings</t>
+          <t>home_greeting</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Tab bar</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -3318,15 +3314,19 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Assalamu’alaikum</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr"/>
+          <t>Assalamu’alaikum</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Kept as-is in EN.</t>
+        </is>
+      </c>
       <c r="H79" s="6" t="inlineStr"/>
       <c r="I79" s="6" t="inlineStr"/>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>home_greeting</t>
+          <t>home_date_line</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Assalamu’alaikum</t>
+          <t>{weekday} · {hijri}</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Assalamu’alaikum</t>
+          <t>{weekday} · {hijri}</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Kept as-is in EN.</t>
+          <t>Example: 'Selasa · 13 Rabiul Akhir 1448 H' / 'Tuesday · 13 Rabi' al-Thani 1448 AH'.</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>home_date_line</t>
+          <t>home_hero_label</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -3388,17 +3388,17 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>{weekday} · {hijri}</t>
+          <t>Kamu sudah terjaga</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>{weekday} · {hijri}</t>
+          <t>You've kept</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Example: 'Selasa · 13 Rabiul Akhir 1448 H' / 'Tuesday · 13 Rabi' al-Thani 1448 AH'.</t>
+          <t>Rendered UPPERCASE. Reads with the big number: 'YOU'VE KEPT 42 days'.</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr"/>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>home_hero_label</t>
+          <t>home_hero_unit</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Kamu sudah terjaga</t>
+          <t>hari</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>You've kept</t>
+          <t>days</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Rendered UPPERCASE. Reads with the big number: 'YOU'VE KEPT 42 days'.</t>
+          <t>PLURAL in EN (1 day, 2 days). ID has no plural.</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr"/>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>home_hero_unit</t>
+          <t>home_today_clock</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -3462,19 +3462,15 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>hari</t>
+          <t>hari ini · {time}</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>PLURAL in EN (1 day, 2 days). ID has no plural.</t>
-        </is>
-      </c>
+          <t>today · {time}</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr"/>
       <c r="H83" s="6" t="inlineStr"/>
       <c r="I83" s="6" t="inlineStr"/>
     </row>
@@ -3484,7 +3480,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>home_today_clock</t>
+          <t>home_shortcut_dzikir</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -3499,12 +3495,12 @@
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>hari ini · {time}</t>
+          <t>Dzikir</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>today · {time}</t>
+          <t>Dhikr</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr"/>
@@ -3517,7 +3513,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>home_shortcut_dzikir</t>
+          <t>home_shortcut_sholat</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -3532,12 +3528,12 @@
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Dzikir</t>
+          <t>Sholat</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Dhikr</t>
+          <t>Prayer</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr"/>
@@ -3550,7 +3546,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>home_shortcut_sholat</t>
+          <t>home_shortcut_jurnal</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -3565,12 +3561,12 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Sholat</t>
+          <t>Jurnal</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Prayer</t>
+          <t>Journal</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr"/>
@@ -3583,7 +3579,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>home_shortcut_jurnal</t>
+          <t>home_shortcut_doa</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -3598,12 +3594,12 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Jurnal</t>
+          <t>Doa</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Journal</t>
+          <t>Dua</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr"/>
@@ -3616,7 +3612,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>home_shortcut_doa</t>
+          <t>home_bars_caption</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -3631,12 +3627,12 @@
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Doa</t>
+          <t>{kept} dari {target} hari menuju target pertamamu</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Dua</t>
+          <t>{kept} of {target} days toward your first goal</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr"/>
@@ -3649,7 +3645,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>home_bars_caption</t>
+          <t>home_bars_hint</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -3664,12 +3660,12 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>{kept} dari {target} hari menuju target pertamamu</t>
+          <t>Ketuk batang untuk detail · lihat semua →</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>{kept} of {target} days toward your first goal</t>
+          <t>Tap a bar for details · see all →</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr"/>
@@ -3682,7 +3678,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>home_bars_hint</t>
+          <t>home_prayer_card</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -3697,15 +3693,19 @@
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Ketuk batang untuk detail · lihat semua →</t>
+          <t>Sholat hari ini · {done}/5</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Tap a bar for details · see all →</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr"/>
+          <t>Today's prayers · {done}/5</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Rendered UPPERCASE.</t>
+        </is>
+      </c>
       <c r="H90" s="6" t="inlineStr"/>
       <c r="I90" s="6" t="inlineStr"/>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>home_prayer_card</t>
+          <t>home_next_prayer</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -3730,19 +3730,15 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Sholat hari ini · {done}/5</t>
+          <t>{prayer} · {time}</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Today's prayers · {done}/5</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>Rendered UPPERCASE.</t>
-        </is>
-      </c>
+          <t>{prayer} · {time}</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="6" t="inlineStr"/>
       <c r="I91" s="6" t="inlineStr"/>
     </row>
@@ -3752,7 +3748,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>home_next_prayer</t>
+          <t>home_prayers_complete</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -3767,12 +3763,12 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>{prayer} · {time}</t>
+          <t>Alhamdulillah, lengkap</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>{prayer} · {time}</t>
+          <t>Alhamdulillah, all done</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr"/>
@@ -3785,7 +3781,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>home_prayers_complete</t>
+          <t>home_dzikir_tag</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -3800,12 +3796,12 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Alhamdulillah, lengkap</t>
+          <t>Al-Ma’tsurat · 7 mnt</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Alhamdulillah, all done</t>
+          <t>Al-Ma’thurat · 7 min</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr"/>
@@ -3818,7 +3814,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>home_dzikir_tag</t>
+          <t>home_dzikir_card</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -3833,89 +3829,89 @@
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Al-Ma’tsurat · 7 mnt</t>
+          <t>Dzikir petang hari ini</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Al-Ma’thurat · 7 min</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr"/>
+          <t>Today's evening dhikr</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Becomes 'Dzikir pagi hari ini' / 'Today's morning dhikr' before Asr (proposed).</t>
+        </is>
+      </c>
       <c r="H94" s="6" t="inlineStr"/>
       <c r="I94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="7" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>home_dzikir_card</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>home_dzikir_card_morning</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>Beranda</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>Dzikir petang hari ini</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>Today's evening dhikr</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>Becomes 'Dzikir pagi hari ini' / 'Today's morning dhikr' before Asr (proposed).</t>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Dzikir pagi hari ini</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Today's morning dhikr</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Morning variant (proposed).</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
       <c r="I95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="7" t="n">
+      <c r="A96" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>home_dzikir_card_morning</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>home_slip_prompt</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>Beranda</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>Dzikir pagi hari ini</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>Today's morning dhikr</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>Morning variant (proposed).</t>
-        </is>
-      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Tadi sempat terpeleset? Pintu taubat selalu terbuka.</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>Slipped earlier? The door of repentance is always open.</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr"/>
       <c r="H96" s="6" t="inlineStr"/>
       <c r="I96" s="6" t="inlineStr"/>
     </row>
@@ -3925,7 +3921,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>home_slip_prompt</t>
+          <t>home_slip_cta</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -3940,12 +3936,12 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Tadi sempat terpeleset? Pintu taubat selalu terbuka.</t>
+          <t>Mulai lagi →</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Slipped earlier? The door of repentance is always open.</t>
+          <t>Begin again →</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr"/>
@@ -3953,70 +3949,74 @@
       <c r="I97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n">
+      <c r="A98" s="7" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>home_slip_cta</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>avatar_cd</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
         <is>
           <t>Beranda</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>Mulai lagi →</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>Begin again →</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Buka pengaturan</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>Open settings</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>Content description for the avatar.</t>
+        </is>
+      </c>
       <c r="H98" s="6" t="inlineStr"/>
       <c r="I98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="7" t="n">
+      <c r="A99" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>avatar_cd</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="inlineStr">
-        <is>
-          <t>Beranda</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>Buka pengaturan</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>Open settings</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>Content description for the avatar.</t>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>day_title</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Detail hari</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Hari ke-{n}</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Day {n}</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Rendered UPPERCASE in the sheet.</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -4028,12 +4028,12 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>day_title</t>
+          <t>day_status_kept</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Detail hari</t>
+          <t>Detail hari / Progres</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -4043,19 +4043,15 @@
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Hari ke-{n}</t>
+          <t>Terjaga</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Day {n}</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>Rendered UPPERCASE in the sheet.</t>
-        </is>
-      </c>
+          <t>Kept</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr"/>
       <c r="H100" s="6" t="inlineStr"/>
       <c r="I100" s="6" t="inlineStr"/>
     </row>
@@ -4065,7 +4061,7 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>day_status_kept</t>
+          <t>day_status_slip</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -4080,15 +4076,19 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Terjaga</t>
+          <t>Terpeleset</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Kept</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr"/>
+          <t>Slipped</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>Never use red or 'reset' language for this state.</t>
+        </is>
+      </c>
       <c r="H101" s="6" t="inlineStr"/>
       <c r="I101" s="6" t="inlineStr"/>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>day_status_slip</t>
+          <t>day_status_today</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -4113,19 +4113,15 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Terpeleset</t>
+          <t>Hari ini</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Slipped</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>Never use red or 'reset' language for this state.</t>
-        </is>
-      </c>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr"/>
       <c r="H102" s="6" t="inlineStr"/>
       <c r="I102" s="6" t="inlineStr"/>
     </row>
@@ -4135,12 +4131,12 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>day_status_today</t>
+          <t>day_checkin_yes</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Detail hari / Progres</t>
+          <t>Detail hari</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -4150,12 +4146,12 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Hari ini</t>
+          <t>Check-in · tercatat</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Check-in · logged</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr"/>
@@ -4168,7 +4164,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>day_checkin_yes</t>
+          <t>day_checkin_no</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -4183,12 +4179,12 @@
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Check-in · tercatat</t>
+          <t>Tidak ada check-in</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Check-in · logged</t>
+          <t>No check-in</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr"/>
@@ -4201,7 +4197,7 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>day_checkin_no</t>
+          <t>day_note_slip</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -4216,15 +4212,19 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Tidak ada check-in</t>
+          <t>Terpeleset malam itu, lalu kamu menekan “Mulai lagi” keesokan paginya.</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>No check-in</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr"/>
+          <t>You slipped that night, then tapped “Begin again” the next morning.</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Auto note for a slip day with no journal entry.</t>
+        </is>
+      </c>
       <c r="H105" s="6" t="inlineStr"/>
       <c r="I105" s="6" t="inlineStr"/>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>day_note_slip</t>
+          <t>day_note_today</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -4249,89 +4249,85 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Terpeleset malam itu, lalu kamu menekan “Mulai lagi” keesokan paginya.</t>
+          <t>Hari ini masih berjalan.</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>You slipped that night, then tapped “Begin again” the next morning.</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>Auto note for a slip day with no journal entry.</t>
-        </is>
-      </c>
+          <t>Today is still in progress.</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr"/>
       <c r="H106" s="6" t="inlineStr"/>
       <c r="I106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="7" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>day_note_today</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>day_note_empty</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
         <is>
           <t>Detail hari</t>
         </is>
       </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>Hari ini masih berjalan.</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>Today is still in progress.</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr"/>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>Tidak ada catatan.</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>No note.</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>Kept day with no journal entry.</t>
+        </is>
+      </c>
       <c r="H107" s="6" t="inlineStr"/>
       <c r="I107" s="6" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="7" t="n">
+      <c r="A108" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>day_note_empty</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="inlineStr">
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>common_close</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>Detail hari</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>Tidak ada catatan.</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>No note.</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>Kept day with no journal entry.</t>
-        </is>
-      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Tutup</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr"/>
       <c r="H108" s="6" t="inlineStr"/>
       <c r="I108" s="6" t="inlineStr"/>
     </row>
@@ -4341,12 +4337,12 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>common_close</t>
+          <t>jeda_header</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Detail hari</t>
+          <t>Jeda</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -4356,15 +4352,19 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Tutup</t>
+          <t>Jeda · {seconds} detik</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr"/>
+          <t>Pause · {seconds} seconds</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Rendered UPPERCASE, countdown 60→0. PLURAL in EN.</t>
+        </is>
+      </c>
       <c r="H109" s="6" t="inlineStr"/>
       <c r="I109" s="6" t="inlineStr"/>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>jeda_header</t>
+          <t>jeda_reminder</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -4389,19 +4389,15 @@
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Jeda · {seconds} detik</t>
+          <t>Ingat {kept} hari yang sudah kamu jaga. Ini juga akan lewat.</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Pause · {seconds} seconds</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>Rendered UPPERCASE, countdown 60→0. PLURAL in EN.</t>
-        </is>
-      </c>
+          <t>Remember the {kept} days you've kept. This too will pass.</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr"/>
       <c r="H110" s="6" t="inlineStr"/>
       <c r="I110" s="6" t="inlineStr"/>
     </row>
@@ -4411,7 +4407,7 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>jeda_reminder</t>
+          <t>jeda_inhale</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
@@ -4426,12 +4422,12 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Ingat {kept} hari yang sudah kamu jaga. Ini juga akan lewat.</t>
+          <t>Tarik napas…</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Remember the {kept} days you've kept. This too will pass.</t>
+          <t>Breathe in…</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr"/>
@@ -4444,7 +4440,7 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>jeda_inhale</t>
+          <t>jeda_exhale</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -4459,12 +4455,12 @@
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Tarik napas…</t>
+          <t>Hembuskan…</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Breathe in…</t>
+          <t>Breathe out…</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr"/>
@@ -4477,7 +4473,7 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>jeda_exhale</t>
+          <t>jeda_translit</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
@@ -4492,12 +4488,12 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>Hembuskan…</t>
+          <t>Astaghfirullāh al-‘aẓīm · napas ke-{n}</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>Breathe out…</t>
+          <t>Astaghfirullāh al-‘aẓīm · breath {n}</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr"/>
@@ -4510,7 +4506,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>jeda_translit</t>
+          <t>jeda_calmer</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -4525,12 +4521,12 @@
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Astaghfirullāh al-‘aẓīm · napas ke-{n}</t>
+          <t>Aku sudah lebih tenang</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Astaghfirullāh al-‘aẓīm · breath {n}</t>
+          <t>I feel calmer now</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr"/>
@@ -4543,7 +4539,7 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>jeda_calmer</t>
+          <t>jeda_read_doa</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -4558,12 +4554,12 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>Aku sudah lebih tenang</t>
+          <t>Baca doa perlindungan</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>I feel calmer now</t>
+          <t>Read a dua for protection</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr"/>
@@ -4576,12 +4572,12 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>jeda_read_doa</t>
+          <t>progress_title</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Jeda</t>
+          <t>Progres</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -4591,12 +4587,12 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Baca doa perlindungan</t>
+          <t>Progres</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Read a dua for protection</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr"/>
@@ -4609,7 +4605,7 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>progress_title</t>
+          <t>progress_of_target</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
@@ -4624,12 +4620,12 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>Progres</t>
+          <t>/ {target} hari</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>/ {target} days</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr"/>
@@ -4642,7 +4638,7 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>progress_of_target</t>
+          <t>progress_summary</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -4657,85 +4653,85 @@
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>/ {target} hari</t>
+          <t>Hari ke-{day} sejak mulai · {slips} hari terpeleset, semuanya kamu lanjutkan.</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>/ {target} days</t>
-        </is>
-      </c>
-      <c r="G118" s="5" t="inlineStr"/>
+          <t>Day {day} since you started · {slips} slips, and you kept going after every one.</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>PLURAL in EN for {slips}. When slips = 0, use the next row.</t>
+        </is>
+      </c>
       <c r="H118" s="6" t="inlineStr"/>
       <c r="I118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n">
+      <c r="A119" s="7" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>progress_summary</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>progress_summary_noslip</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
         <is>
           <t>Progres</t>
         </is>
       </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>Hari ke-{day} sejak mulai · {slips} hari terpeleset, semuanya kamu lanjutkan.</t>
-        </is>
-      </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>Day {day} since you started · {slips} slips, and you kept going after every one.</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>PLURAL in EN for {slips}. When slips = 0, use the next row.</t>
-        </is>
-      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>Hari ke-{day} sejak mulai.</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>Day {day} since you started.</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr"/>
       <c r="H119" s="6" t="inlineStr"/>
       <c r="I119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="7" t="n">
+      <c r="A120" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>progress_summary_noslip</t>
-        </is>
-      </c>
-      <c r="C120" s="7" t="inlineStr">
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>progress_legend_future</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
         <is>
           <t>Progres</t>
         </is>
       </c>
-      <c r="D120" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t>Hari ke-{day} sejak mulai.</t>
-        </is>
-      </c>
-      <c r="F120" s="7" t="inlineStr">
-        <is>
-          <t>Day {day} since you started.</t>
-        </is>
-      </c>
-      <c r="G120" s="7" t="inlineStr"/>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Belum dijalani</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr"/>
       <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" s="6" t="inlineStr"/>
     </row>
@@ -4745,7 +4741,7 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>progress_legend_future</t>
+          <t>progress_bar_caption</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
@@ -4760,12 +4756,12 @@
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>Belum dijalani</t>
+          <t>Makin tinggi batang, makin banyak sholat dan check-in di hari itu.</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>Not yet</t>
+          <t>The taller the bar, the more prayers and check-ins that day.</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr"/>
@@ -4778,7 +4774,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>progress_bar_caption</t>
+          <t>progress_sel_title</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -4793,12 +4789,12 @@
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Makin tinggi batang, makin banyak sholat dan check-in di hari itu.</t>
+          <t>Hari ke-{n} · {date}</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>The taller the bar, the more prayers and check-ins that day.</t>
+          <t>Day {n} · {date}</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr"/>
@@ -4811,7 +4807,7 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>progress_sel_title</t>
+          <t>progress_sel_sub</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
@@ -4826,12 +4822,12 @@
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>Hari ke-{n} · {date}</t>
+          <t>{hijri} · sholat {done}/5</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>Day {n} · {date}</t>
+          <t>{hijri} · prayers {done}/5</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr"/>
@@ -4844,7 +4840,7 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>progress_sel_sub</t>
+          <t>progress_stat_prayer</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -4859,12 +4855,12 @@
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>{hijri} · sholat {done}/5</t>
+          <t>sholat terjaga</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>{hijri} · prayers {done}/5</t>
+          <t>prayers kept</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr"/>
@@ -4877,7 +4873,7 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>progress_stat_prayer</t>
+          <t>progress_stat_checkin</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
@@ -4892,12 +4888,12 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>sholat terjaga</t>
+          <t>hari check-in</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>prayers kept</t>
+          <t>check-in days</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr"/>
@@ -4910,7 +4906,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>progress_stat_checkin</t>
+          <t>progress_stat_jeda</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -4925,12 +4921,12 @@
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>hari check-in</t>
+          <t>jeda berhasil</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>check-in days</t>
+          <t>pauses completed</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr"/>
@@ -4943,7 +4939,7 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>progress_stat_jeda</t>
+          <t>progress_insight_title</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
@@ -4958,12 +4954,12 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>jeda berhasil</t>
+          <t>Pola yang terlihat</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>pauses completed</t>
+          <t>A pattern we noticed</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr"/>
@@ -4976,7 +4972,7 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>progress_insight_title</t>
+          <t>progress_insight_body</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
@@ -4991,15 +4987,19 @@
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Pola yang terlihat</t>
+          <t>Kamu paling sering butuh jeda antara pukul {start} dan {end}. Mau diingatkan dzikir sebelum tidur?</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>A pattern we noticed</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr"/>
+          <t>You most often need a pause between {start} and {end}. Want a dhikr reminder before bed?</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>Show only when there is enough jeda data (proposed: ≥5 pauses).</t>
+        </is>
+      </c>
       <c r="H128" s="6" t="inlineStr"/>
       <c r="I128" s="6" t="inlineStr"/>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>progress_insight_body</t>
+          <t>progress_remind_cta</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
@@ -5024,19 +5024,15 @@
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>Kamu paling sering butuh jeda antara pukul {start} dan {end}. Mau diingatkan dzikir sebelum tidur?</t>
+          <t>Ingatkan jam {time}</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>You most often need a pause between {start} and {end}. Want a dhikr reminder before bed?</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="inlineStr">
-        <is>
-          <t>Show only when there is enough jeda data (proposed: ≥5 pauses).</t>
-        </is>
-      </c>
+          <t>Remind me at {time}</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr"/>
       <c r="H129" s="6" t="inlineStr"/>
       <c r="I129" s="6" t="inlineStr"/>
     </row>
@@ -5046,7 +5042,7 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>progress_remind_cta</t>
+          <t>progress_remind_on</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
@@ -5061,12 +5057,12 @@
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Ingatkan jam {time}</t>
+          <t>✓ Diingatkan jam {time}</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Remind me at {time}</t>
+          <t>✓ Reminder set for {time}</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr"/>
@@ -5079,12 +5075,12 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>progress_remind_on</t>
+          <t>sholat_title</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Progres</t>
+          <t>Sholat</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
@@ -5094,12 +5090,12 @@
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>✓ Diingatkan jam {time}</t>
+          <t>Sholat hari ini</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>✓ Reminder set for {time}</t>
+          <t>Today's prayers</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr"/>
@@ -5112,7 +5108,7 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>sholat_title</t>
+          <t>sholat_of_five</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -5127,12 +5123,12 @@
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Sholat hari ini</t>
+          <t>/ 5</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>Today's prayers</t>
+          <t>/ 5</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr"/>
@@ -5145,7 +5141,7 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>sholat_of_five</t>
+          <t>sholat_location</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
@@ -5160,12 +5156,12 @@
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>/ 5</t>
+          <t>{city} · {hijri}</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>/ 5</t>
+          <t>{city} · {hijri}</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr"/>
@@ -5178,7 +5174,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>sholat_location</t>
+          <t>sholat_footer</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -5193,12 +5189,12 @@
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>{city} · {hijri}</t>
+          <t>Check-in setelah sholat ikut membuat batang hari ini lebih tinggi.</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>{city} · {hijri}</t>
+          <t>Checking in after each prayer makes today's bar taller.</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr"/>
@@ -5206,35 +5202,39 @@
       <c r="I134" s="6" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n">
+      <c r="A135" s="7" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>sholat_footer</t>
-        </is>
-      </c>
-      <c r="C135" s="5" t="inlineStr">
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>sholat_location_pick</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
         <is>
           <t>Sholat</t>
         </is>
       </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>Check-in setelah sholat ikut membuat batang hari ini lebih tinggi.</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>Checking in after each prayer makes today's bar taller.</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr"/>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>Pilih kota</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>Choose city</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>Fallback when location is off or denied.</t>
+        </is>
+      </c>
       <c r="H135" s="6" t="inlineStr"/>
       <c r="I135" s="6" t="inlineStr"/>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>sholat_location_pick</t>
+          <t>sholat_use_location</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
@@ -5259,52 +5259,48 @@
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>Pilih kota</t>
+          <t>Pakai lokasi sekarang</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Choose city</t>
-        </is>
-      </c>
-      <c r="G136" s="7" t="inlineStr">
-        <is>
-          <t>Fallback when location is off or denied.</t>
-        </is>
-      </c>
+          <t>Use current location</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr"/>
       <c r="H136" s="6" t="inlineStr"/>
       <c r="I136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="7" t="n">
+      <c r="A137" s="5" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="7" t="inlineStr">
-        <is>
-          <t>sholat_use_location</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="inlineStr">
-        <is>
-          <t>Sholat</t>
-        </is>
-      </c>
-      <c r="D137" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
-        <is>
-          <t>Pakai lokasi sekarang</t>
-        </is>
-      </c>
-      <c r="F137" s="7" t="inlineStr">
-        <is>
-          <t>Use current location</t>
-        </is>
-      </c>
-      <c r="G137" s="7" t="inlineStr"/>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>prayer_fajr</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Prayer names</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>Subuh</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Fajr</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr"/>
       <c r="H137" s="6" t="inlineStr"/>
       <c r="I137" s="6" t="inlineStr"/>
     </row>
@@ -5314,7 +5310,7 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>prayer_fajr</t>
+          <t>prayer_dhuhr</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
@@ -5329,12 +5325,12 @@
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Subuh</t>
+          <t>Dzuhur</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>Fajr</t>
+          <t>Dhuhr</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr"/>
@@ -5347,7 +5343,7 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>prayer_dhuhr</t>
+          <t>prayer_asr</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
@@ -5362,12 +5358,12 @@
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>Dzuhur</t>
+          <t>Ashar</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>Dhuhr</t>
+          <t>Asr</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr"/>
@@ -5380,7 +5376,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>prayer_asr</t>
+          <t>prayer_maghrib</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
@@ -5395,12 +5391,12 @@
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Ashar</t>
+          <t>Maghrib</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>Asr</t>
+          <t>Maghrib</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr"/>
@@ -5413,7 +5409,7 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>prayer_maghrib</t>
+          <t>prayer_isha</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
@@ -5428,12 +5424,12 @@
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>Maghrib</t>
+          <t>Isya</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>Maghrib</t>
+          <t>Isha</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr"/>
@@ -5446,12 +5442,12 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>prayer_isha</t>
+          <t>dzikir_title</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Prayer names</t>
+          <t>Dzikir</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
@@ -5461,12 +5457,12 @@
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>Isya</t>
+          <t>Dzikir setelah sholat</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>Isha</t>
+          <t>Dhikr after prayer</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr"/>
@@ -5479,7 +5475,7 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>dzikir_title</t>
+          <t>dzikir_hint</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
@@ -5494,12 +5490,12 @@
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>Dzikir setelah sholat</t>
+          <t>dari 33 · ketuk</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>Dhikr after prayer</t>
+          <t>of 33 · tap</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr"/>
@@ -5512,7 +5508,7 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>dzikir_hint</t>
+          <t>dzikir_done</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
@@ -5527,12 +5523,12 @@
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>dari 33 · ketuk</t>
+          <t>selesai · 99</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>of 33 · tap</t>
+          <t>done · 99</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr"/>
@@ -5545,7 +5541,7 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>dzikir_done</t>
+          <t>dzikir_footer</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
@@ -5560,12 +5556,12 @@
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>selesai · 99</t>
+          <t>Getar halus setiap 33. Bisa juga pakai tombol volume.</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>done · 99</t>
+          <t>A gentle vibration every 33. You can also use the volume buttons.</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr"/>
@@ -5573,72 +5569,72 @@
       <c r="I145" s="6" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="n">
+      <c r="A146" s="7" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="5" t="inlineStr">
-        <is>
-          <t>dzikir_footer</t>
-        </is>
-      </c>
-      <c r="C146" s="5" t="inlineStr">
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>dzikir_reset_cd</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
         <is>
           <t>Dzikir</t>
         </is>
       </c>
-      <c r="D146" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>Getar halus setiap 33. Bisa juga pakai tombol volume.</t>
-        </is>
-      </c>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>A gentle vibration every 33. You can also use the volume buttons.</t>
-        </is>
-      </c>
-      <c r="G146" s="5" t="inlineStr"/>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>Ulangi dari awal</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>Start over</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>Content description for ↺.</t>
+        </is>
+      </c>
       <c r="H146" s="6" t="inlineStr"/>
       <c r="I146" s="6" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="7" t="n">
+      <c r="A147" s="5" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="7" t="inlineStr">
-        <is>
-          <t>dzikir_reset_cd</t>
-        </is>
-      </c>
-      <c r="C147" s="7" t="inlineStr">
-        <is>
-          <t>Dzikir</t>
-        </is>
-      </c>
-      <c r="D147" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="inlineStr">
-        <is>
-          <t>Ulangi dari awal</t>
-        </is>
-      </c>
-      <c r="F147" s="7" t="inlineStr">
-        <is>
-          <t>Start over</t>
-        </is>
-      </c>
-      <c r="G147" s="7" t="inlineStr">
-        <is>
-          <t>Content description for ↺.</t>
-        </is>
-      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>doa_title</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>Doa</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>Doa saat goyah</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Duas for shaky moments</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr"/>
       <c r="H147" s="6" t="inlineStr"/>
       <c r="I147" s="6" t="inlineStr"/>
     </row>
@@ -5648,7 +5644,7 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>doa_title</t>
+          <t>doa_subtitle</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
@@ -5663,12 +5659,12 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Doa saat goyah</t>
+          <t>Baca pelan-pelan. Tidak perlu hafal, cukup hadirkan hati.</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>Duas for shaky moments</t>
+          <t>Read slowly. No need to memorize. Just bring your heart.</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr"/>
@@ -5681,12 +5677,12 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>doa_subtitle</t>
+          <t>jurnal_title</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Doa</t>
+          <t>Jurnal</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -5696,12 +5692,12 @@
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>Baca pelan-pelan. Tidak perlu hafal, cukup hadirkan hati.</t>
+          <t>Jurnal</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>Read slowly. No need to memorize. Just bring your heart.</t>
+          <t>Journal</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr"/>
@@ -5714,7 +5710,7 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>jurnal_title</t>
+          <t>jurnal_question</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
@@ -5729,12 +5725,12 @@
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>Jurnal</t>
+          <t>Bagaimana hatimu hari ini?</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>Journal</t>
+          <t>How is your heart today?</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr"/>
@@ -5747,7 +5743,7 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>jurnal_question</t>
+          <t>mood_strong</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
@@ -5762,12 +5758,12 @@
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>Bagaimana hatimu hari ini?</t>
+          <t>Kuat</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>How is your heart today?</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr"/>
@@ -5780,7 +5776,7 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>mood_strong</t>
+          <t>mood_okay</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
@@ -5795,12 +5791,12 @@
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Kuat</t>
+          <t>Biasa</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Okay</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr"/>
@@ -5813,7 +5809,7 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>mood_okay</t>
+          <t>mood_shaky</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
@@ -5828,12 +5824,12 @@
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>Biasa</t>
+          <t>Goyah</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>Okay</t>
+          <t>Shaky</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr"/>
@@ -5846,7 +5842,7 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>mood_shaky</t>
+          <t>mood_heavy</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
@@ -5861,12 +5857,12 @@
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Goyah</t>
+          <t>Berat</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>Shaky</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr"/>
@@ -5879,7 +5875,7 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>mood_heavy</t>
+          <t>jurnal_placeholder</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
@@ -5894,12 +5890,12 @@
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>Berat</t>
+          <t>Tulis sedikit. Apa yang membantu, apa yang berat…</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Write a little. What helped, what felt heavy…</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr"/>
@@ -5912,7 +5908,7 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>jurnal_placeholder</t>
+          <t>jurnal_locked_note</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
@@ -5927,12 +5923,12 @@
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Tulis sedikit. Apa yang membantu, apa yang berat…</t>
+          <t>Terkunci dengan PIN. Hanya kamu yang bisa membaca.</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>Write a little. What helped, what felt heavy…</t>
+          <t>Locked with your PIN. Only you can read it.</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr"/>
@@ -5945,7 +5941,7 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>jurnal_locked_note</t>
+          <t>common_save</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
@@ -5960,12 +5956,12 @@
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>Terkunci dengan PIN. Hanya kamu yang bisa membaca.</t>
+          <t>Simpan</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>Locked with your PIN. Only you can read it.</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr"/>
@@ -5978,7 +5974,7 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>common_save</t>
+          <t>jurnal_saved_toast</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
@@ -5993,12 +5989,12 @@
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>Simpan</t>
+          <t>Tersimpan. Terima kasih sudah jujur pada dirimu.</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Saved. Thank you for being honest with yourself.</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr"/>
@@ -6011,7 +6007,7 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>jurnal_saved_toast</t>
+          <t>jurnal_earlier</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
@@ -6026,12 +6022,12 @@
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>Tersimpan. Terima kasih sudah jujur pada dirimu.</t>
+          <t>Sebelumnya</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>Saved. Thank you for being honest with yourself.</t>
+          <t>Earlier</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr"/>
@@ -6044,7 +6040,7 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>jurnal_earlier</t>
+          <t>jurnal_entry_meta</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
@@ -6059,12 +6055,12 @@
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>Sebelumnya</t>
+          <t>{weekday} · {mood}</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>Earlier</t>
+          <t>{weekday} · {mood}</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr"/>
@@ -6072,72 +6068,72 @@
       <c r="I160" s="6" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="n">
+      <c r="A161" s="7" t="n">
         <v>160</v>
       </c>
-      <c r="B161" s="5" t="inlineStr">
-        <is>
-          <t>jurnal_entry_meta</t>
-        </is>
-      </c>
-      <c r="C161" s="5" t="inlineStr">
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>jurnal_empty</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr">
         <is>
           <t>Jurnal</t>
         </is>
       </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>{weekday} · {mood}</t>
-        </is>
-      </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>{weekday} · {mood}</t>
-        </is>
-      </c>
-      <c r="G161" s="5" t="inlineStr"/>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>Belum ada catatan. Tulisan pertamamu akan muncul di sini.</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>No entries yet. Your first one will show up here.</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>Empty state (design shows sample entries only).</t>
+        </is>
+      </c>
       <c r="H161" s="6" t="inlineStr"/>
       <c r="I161" s="6" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="7" t="n">
+      <c r="A162" s="5" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="7" t="inlineStr">
-        <is>
-          <t>jurnal_empty</t>
-        </is>
-      </c>
-      <c r="C162" s="7" t="inlineStr">
-        <is>
-          <t>Jurnal</t>
-        </is>
-      </c>
-      <c r="D162" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E162" s="7" t="inlineStr">
-        <is>
-          <t>Belum ada catatan. Tulisan pertamamu akan muncul di sini.</t>
-        </is>
-      </c>
-      <c r="F162" s="7" t="inlineStr">
-        <is>
-          <t>No entries yet. Your first one will show up here.</t>
-        </is>
-      </c>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>Empty state (design shows sample entries only).</t>
-        </is>
-      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>mulai_title</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>Mulai lagi</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>Terpeleset bukan akhir perjalanan.</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>A slip is not the end of the journey.</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr"/>
       <c r="H162" s="6" t="inlineStr"/>
       <c r="I162" s="6" t="inlineStr"/>
     </row>
@@ -6147,7 +6143,7 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>mulai_title</t>
+          <t>mulai_body</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
@@ -6162,12 +6158,12 @@
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>Terpeleset bukan akhir perjalanan.</t>
+          <t>{kept} hari yang kamu jaga tetap tercatat. Hari ini cukup jadi satu titik redup di antaranya.</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>A slip is not the end of the journey.</t>
+          <t>The {kept} days you've kept still count. Today is just one dim dot among them.</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr"/>
@@ -6180,7 +6176,7 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>mulai_body</t>
+          <t>mulai_step_1</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
@@ -6195,12 +6191,12 @@
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>{kept} hari yang kamu jaga tetap tercatat. Hari ini cukup jadi satu titik redup di antaranya.</t>
+          <t>Istighfar</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>The {kept} days you've kept still count. Today is just one dim dot among them.</t>
+          <t>Istighfar</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr"/>
@@ -6213,7 +6209,7 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>mulai_step_1</t>
+          <t>mulai_step_1_desc</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
@@ -6228,12 +6224,12 @@
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>Istighfar</t>
+          <t>Astaghfirullāh, 3×</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>Istighfar</t>
+          <t>Astaghfirullāh, 3×</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr"/>
@@ -6246,7 +6242,7 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>mulai_step_1_desc</t>
+          <t>mulai_step_2</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
@@ -6261,12 +6257,12 @@
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Astaghfirullāh, 3×</t>
+          <t>Wudhu &amp; sholat taubat</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>Astaghfirullāh, 3×</t>
+          <t>Wudu &amp; the prayer of repentance</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr"/>
@@ -6279,7 +6275,7 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>mulai_step_2</t>
+          <t>mulai_step_2_desc</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
@@ -6294,12 +6290,12 @@
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>Wudhu &amp; sholat taubat</t>
+          <t>2 rakaat, kapan pun kamu siap</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>Wudu &amp; the prayer of repentance</t>
+          <t>2 rak‘ahs, whenever you're ready</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr"/>
@@ -6312,7 +6308,7 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>mulai_step_2_desc</t>
+          <t>mulai_step_3</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
@@ -6327,12 +6323,12 @@
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>2 rakaat, kapan pun kamu siap</t>
+          <t>Satu langkah kecil</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>2 rak‘ahs, whenever you're ready</t>
+          <t>One small step</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr"/>
@@ -6345,7 +6341,7 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>mulai_step_3</t>
+          <t>mulai_step_3_desc</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
@@ -6360,12 +6356,12 @@
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>Satu langkah kecil</t>
+          <t>Hapus satu pemicu, misalnya satu aplikasi</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>One small step</t>
+          <t>Remove one trigger, like a single app</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr"/>
@@ -6378,7 +6374,7 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>mulai_step_3_desc</t>
+          <t>mulai_triggers_title</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
@@ -6393,12 +6389,12 @@
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>Hapus satu pemicu, misalnya satu aplikasi</t>
+          <t>Apa pemicunya? (hanya untukmu)</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>Remove one trigger, like a single app</t>
+          <t>What triggered it? (just for you)</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr"/>
@@ -6411,7 +6407,7 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>mulai_triggers_title</t>
+          <t>trigger_alone_night</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
@@ -6426,12 +6422,12 @@
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>Apa pemicunya? (hanya untukmu)</t>
+          <t>Sendirian malam</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>What triggered it? (just for you)</t>
+          <t>Alone at night</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr"/>
@@ -6444,7 +6440,7 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>trigger_alone_night</t>
+          <t>trigger_bored</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
@@ -6459,12 +6455,12 @@
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Sendirian malam</t>
+          <t>Bosan</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>Alone at night</t>
+          <t>Bored</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr"/>
@@ -6477,7 +6473,7 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>trigger_bored</t>
+          <t>trigger_work_stress</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
@@ -6492,12 +6488,12 @@
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>Bosan</t>
+          <t>Stres kerja</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>Bored</t>
+          <t>Work stress</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr"/>
@@ -6510,7 +6506,7 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>trigger_work_stress</t>
+          <t>trigger_social</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
@@ -6525,12 +6521,12 @@
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Stres kerja</t>
+          <t>Media sosial</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>Work stress</t>
+          <t>Social media</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr"/>
@@ -6543,7 +6539,7 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>trigger_social</t>
+          <t>trigger_tired</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
@@ -6558,12 +6554,12 @@
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>Media sosial</t>
+          <t>Lelah</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>Social media</t>
+          <t>Tired</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr"/>
@@ -6576,7 +6572,7 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>trigger_tired</t>
+          <t>trigger_no_sleep</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
@@ -6591,12 +6587,12 @@
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Lelah</t>
+          <t>Sulit tidur</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>Tired</t>
+          <t>Couldn't sleep</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr"/>
@@ -6609,7 +6605,7 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>trigger_no_sleep</t>
+          <t>mulai_cta</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
@@ -6624,12 +6620,12 @@
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>Sulit tidur</t>
+          <t>Mulai lagi hari ini</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>Couldn't sleep</t>
+          <t>Begin again today</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr"/>
@@ -6637,72 +6633,72 @@
       <c r="I177" s="6" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="5" t="n">
+      <c r="A178" s="7" t="n">
         <v>177</v>
       </c>
-      <c r="B178" s="5" t="inlineStr">
-        <is>
-          <t>mulai_cta</t>
-        </is>
-      </c>
-      <c r="C178" s="5" t="inlineStr">
+      <c r="B178" s="7" t="inlineStr">
+        <is>
+          <t>mulai_close_cd</t>
+        </is>
+      </c>
+      <c r="C178" s="7" t="inlineStr">
         <is>
           <t>Mulai lagi</t>
         </is>
       </c>
-      <c r="D178" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E178" s="5" t="inlineStr">
-        <is>
-          <t>Mulai lagi hari ini</t>
-        </is>
-      </c>
-      <c r="F178" s="5" t="inlineStr">
-        <is>
-          <t>Begin again today</t>
-        </is>
-      </c>
-      <c r="G178" s="5" t="inlineStr"/>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>Tutup</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>Content description for ✕.</t>
+        </is>
+      </c>
       <c r="H178" s="6" t="inlineStr"/>
       <c r="I178" s="6" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="7" t="n">
+      <c r="A179" s="5" t="n">
         <v>178</v>
       </c>
-      <c r="B179" s="7" t="inlineStr">
-        <is>
-          <t>mulai_close_cd</t>
-        </is>
-      </c>
-      <c r="C179" s="7" t="inlineStr">
-        <is>
-          <t>Mulai lagi</t>
-        </is>
-      </c>
-      <c r="D179" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="inlineStr">
-        <is>
-          <t>Tutup</t>
-        </is>
-      </c>
-      <c r="F179" s="7" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="G179" s="7" t="inlineStr">
-        <is>
-          <t>Content description for ✕.</t>
-        </is>
-      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>protect_title</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>Lindungi</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>Lindungi</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr"/>
       <c r="H179" s="6" t="inlineStr"/>
       <c r="I179" s="6" t="inlineStr"/>
     </row>
@@ -6712,7 +6708,7 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>protect_title</t>
+          <t>protect_desc</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
@@ -6727,12 +6723,12 @@
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Lindungi</t>
+          <t>Aplikasi tertentu dikunci di jam-jam rawan. Bukan hukuman, hanya pagar kecil supaya kamu tidak berjuang sendirian.</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Chosen apps are locked during your hard hours. Not a punishment, just a small fence so you don't fight alone.</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr"/>
@@ -6745,7 +6741,7 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>protect_desc</t>
+          <t>protect_schedule</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
@@ -6760,12 +6756,12 @@
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>Aplikasi tertentu dikunci di jam-jam rawan. Bukan hukuman, hanya pagar kecil supaya kamu tidak berjuang sendirian.</t>
+          <t>Jadwal</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>Chosen apps are locked during your hard hours. Not a punishment, just a small fence so you don't fight alone.</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr"/>
@@ -6778,7 +6774,7 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>protect_schedule</t>
+          <t>slot_tag_risky</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
@@ -6793,12 +6789,12 @@
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Jadwal</t>
+          <t>Rawan</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>High-risk</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr"/>
@@ -6811,7 +6807,7 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>slot_tag_risky</t>
+          <t>slot_tag_optional</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
@@ -6826,12 +6822,12 @@
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>Rawan</t>
+          <t>Opsional</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>High-risk</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr"/>
@@ -6844,7 +6840,7 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>slot_tag_optional</t>
+          <t>slot_tag_auto</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
@@ -6859,12 +6855,12 @@
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Opsional</t>
+          <t>Otomatis</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr"/>
@@ -6877,7 +6873,7 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>slot_tag_auto</t>
+          <t>slot_1_desc</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
@@ -6892,12 +6888,12 @@
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>Otomatis</t>
+          <t>Setiap hari · dari pola jedamu</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Every day · based on your pauses</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr"/>
@@ -6910,7 +6906,7 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>slot_1_desc</t>
+          <t>slot_2_desc</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
@@ -6925,12 +6921,12 @@
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Setiap hari · dari pola jedamu</t>
+          <t>Senin–Jumat · jam sepi di kantor</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>Every day · based on your pauses</t>
+          <t>Mon–Fri · quiet hours at work</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr"/>
@@ -6943,7 +6939,7 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>slot_2_desc</t>
+          <t>slot_3_title</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
@@ -6958,15 +6954,19 @@
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>Senin–Jumat · jam sepi di kantor</t>
+          <t>Saat sendirian di rumah</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>Mon–Fri · quiet hours at work</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr"/>
+          <t>When alone at home</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>Needs location permission + geofencing. Proposal: leave out of v1.</t>
+        </is>
+      </c>
       <c r="H187" s="6" t="inlineStr"/>
       <c r="I187" s="6" t="inlineStr"/>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>slot_3_title</t>
+          <t>slot_3_desc</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
@@ -6991,19 +6991,15 @@
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Saat sendirian di rumah</t>
+          <t>Saat lokasi Rumah &amp; tidak ada jadwal</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>When alone at home</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr">
-        <is>
-          <t>Needs location permission + geofencing. Proposal: leave out of v1.</t>
-        </is>
-      </c>
+          <t>When you're at Home &amp; nothing is scheduled</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr"/>
       <c r="H188" s="6" t="inlineStr"/>
       <c r="I188" s="6" t="inlineStr"/>
     </row>
@@ -7013,7 +7009,7 @@
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>slot_3_desc</t>
+          <t>protect_locked_apps</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
@@ -7028,89 +7024,89 @@
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>Saat lokasi Rumah &amp; tidak ada jadwal</t>
+          <t>Yang dikunci · {n} aplikasi</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>When you're at Home &amp; nothing is scheduled</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr"/>
+          <t>Locked · {n} apps</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>PLURAL in EN (1 app).</t>
+        </is>
+      </c>
       <c r="H189" s="6" t="inlineStr"/>
       <c r="I189" s="6" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="n">
+      <c r="A190" s="7" t="n">
         <v>189</v>
       </c>
-      <c r="B190" s="5" t="inlineStr">
-        <is>
-          <t>protect_locked_apps</t>
-        </is>
-      </c>
-      <c r="C190" s="5" t="inlineStr">
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>protect_add_app</t>
+        </is>
+      </c>
+      <c r="C190" s="7" t="inlineStr">
         <is>
           <t>Lindungi</t>
         </is>
       </c>
-      <c r="D190" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E190" s="5" t="inlineStr">
-        <is>
-          <t>Yang dikunci · {n} aplikasi</t>
-        </is>
-      </c>
-      <c r="F190" s="5" t="inlineStr">
-        <is>
-          <t>Locked · {n} apps</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr">
-        <is>
-          <t>PLURAL in EN (1 app).</t>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>+ Tambah aplikasi</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>+ Add app</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>Opens the installed-app picker (replaces iOS FamilyActivityPicker).</t>
         </is>
       </c>
       <c r="H190" s="6" t="inlineStr"/>
       <c r="I190" s="6" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="7" t="n">
+      <c r="A191" s="5" t="n">
         <v>190</v>
       </c>
-      <c r="B191" s="7" t="inlineStr">
-        <is>
-          <t>protect_add_app</t>
-        </is>
-      </c>
-      <c r="C191" s="7" t="inlineStr">
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>protect_when_opened</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
         <is>
           <t>Lindungi</t>
         </is>
       </c>
-      <c r="D191" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E191" s="7" t="inlineStr">
-        <is>
-          <t>+ Tambah aplikasi</t>
-        </is>
-      </c>
-      <c r="F191" s="7" t="inlineStr">
-        <is>
-          <t>+ Add app</t>
-        </is>
-      </c>
-      <c r="G191" s="7" t="inlineStr">
-        <is>
-          <t>Opens the installed-app picker (replaces iOS FamilyActivityPicker).</t>
-        </is>
-      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>Saat dibuka</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>When opened</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr"/>
       <c r="H191" s="6" t="inlineStr"/>
       <c r="I191" s="6" t="inlineStr"/>
     </row>
@@ -7120,7 +7116,7 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>protect_when_opened</t>
+          <t>mode_gentle</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
@@ -7135,12 +7131,12 @@
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Saat dibuka</t>
+          <t>Pengingat lembut</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>When opened</t>
+          <t>Gentle reminder</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr"/>
@@ -7153,7 +7149,7 @@
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>mode_gentle</t>
+          <t>mode_gentle_desc</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
@@ -7168,12 +7164,12 @@
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>Pengingat lembut</t>
+          <t>Muncul pesan, tetap bisa lanjut</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>Gentle reminder</t>
+          <t>A message appears, you can still continue</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr"/>
@@ -7186,7 +7182,7 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>mode_gentle_desc</t>
+          <t>mode_pause</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
@@ -7201,12 +7197,12 @@
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Muncul pesan, tetap bisa lanjut</t>
+          <t>Jeda 60 detik dulu</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>A message appears, you can still continue</t>
+          <t>60-second pause first</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr"/>
@@ -7219,7 +7215,7 @@
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>mode_pause</t>
+          <t>mode_pause_desc</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
@@ -7234,12 +7230,12 @@
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>Jeda 60 detik dulu</t>
+          <t>Napas dulu, lalu boleh buka 5 menit</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>60-second pause first</t>
+          <t>Breathe first, then it opens for 5 minutes</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr"/>
@@ -7252,7 +7248,7 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>mode_pause_desc</t>
+          <t>mode_full</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
@@ -7267,12 +7263,12 @@
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Napas dulu, lalu boleh buka 5 menit</t>
+          <t>Kunci penuh</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>Breathe first, then it opens for 5 minutes</t>
+          <t>Full lock</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr"/>
@@ -7285,7 +7281,7 @@
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>mode_full</t>
+          <t>mode_full_desc</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
@@ -7300,12 +7296,12 @@
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>Kunci penuh</t>
+          <t>Tidak bisa dibuka sampai jadwal selesai</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>Full lock</t>
+          <t>Can't be opened until the schedule ends</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr"/>
@@ -7318,7 +7314,7 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>mode_full_desc</t>
+          <t>protect_preview_shield</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
@@ -7333,12 +7329,12 @@
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>Tidak bisa dibuka sampai jadwal selesai</t>
+          <t>Lihat tampilan saat terkunci</t>
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>Can't be opened until the schedule ends</t>
+          <t>Preview the locked screen</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr"/>
@@ -7351,12 +7347,12 @@
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>protect_preview_shield</t>
+          <t>shield_label</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>Lindungi</t>
+          <t>Layar terkunci</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
@@ -7366,15 +7362,19 @@
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>Lihat tampilan saat terkunci</t>
+          <t>Waktu terjaga · sampai {time}</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>Preview the locked screen</t>
-        </is>
-      </c>
-      <c r="G199" s="5" t="inlineStr"/>
+          <t>Guarded hours · until {time}</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>Rendered UPPERCASE.</t>
+        </is>
+      </c>
       <c r="H199" s="6" t="inlineStr"/>
       <c r="I199" s="6" t="inlineStr"/>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>shield_label</t>
+          <t>shield_title</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
@@ -7399,93 +7399,89 @@
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Waktu terjaga · sampai {time}</t>
+          <t>Sudah larut. Istirahat dulu, yuk.</t>
         </is>
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
-          <t>Guarded hours · until {time}</t>
+          <t>It's late. Time to rest, okay?</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>Rendered UPPERCASE.</t>
+          <t>Fits a late-night slot only. A daytime variant is proposed below.</t>
         </is>
       </c>
       <c r="H200" s="6" t="inlineStr"/>
       <c r="I200" s="6" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="5" t="n">
+      <c r="A201" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="B201" s="5" t="inlineStr">
-        <is>
-          <t>shield_title</t>
-        </is>
-      </c>
-      <c r="C201" s="5" t="inlineStr">
+      <c r="B201" s="7" t="inlineStr">
+        <is>
+          <t>shield_title_day</t>
+        </is>
+      </c>
+      <c r="C201" s="7" t="inlineStr">
         <is>
           <t>Layar terkunci</t>
         </is>
       </c>
-      <c r="D201" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E201" s="5" t="inlineStr">
-        <is>
-          <t>Sudah larut. Istirahat dulu, yuk.</t>
-        </is>
-      </c>
-      <c r="F201" s="5" t="inlineStr">
-        <is>
-          <t>It's late. Time to rest, okay?</t>
-        </is>
-      </c>
-      <c r="G201" s="5" t="inlineStr">
-        <is>
-          <t>Fits a late-night slot only. A daytime variant is proposed below.</t>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="inlineStr">
+        <is>
+          <t>Sebentar dulu. Tarik napas, yuk.</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>Hold on a moment. Let's take a breath.</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>For daytime slots (e.g. 13.00–15.00).</t>
         </is>
       </c>
       <c r="H201" s="6" t="inlineStr"/>
       <c r="I201" s="6" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="7" t="n">
+      <c r="A202" s="5" t="n">
         <v>201</v>
       </c>
-      <c r="B202" s="7" t="inlineStr">
-        <is>
-          <t>shield_title_day</t>
-        </is>
-      </c>
-      <c r="C202" s="7" t="inlineStr">
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>shield_body</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
         <is>
           <t>Layar terkunci</t>
         </is>
       </c>
-      <c r="D202" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E202" s="7" t="inlineStr">
-        <is>
-          <t>Sebentar dulu. Tarik napas, yuk.</t>
-        </is>
-      </c>
-      <c r="F202" s="7" t="inlineStr">
-        <is>
-          <t>Hold on a moment. Let's take a breath.</t>
-        </is>
-      </c>
-      <c r="G202" s="7" t="inlineStr">
-        <is>
-          <t>For daytime slots (e.g. 13.00–15.00).</t>
-        </is>
-      </c>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>Kamu sendiri yang memasang pagar ini, di saat kamu sedang kuat.</t>
+        </is>
+      </c>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>You put up this fence yourself, at a moment you were strong.</t>
+        </is>
+      </c>
+      <c r="G202" s="5" t="inlineStr"/>
       <c r="H202" s="6" t="inlineStr"/>
       <c r="I202" s="6" t="inlineStr"/>
     </row>
@@ -7495,7 +7491,7 @@
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>shield_body</t>
+          <t>shield_take_jeda</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
@@ -7510,12 +7506,12 @@
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>Kamu sendiri yang memasang pagar ini, di saat kamu sedang kuat.</t>
+          <t>Ambil jeda 60 detik</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>You put up this fence yourself, at a moment you were strong.</t>
+          <t>Take a 60-second pause</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr"/>
@@ -7528,7 +7524,7 @@
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>shield_take_jeda</t>
+          <t>shield_close_app</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
@@ -7543,12 +7539,12 @@
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>Ambil jeda 60 detik</t>
+          <t>Tutup aplikasi</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>Take a 60-second pause</t>
+          <t>Close the app</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr"/>
@@ -7556,72 +7552,72 @@
       <c r="I204" s="6" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="5" t="n">
+      <c r="A205" s="7" t="n">
         <v>204</v>
       </c>
-      <c r="B205" s="5" t="inlineStr">
-        <is>
-          <t>shield_close_app</t>
-        </is>
-      </c>
-      <c r="C205" s="5" t="inlineStr">
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>shield_continue</t>
+        </is>
+      </c>
+      <c r="C205" s="7" t="inlineStr">
         <is>
           <t>Layar terkunci</t>
         </is>
       </c>
-      <c r="D205" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E205" s="5" t="inlineStr">
-        <is>
-          <t>Tutup aplikasi</t>
-        </is>
-      </c>
-      <c r="F205" s="5" t="inlineStr">
-        <is>
-          <t>Close the app</t>
-        </is>
-      </c>
-      <c r="G205" s="5" t="inlineStr"/>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>Tetap lanjutkan</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>Continue anyway</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>Needed for 'Pengingat lembut' mode, where the design has no continue button.</t>
+        </is>
+      </c>
       <c r="H205" s="6" t="inlineStr"/>
       <c r="I205" s="6" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="7" t="n">
+      <c r="A206" s="5" t="n">
         <v>205</v>
       </c>
-      <c r="B206" s="7" t="inlineStr">
-        <is>
-          <t>shield_continue</t>
-        </is>
-      </c>
-      <c r="C206" s="7" t="inlineStr">
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>shield_note_gentle</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
         <is>
           <t>Layar terkunci</t>
         </is>
       </c>
-      <c r="D206" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E206" s="7" t="inlineStr">
-        <is>
-          <t>Tetap lanjutkan</t>
-        </is>
-      </c>
-      <c r="F206" s="7" t="inlineStr">
-        <is>
-          <t>Continue anyway</t>
-        </is>
-      </c>
-      <c r="G206" s="7" t="inlineStr">
-        <is>
-          <t>Needed for 'Pengingat lembut' mode, where the design has no continue button.</t>
-        </is>
-      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>Kamu tetap bisa melanjutkan jika memang perlu</t>
+        </is>
+      </c>
+      <c r="F206" s="5" t="inlineStr">
+        <is>
+          <t>You can still continue if you really need to</t>
+        </is>
+      </c>
+      <c r="G206" s="5" t="inlineStr"/>
       <c r="H206" s="6" t="inlineStr"/>
       <c r="I206" s="6" t="inlineStr"/>
     </row>
@@ -7631,7 +7627,7 @@
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>shield_note_gentle</t>
+          <t>shield_note_pause</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
@@ -7646,12 +7642,12 @@
       </c>
       <c r="E207" s="5" t="inlineStr">
         <is>
-          <t>Kamu tetap bisa melanjutkan jika memang perlu</t>
+          <t>Setelah jeda, aplikasi terbuka 5 menit</t>
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>You can still continue if you really need to</t>
+          <t>After the pause, the app opens for 5 minutes</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr"/>
@@ -7664,7 +7660,7 @@
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>shield_note_pause</t>
+          <t>shield_note_full</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
@@ -7679,12 +7675,12 @@
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>Setelah jeda, aplikasi terbuka 5 menit</t>
+          <t>Terbuka lagi pukul {time}</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>After the pause, the app opens for 5 minutes</t>
+          <t>Opens again at {time}</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr"/>
@@ -7697,12 +7693,12 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>shield_note_full</t>
+          <t>settings_title</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>Layar terkunci</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
@@ -7712,12 +7708,12 @@
       </c>
       <c r="E209" s="5" t="inlineStr">
         <is>
-          <t>Terbuka lagi pukul {time}</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>Opens again at {time}</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr"/>
@@ -7730,7 +7726,7 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>settings_title</t>
+          <t>settings_profile_title</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
@@ -7745,12 +7741,12 @@
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Akun anonim</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Anonymous account</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr"/>
@@ -7763,7 +7759,7 @@
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>settings_profile_title</t>
+          <t>settings_profile_sub</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
@@ -7778,12 +7774,12 @@
       </c>
       <c r="E211" s="5" t="inlineStr">
         <is>
-          <t>Akun anonim</t>
+          <t>Tanpa email · data hanya di HP ini</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>Anonymous account</t>
+          <t>No email · data stays on this phone</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr"/>
@@ -7796,7 +7792,7 @@
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>settings_profile_sub</t>
+          <t>settings_group_privacy</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
@@ -7811,12 +7807,12 @@
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>Tanpa email · data hanya di HP ini</t>
+          <t>Privasi</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>No email · data stays on this phone</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr"/>
@@ -7824,72 +7820,72 @@
       <c r="I212" s="6" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="n">
+      <c r="A213" s="8" t="n">
         <v>212</v>
       </c>
-      <c r="B213" s="5" t="inlineStr">
-        <is>
-          <t>settings_group_privacy</t>
-        </is>
-      </c>
-      <c r="C213" s="5" t="inlineStr">
+      <c r="B213" s="8" t="inlineStr">
+        <is>
+          <t>settings_pin_lock</t>
+        </is>
+      </c>
+      <c r="C213" s="8" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D213" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E213" s="5" t="inlineStr">
-        <is>
-          <t>Privasi</t>
-        </is>
-      </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>Privacy</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr"/>
+      <c r="D213" s="8" t="inlineStr">
+        <is>
+          <t>ANDROID</t>
+        </is>
+      </c>
+      <c r="E213" s="8" t="inlineStr">
+        <is>
+          <t>Kunci dengan PIN &amp; sidik jari</t>
+        </is>
+      </c>
+      <c r="F213" s="8" t="inlineStr">
+        <is>
+          <t>Lock with PIN &amp; fingerprint</t>
+        </is>
+      </c>
+      <c r="G213" s="8" t="inlineStr">
+        <is>
+          <t>Original: '…&amp; Face ID'.</t>
+        </is>
+      </c>
       <c r="H213" s="6" t="inlineStr"/>
       <c r="I213" s="6" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="8" t="n">
+      <c r="A214" s="5" t="n">
         <v>213</v>
       </c>
-      <c r="B214" s="8" t="inlineStr">
-        <is>
-          <t>settings_pin_lock</t>
-        </is>
-      </c>
-      <c r="C214" s="8" t="inlineStr">
+      <c r="B214" s="5" t="inlineStr">
+        <is>
+          <t>settings_disguise</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D214" s="8" t="inlineStr">
-        <is>
-          <t>ANDROID</t>
-        </is>
-      </c>
-      <c r="E214" s="8" t="inlineStr">
-        <is>
-          <t>Kunci dengan PIN &amp; sidik jari</t>
-        </is>
-      </c>
-      <c r="F214" s="8" t="inlineStr">
-        <is>
-          <t>Lock with PIN &amp; fingerprint</t>
-        </is>
-      </c>
-      <c r="G214" s="8" t="inlineStr">
-        <is>
-          <t>Original: '…&amp; Face ID'.</t>
-        </is>
-      </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="inlineStr">
+        <is>
+          <t>Ikon &amp; nama samaran</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>Disguised icon &amp; name</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr"/>
       <c r="H214" s="6" t="inlineStr"/>
       <c r="I214" s="6" t="inlineStr"/>
     </row>
@@ -7899,7 +7895,7 @@
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>settings_disguise</t>
+          <t>settings_hide_search</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
@@ -7914,89 +7910,89 @@
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>Ikon &amp; nama samaran</t>
+          <t>Sembunyikan dari pencarian HP</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>Disguised icon &amp; name</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr"/>
+          <t>Hide from phone search</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr">
+        <is>
+          <t>Android has no reliable API for this. Proposal: remove it, or replace it with 'Sembunyikan isi di layar Recent' / 'Hide content in Recents' (FLAG_SECURE).</t>
+        </is>
+      </c>
       <c r="H215" s="6" t="inlineStr"/>
       <c r="I215" s="6" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="n">
+      <c r="A216" s="7" t="n">
         <v>215</v>
       </c>
-      <c r="B216" s="5" t="inlineStr">
-        <is>
-          <t>settings_hide_search</t>
-        </is>
-      </c>
-      <c r="C216" s="5" t="inlineStr">
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>settings_hide_recents</t>
+        </is>
+      </c>
+      <c r="C216" s="7" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D216" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E216" s="5" t="inlineStr">
-        <is>
-          <t>Sembunyikan dari pencarian HP</t>
-        </is>
-      </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>Hide from phone search</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr">
-        <is>
-          <t>Android has no reliable API for this. Proposal: remove it, or replace it with 'Sembunyikan isi di layar Recent' / 'Hide content in Recents' (FLAG_SECURE).</t>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E216" s="7" t="inlineStr">
+        <is>
+          <t>Sembunyikan isi di layar Recent</t>
+        </is>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>Hide content in Recents</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="inlineStr">
+        <is>
+          <t>Android replacement for the row above (FLAG_SECURE also blocks screenshots).</t>
         </is>
       </c>
       <c r="H216" s="6" t="inlineStr"/>
       <c r="I216" s="6" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="7" t="n">
+      <c r="A217" s="5" t="n">
         <v>216</v>
       </c>
-      <c r="B217" s="7" t="inlineStr">
-        <is>
-          <t>settings_hide_recents</t>
-        </is>
-      </c>
-      <c r="C217" s="7" t="inlineStr">
+      <c r="B217" s="5" t="inlineStr">
+        <is>
+          <t>settings_group_journey</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D217" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E217" s="7" t="inlineStr">
-        <is>
-          <t>Sembunyikan isi di layar Recent</t>
-        </is>
-      </c>
-      <c r="F217" s="7" t="inlineStr">
-        <is>
-          <t>Hide content in Recents</t>
-        </is>
-      </c>
-      <c r="G217" s="7" t="inlineStr">
-        <is>
-          <t>Android replacement for the row above (FLAG_SECURE also blocks screenshots).</t>
-        </is>
-      </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="inlineStr">
+        <is>
+          <t>Perjalanan</t>
+        </is>
+      </c>
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>Journey</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr"/>
       <c r="H217" s="6" t="inlineStr"/>
       <c r="I217" s="6" t="inlineStr"/>
     </row>
@@ -8006,7 +8002,7 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>settings_group_journey</t>
+          <t>settings_target</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
@@ -8021,12 +8017,12 @@
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>Perjalanan</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>Journey</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr"/>
@@ -8039,7 +8035,7 @@
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>settings_target</t>
+          <t>settings_target_value</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
@@ -8054,15 +8050,19 @@
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>{n} hari</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="G219" s="5" t="inlineStr"/>
+          <t>{n} days</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="inlineStr">
+        <is>
+          <t>PLURAL in EN.</t>
+        </is>
+      </c>
       <c r="H219" s="6" t="inlineStr"/>
       <c r="I219" s="6" t="inlineStr"/>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>settings_target_value</t>
+          <t>settings_reminders</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
@@ -8087,19 +8087,15 @@
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>{n} hari</t>
+          <t>Pengingat sholat &amp; dzikir</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>{n} days</t>
-        </is>
-      </c>
-      <c r="G220" s="5" t="inlineStr">
-        <is>
-          <t>PLURAL in EN.</t>
-        </is>
-      </c>
+          <t>Prayer &amp; dhikr reminders</t>
+        </is>
+      </c>
+      <c r="G220" s="5" t="inlineStr"/>
       <c r="H220" s="6" t="inlineStr"/>
       <c r="I220" s="6" t="inlineStr"/>
     </row>
@@ -8109,7 +8105,7 @@
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>settings_reminders</t>
+          <t>settings_schedule</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
@@ -8124,12 +8120,12 @@
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>Pengingat sholat &amp; dzikir</t>
+          <t>Jadwal waktu terjaga</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>Prayer &amp; dhikr reminders</t>
+          <t>Guarded-hours schedule</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr"/>
@@ -8142,7 +8138,7 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>settings_schedule</t>
+          <t>settings_group_data</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
@@ -8157,12 +8153,12 @@
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>Jadwal waktu terjaga</t>
+          <t>Data &amp; bantuan</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Guarded-hours schedule</t>
+          <t>Data &amp; help</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr"/>
@@ -8175,7 +8171,7 @@
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>settings_group_data</t>
+          <t>settings_export_delete</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
@@ -8190,12 +8186,12 @@
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>Data &amp; bantuan</t>
+          <t>Ekspor &amp; hapus data</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>Data &amp; help</t>
+          <t>Export &amp; delete data</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr"/>
@@ -8208,7 +8204,7 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>settings_export_delete</t>
+          <t>settings_counselor</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
@@ -8223,122 +8219,126 @@
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>Ekspor &amp; hapus data</t>
+          <t>Bicara dengan konselor</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>Export &amp; delete data</t>
-        </is>
-      </c>
-      <c r="G224" s="5" t="inlineStr"/>
+          <t>Talk to a counselor</t>
+        </is>
+      </c>
+      <c r="G224" s="5" t="inlineStr">
+        <is>
+          <t>Where does it go? Needs a real contact or link before release.</t>
+        </is>
+      </c>
       <c r="H224" s="6" t="inlineStr"/>
       <c r="I224" s="6" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="5" t="n">
+      <c r="A225" s="7" t="n">
         <v>224</v>
       </c>
-      <c r="B225" s="5" t="inlineStr">
-        <is>
-          <t>settings_counselor</t>
-        </is>
-      </c>
-      <c r="C225" s="5" t="inlineStr">
+      <c r="B225" s="7" t="inlineStr">
+        <is>
+          <t>counselor_placeholder</t>
+        </is>
+      </c>
+      <c r="C225" s="7" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D225" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E225" s="5" t="inlineStr">
-        <is>
-          <t>Bicara dengan konselor</t>
-        </is>
-      </c>
-      <c r="F225" s="5" t="inlineStr">
-        <is>
-          <t>Talk to a counselor</t>
-        </is>
-      </c>
-      <c r="G225" s="5" t="inlineStr">
-        <is>
-          <t>Where does it go? Needs a real contact or link before release.</t>
+      <c r="D225" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>Segera hadir. Kami sedang menyiapkan kontak konselor yang tepercaya.</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>Coming soon. We're preparing a trusted counselor contact.</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>Shown in the counselor sheet until a real contact or link exists.</t>
         </is>
       </c>
       <c r="H225" s="6" t="inlineStr"/>
       <c r="I225" s="6" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="7" t="n">
+      <c r="A226" s="5" t="n">
         <v>225</v>
       </c>
-      <c r="B226" s="7" t="inlineStr">
-        <is>
-          <t>counselor_placeholder</t>
-        </is>
-      </c>
-      <c r="C226" s="7" t="inlineStr">
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>settings_about</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D226" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E226" s="7" t="inlineStr">
-        <is>
-          <t>Segera hadir. Kami sedang menyiapkan kontak konselor yang tepercaya.</t>
-        </is>
-      </c>
-      <c r="F226" s="7" t="inlineStr">
-        <is>
-          <t>Coming soon. We're preparing a trusted counselor contact.</t>
-        </is>
-      </c>
-      <c r="G226" s="7" t="inlineStr">
-        <is>
-          <t>Shown in the counselor sheet until a real contact or link exists.</t>
-        </is>
-      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="inlineStr">
+        <is>
+          <t>Tentang Izzah</t>
+        </is>
+      </c>
+      <c r="F226" s="5" t="inlineStr">
+        <is>
+          <t>About Izzah</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="inlineStr"/>
       <c r="H226" s="6" t="inlineStr"/>
       <c r="I226" s="6" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="5" t="n">
+      <c r="A227" s="7" t="n">
         <v>226</v>
       </c>
-      <c r="B227" s="5" t="inlineStr">
-        <is>
-          <t>settings_about</t>
-        </is>
-      </c>
-      <c r="C227" s="5" t="inlineStr">
+      <c r="B227" s="7" t="inlineStr">
+        <is>
+          <t>settings_language</t>
+        </is>
+      </c>
+      <c r="C227" s="7" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D227" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E227" s="5" t="inlineStr">
-        <is>
-          <t>Tentang Izzah</t>
-        </is>
-      </c>
-      <c r="F227" s="5" t="inlineStr">
-        <is>
-          <t>About Izzah</t>
-        </is>
-      </c>
-      <c r="G227" s="5" t="inlineStr"/>
+      <c r="D227" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>Bahasa</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>Language picker row, under Privasi or a new 'Umum' group.</t>
+        </is>
+      </c>
       <c r="H227" s="6" t="inlineStr"/>
       <c r="I227" s="6" t="inlineStr"/>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="B228" s="7" t="inlineStr">
         <is>
-          <t>settings_language</t>
+          <t>language_system</t>
         </is>
       </c>
       <c r="C228" s="7" t="inlineStr">
@@ -8363,19 +8363,15 @@
       </c>
       <c r="E228" s="7" t="inlineStr">
         <is>
-          <t>Bahasa</t>
+          <t>Ikuti sistem</t>
         </is>
       </c>
       <c r="F228" s="7" t="inlineStr">
         <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="G228" s="7" t="inlineStr">
-        <is>
-          <t>Language picker row, under Privasi or a new 'Umum' group.</t>
-        </is>
-      </c>
+          <t>System default</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="inlineStr"/>
       <c r="H228" s="6" t="inlineStr"/>
       <c r="I228" s="6" t="inlineStr"/>
     </row>
@@ -8385,7 +8381,7 @@
       </c>
       <c r="B229" s="7" t="inlineStr">
         <is>
-          <t>language_system</t>
+          <t>language_id</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
@@ -8400,15 +8396,19 @@
       </c>
       <c r="E229" s="7" t="inlineStr">
         <is>
-          <t>Ikuti sistem</t>
+          <t>Bahasa Indonesia</t>
         </is>
       </c>
       <c r="F229" s="7" t="inlineStr">
         <is>
-          <t>System default</t>
-        </is>
-      </c>
-      <c r="G229" s="7" t="inlineStr"/>
+          <t>Bahasa Indonesia</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr">
+        <is>
+          <t>Always shown in its own language.</t>
+        </is>
+      </c>
       <c r="H229" s="6" t="inlineStr"/>
       <c r="I229" s="6" t="inlineStr"/>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="B230" s="7" t="inlineStr">
         <is>
-          <t>language_id</t>
+          <t>language_en</t>
         </is>
       </c>
       <c r="C230" s="7" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="E230" s="7" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>English</t>
         </is>
       </c>
       <c r="F230" s="7" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>English</t>
         </is>
       </c>
       <c r="G230" s="7" t="inlineStr">
@@ -8450,39 +8450,35 @@
       <c r="I230" s="6" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="7" t="n">
+      <c r="A231" s="5" t="n">
         <v>230</v>
       </c>
-      <c r="B231" s="7" t="inlineStr">
-        <is>
-          <t>language_en</t>
-        </is>
-      </c>
-      <c r="C231" s="7" t="inlineStr">
-        <is>
-          <t>Pengaturan</t>
-        </is>
-      </c>
-      <c r="D231" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E231" s="7" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="F231" s="7" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G231" s="7" t="inlineStr">
-        <is>
-          <t>Always shown in its own language.</t>
-        </is>
-      </c>
+      <c r="B231" s="5" t="inlineStr">
+        <is>
+          <t>disguise_title</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t>Ikon samaran</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="inlineStr">
+        <is>
+          <t>Ikon samaran</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>Disguised icon</t>
+        </is>
+      </c>
+      <c r="G231" s="5" t="inlineStr"/>
       <c r="H231" s="6" t="inlineStr"/>
       <c r="I231" s="6" t="inlineStr"/>
     </row>
@@ -8492,7 +8488,7 @@
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>disguise_title</t>
+          <t>disguise_desc</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
@@ -8507,12 +8503,12 @@
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>Ikon samaran</t>
+          <t>Ganti ikon dan nama di layar HP supaya tidak menarik perhatian.</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>Disguised icon</t>
+          <t>Change the icon and name on your home screen so it doesn't draw attention.</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr"/>
@@ -8525,7 +8521,7 @@
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>disguise_desc</t>
+          <t>disguise_izzah</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
@@ -8540,12 +8536,12 @@
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>Ganti ikon dan nama di layar HP supaya tidak menarik perhatian.</t>
+          <t>Izzah</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>Change the icon and name on your home screen so it doesn't draw attention.</t>
+          <t>Izzah</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr"/>
@@ -8558,7 +8554,7 @@
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>disguise_izzah</t>
+          <t>disguise_steps</t>
         </is>
       </c>
       <c r="C234" s="5" t="inlineStr">
@@ -8573,15 +8569,19 @@
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>Izzah</t>
+          <t>Langkah</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>Izzah</t>
-        </is>
-      </c>
-      <c r="G234" s="5" t="inlineStr"/>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G234" s="5" t="inlineStr">
+        <is>
+          <t>This becomes the launcher label, so it's localized too.</t>
+        </is>
+      </c>
       <c r="H234" s="6" t="inlineStr"/>
       <c r="I234" s="6" t="inlineStr"/>
     </row>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>disguise_steps</t>
+          <t>disguise_focus</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
@@ -8606,19 +8606,15 @@
       </c>
       <c r="E235" s="5" t="inlineStr">
         <is>
-          <t>Langkah</t>
+          <t>Fokus</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G235" s="5" t="inlineStr">
-        <is>
-          <t>This becomes the launcher label, so it's localized too.</t>
-        </is>
-      </c>
+          <t>Focus</t>
+        </is>
+      </c>
+      <c r="G235" s="5" t="inlineStr"/>
       <c r="H235" s="6" t="inlineStr"/>
       <c r="I235" s="6" t="inlineStr"/>
     </row>
@@ -8628,7 +8624,7 @@
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>disguise_focus</t>
+          <t>disguise_notes</t>
         </is>
       </c>
       <c r="C236" s="5" t="inlineStr">
@@ -8643,12 +8639,12 @@
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>Fokus</t>
+          <t>Catatan</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>Focus</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr"/>
@@ -8656,72 +8652,72 @@
       <c r="I236" s="6" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="5" t="n">
+      <c r="A237" s="8" t="n">
         <v>236</v>
       </c>
-      <c r="B237" s="5" t="inlineStr">
-        <is>
-          <t>disguise_notes</t>
-        </is>
-      </c>
-      <c r="C237" s="5" t="inlineStr">
+      <c r="B237" s="8" t="inlineStr">
+        <is>
+          <t>disguise_footer</t>
+        </is>
+      </c>
+      <c r="C237" s="8" t="inlineStr">
         <is>
           <t>Ikon samaran</t>
         </is>
       </c>
-      <c r="D237" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E237" s="5" t="inlineStr">
-        <is>
-          <t>Catatan</t>
-        </is>
-      </c>
-      <c r="F237" s="5" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="G237" s="5" t="inlineStr"/>
+      <c r="D237" s="8" t="inlineStr">
+        <is>
+          <t>ANDROID</t>
+        </is>
+      </c>
+      <c r="E237" s="8" t="inlineStr">
+        <is>
+          <t>Nama di notifikasi tetap “Izzah”, tapi isinya selalu netral.</t>
+        </is>
+      </c>
+      <c r="F237" s="8" t="inlineStr">
+        <is>
+          <t>Notifications still show “Izzah”, but their content is always neutral.</t>
+        </is>
+      </c>
+      <c r="G237" s="8" t="inlineStr">
+        <is>
+          <t>Original: 'Notifikasi akan memakai nama yang sama.' Android always shows the application label in notifications; an activity-alias can't change it.</t>
+        </is>
+      </c>
       <c r="H237" s="6" t="inlineStr"/>
       <c r="I237" s="6" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="8" t="n">
+      <c r="A238" s="5" t="n">
         <v>237</v>
       </c>
-      <c r="B238" s="8" t="inlineStr">
-        <is>
-          <t>disguise_footer</t>
-        </is>
-      </c>
-      <c r="C238" s="8" t="inlineStr">
-        <is>
-          <t>Ikon samaran</t>
-        </is>
-      </c>
-      <c r="D238" s="8" t="inlineStr">
-        <is>
-          <t>ANDROID</t>
-        </is>
-      </c>
-      <c r="E238" s="8" t="inlineStr">
-        <is>
-          <t>Nama di notifikasi tetap “Izzah”, tapi isinya selalu netral.</t>
-        </is>
-      </c>
-      <c r="F238" s="8" t="inlineStr">
-        <is>
-          <t>Notifications still show “Izzah”, but their content is always neutral.</t>
-        </is>
-      </c>
-      <c r="G238" s="8" t="inlineStr">
-        <is>
-          <t>Original: 'Notifikasi akan memakai nama yang sama.' Android always shows the application label in notifications; an activity-alias can't change it.</t>
-        </is>
-      </c>
+      <c r="B238" s="5" t="inlineStr">
+        <is>
+          <t>data_title</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>Datamu</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E238" s="5" t="inlineStr">
+        <is>
+          <t>Datamu</t>
+        </is>
+      </c>
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>Your data</t>
+        </is>
+      </c>
+      <c r="G238" s="5" t="inlineStr"/>
       <c r="H238" s="6" t="inlineStr"/>
       <c r="I238" s="6" t="inlineStr"/>
     </row>
@@ -8731,7 +8727,7 @@
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
-          <t>data_title</t>
+          <t>data_desc</t>
         </is>
       </c>
       <c r="C239" s="5" t="inlineStr">
@@ -8746,12 +8742,12 @@
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
-          <t>Datamu</t>
+          <t>Semua tersimpan di HP ini. Tidak ada di server kami.</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>Your data</t>
+          <t>Everything is stored on this phone. Nothing is on our servers.</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr"/>
@@ -8764,7 +8760,7 @@
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>data_desc</t>
+          <t>data_export_title</t>
         </is>
       </c>
       <c r="C240" s="5" t="inlineStr">
@@ -8779,12 +8775,12 @@
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>Semua tersimpan di HP ini. Tidak ada di server kami.</t>
+          <t>Ekspor cadangan</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>Everything is stored on this phone. Nothing is on our servers.</t>
+          <t>Export a backup</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr"/>
@@ -8797,7 +8793,7 @@
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>data_export_title</t>
+          <t>data_export_desc</t>
         </is>
       </c>
       <c r="C241" s="5" t="inlineStr">
@@ -8812,12 +8808,12 @@
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>Ekspor cadangan</t>
+          <t>File terenkripsi dengan PIN-mu. Pakai saat pindah HP.</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>Export a backup</t>
+          <t>A file encrypted with your PIN. Use it when you switch phones.</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr"/>
@@ -8830,7 +8826,7 @@
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>data_export_desc</t>
+          <t>data_export_cta</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr">
@@ -8845,12 +8841,12 @@
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>File terenkripsi dengan PIN-mu. Pakai saat pindah HP.</t>
+          <t>Buat file cadangan</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>A file encrypted with your PIN. Use it when you switch phones.</t>
+          <t>Create backup file</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr"/>
@@ -8858,35 +8854,35 @@
       <c r="I242" s="6" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="n">
+      <c r="A243" s="7" t="n">
         <v>242</v>
       </c>
-      <c r="B243" s="5" t="inlineStr">
-        <is>
-          <t>data_export_cta</t>
-        </is>
-      </c>
-      <c r="C243" s="5" t="inlineStr">
+      <c r="B243" s="7" t="inlineStr">
+        <is>
+          <t>data_import_wrong_pin</t>
+        </is>
+      </c>
+      <c r="C243" s="7" t="inlineStr">
         <is>
           <t>Datamu</t>
         </is>
       </c>
-      <c r="D243" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E243" s="5" t="inlineStr">
-        <is>
-          <t>Buat file cadangan</t>
-        </is>
-      </c>
-      <c r="F243" s="5" t="inlineStr">
-        <is>
-          <t>Create backup file</t>
-        </is>
-      </c>
-      <c r="G243" s="5" t="inlineStr"/>
+      <c r="D243" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E243" s="7" t="inlineStr">
+        <is>
+          <t>PIN cadangan tidak cocok.</t>
+        </is>
+      </c>
+      <c r="F243" s="7" t="inlineStr">
+        <is>
+          <t>The backup PIN doesn't match.</t>
+        </is>
+      </c>
+      <c r="G243" s="7" t="inlineStr"/>
       <c r="H243" s="6" t="inlineStr"/>
       <c r="I243" s="6" t="inlineStr"/>
     </row>
@@ -8896,7 +8892,7 @@
       </c>
       <c r="B244" s="7" t="inlineStr">
         <is>
-          <t>data_import_wrong_pin</t>
+          <t>data_export_done</t>
         </is>
       </c>
       <c r="C244" s="7" t="inlineStr">
@@ -8911,15 +8907,19 @@
       </c>
       <c r="E244" s="7" t="inlineStr">
         <is>
-          <t>PIN cadangan tidak cocok.</t>
+          <t>Cadangan tersimpan.</t>
         </is>
       </c>
       <c r="F244" s="7" t="inlineStr">
         <is>
-          <t>The backup PIN doesn't match.</t>
-        </is>
-      </c>
-      <c r="G244" s="7" t="inlineStr"/>
+          <t>Backup saved.</t>
+        </is>
+      </c>
+      <c r="G244" s="7" t="inlineStr">
+        <is>
+          <t>Toast after the system save dialog.</t>
+        </is>
+      </c>
       <c r="H244" s="6" t="inlineStr"/>
       <c r="I244" s="6" t="inlineStr"/>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="B245" s="7" t="inlineStr">
         <is>
-          <t>data_export_done</t>
+          <t>data_import_cta</t>
         </is>
       </c>
       <c r="C245" s="7" t="inlineStr">
@@ -8944,56 +8944,52 @@
       </c>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>Cadangan tersimpan.</t>
+          <t>Pulihkan dari cadangan</t>
         </is>
       </c>
       <c r="F245" s="7" t="inlineStr">
         <is>
-          <t>Backup saved.</t>
+          <t>Restore from backup</t>
         </is>
       </c>
       <c r="G245" s="7" t="inlineStr">
         <is>
-          <t>Toast after the system save dialog.</t>
+          <t>Without this, the export is useless on a new phone. Proposed for v1.</t>
         </is>
       </c>
       <c r="H245" s="6" t="inlineStr"/>
       <c r="I245" s="6" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="7" t="n">
+      <c r="A246" s="5" t="n">
         <v>245</v>
       </c>
-      <c r="B246" s="7" t="inlineStr">
-        <is>
-          <t>data_import_cta</t>
-        </is>
-      </c>
-      <c r="C246" s="7" t="inlineStr">
+      <c r="B246" s="5" t="inlineStr">
+        <is>
+          <t>data_delete_title</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="inlineStr">
         <is>
           <t>Datamu</t>
         </is>
       </c>
-      <c r="D246" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E246" s="7" t="inlineStr">
-        <is>
-          <t>Pulihkan dari cadangan</t>
-        </is>
-      </c>
-      <c r="F246" s="7" t="inlineStr">
-        <is>
-          <t>Restore from backup</t>
-        </is>
-      </c>
-      <c r="G246" s="7" t="inlineStr">
-        <is>
-          <t>Without this, the export is useless on a new phone. Proposed for v1.</t>
-        </is>
-      </c>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E246" s="5" t="inlineStr">
+        <is>
+          <t>Hapus semua data</t>
+        </is>
+      </c>
+      <c r="F246" s="5" t="inlineStr">
+        <is>
+          <t>Delete all data</t>
+        </is>
+      </c>
+      <c r="G246" s="5" t="inlineStr"/>
       <c r="H246" s="6" t="inlineStr"/>
       <c r="I246" s="6" t="inlineStr"/>
     </row>
@@ -9003,7 +8999,7 @@
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>data_delete_title</t>
+          <t>data_delete_desc</t>
         </is>
       </c>
       <c r="C247" s="5" t="inlineStr">
@@ -9018,12 +9014,12 @@
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>Hapus semua data</t>
+          <t>Progres, jurnal, dan pengaturan akan hilang permanen.</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>Delete all data</t>
+          <t>Your progress, journal and settings will be permanently erased.</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr"/>
@@ -9036,7 +9032,7 @@
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>data_delete_desc</t>
+          <t>data_delete_cta</t>
         </is>
       </c>
       <c r="C248" s="5" t="inlineStr">
@@ -9051,12 +9047,12 @@
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>Progres, jurnal, dan pengaturan akan hilang permanen.</t>
+          <t>Hapus data</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>Your progress, journal and settings will be permanently erased.</t>
+          <t>Delete data</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr"/>
@@ -9069,12 +9065,12 @@
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>data_delete_cta</t>
+          <t>delete_sheet_title</t>
         </is>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>Datamu</t>
+          <t>Hapus (sheet)</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
@@ -9084,12 +9080,12 @@
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>Hapus data</t>
+          <t>Yakin hapus semua?</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>Delete data</t>
+          <t>Delete everything?</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr"/>
@@ -9102,7 +9098,7 @@
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>delete_sheet_title</t>
+          <t>delete_sheet_body</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
@@ -9117,12 +9113,12 @@
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>Yakin hapus semua?</t>
+          <t>Ini tidak bisa dibatalkan. Kalau hanya ingin istirahat, kamu bisa menjeda pengingat saja.</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>Delete everything?</t>
+          <t>This can't be undone. If you just need a break, you can pause the reminders instead.</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr"/>
@@ -9135,7 +9131,7 @@
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>delete_sheet_body</t>
+          <t>delete_sheet_confirm</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
@@ -9150,12 +9146,12 @@
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>Ini tidak bisa dibatalkan. Kalau hanya ingin istirahat, kamu bisa menjeda pengingat saja.</t>
+          <t>Ya, hapus semuanya</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>This can't be undone. If you just need a break, you can pause the reminders instead.</t>
+          <t>Yes, delete everything</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr"/>
@@ -9168,7 +9164,7 @@
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>delete_sheet_confirm</t>
+          <t>common_cancel</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
@@ -9183,12 +9179,12 @@
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>Ya, hapus semuanya</t>
+          <t>Batal</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>Yes, delete everything</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr"/>
@@ -9201,12 +9197,12 @@
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>common_cancel</t>
+          <t>unlock_title</t>
         </is>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>Hapus (sheet)</t>
+          <t>Buka dengan PIN</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
@@ -9216,12 +9212,12 @@
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>Batal</t>
+          <t>Masukkan PIN</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Enter your PIN</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr"/>
@@ -9234,7 +9230,7 @@
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>unlock_title</t>
+          <t>unlock_subtitle</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr">
@@ -9249,12 +9245,12 @@
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>Masukkan PIN</t>
+          <t>Assalamu’alaikum. Selamat datang kembali.</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>Enter your PIN</t>
+          <t>Assalamu’alaikum. Welcome back.</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr"/>
@@ -9262,35 +9258,35 @@
       <c r="I254" s="6" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="5" t="n">
+      <c r="A255" s="7" t="n">
         <v>254</v>
       </c>
-      <c r="B255" s="5" t="inlineStr">
-        <is>
-          <t>unlock_subtitle</t>
-        </is>
-      </c>
-      <c r="C255" s="5" t="inlineStr">
+      <c r="B255" s="7" t="inlineStr">
+        <is>
+          <t>unlock_wrong</t>
+        </is>
+      </c>
+      <c r="C255" s="7" t="inlineStr">
         <is>
           <t>Buka dengan PIN</t>
         </is>
       </c>
-      <c r="D255" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E255" s="5" t="inlineStr">
-        <is>
-          <t>Assalamu’alaikum. Selamat datang kembali.</t>
-        </is>
-      </c>
-      <c r="F255" s="5" t="inlineStr">
-        <is>
-          <t>Assalamu’alaikum. Welcome back.</t>
-        </is>
-      </c>
-      <c r="G255" s="5" t="inlineStr"/>
+      <c r="D255" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E255" s="7" t="inlineStr">
+        <is>
+          <t>PIN salah. Coba lagi.</t>
+        </is>
+      </c>
+      <c r="F255" s="7" t="inlineStr">
+        <is>
+          <t>Wrong PIN. Try again.</t>
+        </is>
+      </c>
+      <c r="G255" s="7" t="inlineStr"/>
       <c r="H255" s="6" t="inlineStr"/>
       <c r="I255" s="6" t="inlineStr"/>
     </row>
@@ -9300,7 +9296,7 @@
       </c>
       <c r="B256" s="7" t="inlineStr">
         <is>
-          <t>unlock_wrong</t>
+          <t>unlock_cooldown</t>
         </is>
       </c>
       <c r="C256" s="7" t="inlineStr">
@@ -9315,15 +9311,19 @@
       </c>
       <c r="E256" s="7" t="inlineStr">
         <is>
-          <t>PIN salah. Coba lagi.</t>
+          <t>Terlalu banyak percobaan. Coba lagi dalam {seconds} detik.</t>
         </is>
       </c>
       <c r="F256" s="7" t="inlineStr">
         <is>
-          <t>Wrong PIN. Try again.</t>
-        </is>
-      </c>
-      <c r="G256" s="7" t="inlineStr"/>
+          <t>Too many tries. Try again in {seconds} seconds.</t>
+        </is>
+      </c>
+      <c r="G256" s="7" t="inlineStr">
+        <is>
+          <t>After 5 wrong PINs: 30 s cooldown. PLURAL in EN.</t>
+        </is>
+      </c>
       <c r="H256" s="6" t="inlineStr"/>
       <c r="I256" s="6" t="inlineStr"/>
     </row>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="B257" s="7" t="inlineStr">
         <is>
-          <t>unlock_cooldown</t>
+          <t>unlock_forgot</t>
         </is>
       </c>
       <c r="C257" s="7" t="inlineStr">
@@ -9348,19 +9348,15 @@
       </c>
       <c r="E257" s="7" t="inlineStr">
         <is>
-          <t>Terlalu banyak percobaan. Coba lagi dalam {seconds} detik.</t>
+          <t>Lupa PIN?</t>
         </is>
       </c>
       <c r="F257" s="7" t="inlineStr">
         <is>
-          <t>Too many tries. Try again in {seconds} seconds.</t>
-        </is>
-      </c>
-      <c r="G257" s="7" t="inlineStr">
-        <is>
-          <t>After 5 wrong PINs: 30 s cooldown. PLURAL in EN.</t>
-        </is>
-      </c>
+          <t>Forgot your PIN?</t>
+        </is>
+      </c>
+      <c r="G257" s="7" t="inlineStr"/>
       <c r="H257" s="6" t="inlineStr"/>
       <c r="I257" s="6" t="inlineStr"/>
     </row>
@@ -9370,7 +9366,7 @@
       </c>
       <c r="B258" s="7" t="inlineStr">
         <is>
-          <t>unlock_forgot</t>
+          <t>unlock_forgot_body</t>
         </is>
       </c>
       <c r="C258" s="7" t="inlineStr">
@@ -9385,15 +9381,19 @@
       </c>
       <c r="E258" s="7" t="inlineStr">
         <is>
-          <t>Lupa PIN?</t>
+          <t>Karena akunmu anonim, PIN tidak bisa dipulihkan. Kamu bisa menghapus data dan mulai dari awal, atau memulihkan dari file cadangan.</t>
         </is>
       </c>
       <c r="F258" s="7" t="inlineStr">
         <is>
-          <t>Forgot your PIN?</t>
-        </is>
-      </c>
-      <c r="G258" s="7" t="inlineStr"/>
+          <t>Your account is anonymous, so the PIN can't be recovered. You can delete your data and start fresh, or restore from a backup file.</t>
+        </is>
+      </c>
+      <c r="G258" s="7" t="inlineStr">
+        <is>
+          <t>Bottom sheet. Buttons reuse delete_sheet_confirm + data_import_cta + common_cancel.</t>
+        </is>
+      </c>
       <c r="H258" s="6" t="inlineStr"/>
       <c r="I258" s="6" t="inlineStr"/>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="B259" s="7" t="inlineStr">
         <is>
-          <t>unlock_forgot_body</t>
+          <t>biometric_title</t>
         </is>
       </c>
       <c r="C259" s="7" t="inlineStr">
@@ -9418,17 +9418,17 @@
       </c>
       <c r="E259" s="7" t="inlineStr">
         <is>
-          <t>Karena akunmu anonim, PIN tidak bisa dipulihkan. Kamu bisa menghapus data dan mulai dari awal, atau memulihkan dari file cadangan.</t>
+          <t>Buka Izzah</t>
         </is>
       </c>
       <c r="F259" s="7" t="inlineStr">
         <is>
-          <t>Your account is anonymous, so the PIN can't be recovered. You can delete your data and start fresh, or restore from a backup file.</t>
+          <t>Unlock Izzah</t>
         </is>
       </c>
       <c r="G259" s="7" t="inlineStr">
         <is>
-          <t>Bottom sheet. Buttons reuse delete_sheet_confirm + data_import_cta + common_cancel.</t>
+          <t>Title of the system BiometricPrompt. Shows the disguise name if a disguise is active.</t>
         </is>
       </c>
       <c r="H259" s="6" t="inlineStr"/>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="B260" s="7" t="inlineStr">
         <is>
-          <t>biometric_title</t>
+          <t>biometric_use_pin</t>
         </is>
       </c>
       <c r="C260" s="7" t="inlineStr">
@@ -9455,89 +9455,85 @@
       </c>
       <c r="E260" s="7" t="inlineStr">
         <is>
-          <t>Buka Izzah</t>
+          <t>Pakai PIN</t>
         </is>
       </c>
       <c r="F260" s="7" t="inlineStr">
         <is>
-          <t>Unlock Izzah</t>
-        </is>
-      </c>
-      <c r="G260" s="7" t="inlineStr">
-        <is>
-          <t>Title of the system BiometricPrompt. Shows the disguise name if a disguise is active.</t>
-        </is>
-      </c>
+          <t>Use PIN</t>
+        </is>
+      </c>
+      <c r="G260" s="7" t="inlineStr"/>
       <c r="H260" s="6" t="inlineStr"/>
       <c r="I260" s="6" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="7" t="n">
+      <c r="A261" s="5" t="n">
         <v>260</v>
       </c>
-      <c r="B261" s="7" t="inlineStr">
-        <is>
-          <t>biometric_use_pin</t>
-        </is>
-      </c>
-      <c r="C261" s="7" t="inlineStr">
-        <is>
-          <t>Buka dengan PIN</t>
-        </is>
-      </c>
-      <c r="D261" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E261" s="7" t="inlineStr">
-        <is>
-          <t>Pakai PIN</t>
-        </is>
-      </c>
-      <c r="F261" s="7" t="inlineStr">
-        <is>
-          <t>Use PIN</t>
-        </is>
-      </c>
-      <c r="G261" s="7" t="inlineStr"/>
+      <c r="B261" s="5" t="inlineStr">
+        <is>
+          <t>notif_prayer_body</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="inlineStr">
+        <is>
+          <t>Notifikasi (sistem)</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="inlineStr">
+        <is>
+          <t>Waktunya {prayer}. Sejenak untuk dirimu.</t>
+        </is>
+      </c>
+      <c r="F261" s="5" t="inlineStr">
+        <is>
+          <t>Time for {prayer}. A moment for yourself.</t>
+        </is>
+      </c>
+      <c r="G261" s="5" t="inlineStr">
+        <is>
+          <t>RULE: no notification may mention porn, relapse or addiction.</t>
+        </is>
+      </c>
       <c r="H261" s="6" t="inlineStr"/>
       <c r="I261" s="6" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="5" t="n">
+      <c r="A262" s="7" t="n">
         <v>261</v>
       </c>
-      <c r="B262" s="5" t="inlineStr">
-        <is>
-          <t>notif_prayer_body</t>
-        </is>
-      </c>
-      <c r="C262" s="5" t="inlineStr">
+      <c r="B262" s="7" t="inlineStr">
+        <is>
+          <t>notif_dzikir_morning</t>
+        </is>
+      </c>
+      <c r="C262" s="7" t="inlineStr">
         <is>
           <t>Notifikasi (sistem)</t>
         </is>
       </c>
-      <c r="D262" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E262" s="5" t="inlineStr">
-        <is>
-          <t>Waktunya {prayer}. Sejenak untuk dirimu.</t>
-        </is>
-      </c>
-      <c r="F262" s="5" t="inlineStr">
-        <is>
-          <t>Time for {prayer}. A moment for yourself.</t>
-        </is>
-      </c>
-      <c r="G262" s="5" t="inlineStr">
-        <is>
-          <t>RULE: no notification may mention porn, relapse or addiction.</t>
-        </is>
-      </c>
+      <c r="D262" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E262" s="7" t="inlineStr">
+        <is>
+          <t>Pagi yang baru. Ada waktu sebentar untuk dirimu?</t>
+        </is>
+      </c>
+      <c r="F262" s="7" t="inlineStr">
+        <is>
+          <t>A fresh morning. Got a minute for yourself?</t>
+        </is>
+      </c>
+      <c r="G262" s="7" t="inlineStr"/>
       <c r="H262" s="6" t="inlineStr"/>
       <c r="I262" s="6" t="inlineStr"/>
     </row>
@@ -9547,7 +9543,7 @@
       </c>
       <c r="B263" s="7" t="inlineStr">
         <is>
-          <t>notif_dzikir_morning</t>
+          <t>notif_dzikir_evening</t>
         </is>
       </c>
       <c r="C263" s="7" t="inlineStr">
@@ -9562,12 +9558,12 @@
       </c>
       <c r="E263" s="7" t="inlineStr">
         <is>
-          <t>Pagi yang baru. Ada waktu sebentar untuk dirimu?</t>
+          <t>Sore menjelang. Sejenak untuk menenangkan hati.</t>
         </is>
       </c>
       <c r="F263" s="7" t="inlineStr">
         <is>
-          <t>A fresh morning. Got a minute for yourself?</t>
+          <t>Evening is here. A moment to settle your heart.</t>
         </is>
       </c>
       <c r="G263" s="7" t="inlineStr"/>
@@ -9580,7 +9576,7 @@
       </c>
       <c r="B264" s="7" t="inlineStr">
         <is>
-          <t>notif_dzikir_evening</t>
+          <t>notif_checkin</t>
         </is>
       </c>
       <c r="C264" s="7" t="inlineStr">
@@ -9595,12 +9591,12 @@
       </c>
       <c r="E264" s="7" t="inlineStr">
         <is>
-          <t>Sore menjelang. Sejenak untuk menenangkan hati.</t>
+          <t>Bagaimana harimu? Catat sebentar sebelum istirahat.</t>
         </is>
       </c>
       <c r="F264" s="7" t="inlineStr">
         <is>
-          <t>Evening is here. A moment to settle your heart.</t>
+          <t>How was your day? A quick note before you rest.</t>
         </is>
       </c>
       <c r="G264" s="7" t="inlineStr"/>
@@ -9613,7 +9609,7 @@
       </c>
       <c r="B265" s="7" t="inlineStr">
         <is>
-          <t>notif_checkin</t>
+          <t>notif_channel_reminders</t>
         </is>
       </c>
       <c r="C265" s="7" t="inlineStr">
@@ -9628,15 +9624,19 @@
       </c>
       <c r="E265" s="7" t="inlineStr">
         <is>
-          <t>Bagaimana harimu? Catat sebentar sebelum istirahat.</t>
+          <t>Pengingat</t>
         </is>
       </c>
       <c r="F265" s="7" t="inlineStr">
         <is>
-          <t>How was your day? A quick note before you rest.</t>
-        </is>
-      </c>
-      <c r="G265" s="7" t="inlineStr"/>
+          <t>Reminders</t>
+        </is>
+      </c>
+      <c r="G265" s="7" t="inlineStr">
+        <is>
+          <t>Android notification channel name (visible in system settings).</t>
+        </is>
+      </c>
       <c r="H265" s="6" t="inlineStr"/>
       <c r="I265" s="6" t="inlineStr"/>
     </row>
@@ -9646,7 +9646,7 @@
       </c>
       <c r="B266" s="7" t="inlineStr">
         <is>
-          <t>notif_channel_reminders</t>
+          <t>notif_channel_protect</t>
         </is>
       </c>
       <c r="C266" s="7" t="inlineStr">
@@ -9661,17 +9661,17 @@
       </c>
       <c r="E266" s="7" t="inlineStr">
         <is>
-          <t>Pengingat</t>
+          <t>Penjagaan aktif</t>
         </is>
       </c>
       <c r="F266" s="7" t="inlineStr">
         <is>
-          <t>Reminders</t>
+          <t>Protection running</t>
         </is>
       </c>
       <c r="G266" s="7" t="inlineStr">
         <is>
-          <t>Android notification channel name (visible in system settings).</t>
+          <t>Foreground service channel for the blocker.</t>
         </is>
       </c>
       <c r="H266" s="6" t="inlineStr"/>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="B267" s="7" t="inlineStr">
         <is>
-          <t>notif_channel_protect</t>
+          <t>notif_protect_ongoing</t>
         </is>
       </c>
       <c r="C267" s="7" t="inlineStr">
@@ -9698,54 +9698,54 @@
       </c>
       <c r="E267" s="7" t="inlineStr">
         <is>
-          <t>Penjagaan aktif</t>
+          <t>Berjalan di latar belakang.</t>
         </is>
       </c>
       <c r="F267" s="7" t="inlineStr">
         <is>
-          <t>Protection running</t>
+          <t>Running in the background.</t>
         </is>
       </c>
       <c r="G267" s="7" t="inlineStr">
         <is>
-          <t>Foreground service channel for the blocker.</t>
+          <t>Persistent foreground-service notification. Must stay neutral.</t>
         </is>
       </c>
       <c r="H267" s="6" t="inlineStr"/>
       <c r="I267" s="6" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="7" t="n">
+      <c r="A268" s="5" t="n">
         <v>267</v>
       </c>
-      <c r="B268" s="7" t="inlineStr">
-        <is>
-          <t>notif_protect_ongoing</t>
-        </is>
-      </c>
-      <c r="C268" s="7" t="inlineStr">
-        <is>
-          <t>Notifikasi (sistem)</t>
-        </is>
-      </c>
-      <c r="D268" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E268" s="7" t="inlineStr">
-        <is>
-          <t>Berjalan di latar belakang.</t>
-        </is>
-      </c>
-      <c r="F268" s="7" t="inlineStr">
-        <is>
-          <t>Running in the background.</t>
-        </is>
-      </c>
-      <c r="G268" s="7" t="inlineStr">
-        <is>
-          <t>Persistent foreground-service notification. Must stay neutral.</t>
+      <c r="B268" s="5" t="inlineStr">
+        <is>
+          <t>hijri_month_1</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E268" s="5" t="inlineStr">
+        <is>
+          <t>Muharram</t>
+        </is>
+      </c>
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>Muharram</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="inlineStr">
+        <is>
+          <t>Used by {hijri}.</t>
         </is>
       </c>
       <c r="H268" s="6" t="inlineStr"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_1</t>
+          <t>hijri_month_2</t>
         </is>
       </c>
       <c r="C269" s="5" t="inlineStr">
@@ -9772,19 +9772,15 @@
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>Muharram</t>
+          <t>Safar</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>Muharram</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr">
-        <is>
-          <t>Used by {hijri}.</t>
-        </is>
-      </c>
+          <t>Safar</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr"/>
       <c r="H269" s="6" t="inlineStr"/>
       <c r="I269" s="6" t="inlineStr"/>
     </row>
@@ -9794,7 +9790,7 @@
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_2</t>
+          <t>hijri_month_3</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
@@ -9809,12 +9805,12 @@
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>Safar</t>
+          <t>Rabiul Awal</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>Safar</t>
+          <t>Rabi‘ al-Awwal</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr"/>
@@ -9827,7 +9823,7 @@
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_3</t>
+          <t>hijri_month_4</t>
         </is>
       </c>
       <c r="C271" s="5" t="inlineStr">
@@ -9842,12 +9838,12 @@
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>Rabiul Awal</t>
+          <t>Rabiul Akhir</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>Rabi‘ al-Awwal</t>
+          <t>Rabi‘ al-Thani</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr"/>
@@ -9860,7 +9856,7 @@
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_4</t>
+          <t>hijri_month_5</t>
         </is>
       </c>
       <c r="C272" s="5" t="inlineStr">
@@ -9875,12 +9871,12 @@
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>Rabiul Akhir</t>
+          <t>Jumadil Awal</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>Rabi‘ al-Thani</t>
+          <t>Jumada al-Ula</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr"/>
@@ -9893,7 +9889,7 @@
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_5</t>
+          <t>hijri_month_6</t>
         </is>
       </c>
       <c r="C273" s="5" t="inlineStr">
@@ -9908,12 +9904,12 @@
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>Jumadil Awal</t>
+          <t>Jumadil Akhir</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>Jumada al-Ula</t>
+          <t>Jumada al-Akhirah</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr"/>
@@ -9926,7 +9922,7 @@
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_6</t>
+          <t>hijri_month_7</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
@@ -9941,12 +9937,12 @@
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>Jumadil Akhir</t>
+          <t>Rajab</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>Jumada al-Akhirah</t>
+          <t>Rajab</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr"/>
@@ -9959,7 +9955,7 @@
       </c>
       <c r="B275" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_7</t>
+          <t>hijri_month_8</t>
         </is>
       </c>
       <c r="C275" s="5" t="inlineStr">
@@ -9974,12 +9970,12 @@
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
-          <t>Rajab</t>
+          <t>Sya’ban</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>Rajab</t>
+          <t>Sha‘ban</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr"/>
@@ -9992,7 +9988,7 @@
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_8</t>
+          <t>hijri_month_9</t>
         </is>
       </c>
       <c r="C276" s="5" t="inlineStr">
@@ -10007,12 +10003,12 @@
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>Sya’ban</t>
+          <t>Ramadhan</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>Sha‘ban</t>
+          <t>Ramadan</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr"/>
@@ -10025,7 +10021,7 @@
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_9</t>
+          <t>hijri_month_10</t>
         </is>
       </c>
       <c r="C277" s="5" t="inlineStr">
@@ -10040,12 +10036,12 @@
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>Ramadhan</t>
+          <t>Syawal</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>Ramadan</t>
+          <t>Shawwal</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr"/>
@@ -10058,7 +10054,7 @@
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_10</t>
+          <t>hijri_month_11</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
@@ -10073,12 +10069,12 @@
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>Syawal</t>
+          <t>Dzulqa’dah</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>Shawwal</t>
+          <t>Dhu al-Qa‘dah</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr"/>
@@ -10091,7 +10087,7 @@
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_11</t>
+          <t>hijri_month_12</t>
         </is>
       </c>
       <c r="C279" s="5" t="inlineStr">
@@ -10106,12 +10102,12 @@
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>Dzulqa’dah</t>
+          <t>Dzulhijjah</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>Dhu al-Qa‘dah</t>
+          <t>Dhu al-Hijjah</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr"/>
@@ -10124,7 +10120,7 @@
       </c>
       <c r="B280" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_12</t>
+          <t>hijri_suffix</t>
         </is>
       </c>
       <c r="C280" s="5" t="inlineStr">
@@ -10139,55 +10135,22 @@
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>Dzulhijjah</t>
+          <t>{day} {month} {year} H</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>Dhu al-Hijjah</t>
+          <t>{day} {month} {year} AH</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr"/>
       <c r="H280" s="6" t="inlineStr"/>
       <c r="I280" s="6" t="inlineStr"/>
     </row>
-    <row r="281">
-      <c r="A281" s="5" t="n">
-        <v>280</v>
-      </c>
-      <c r="B281" s="5" t="inlineStr">
-        <is>
-          <t>hijri_suffix</t>
-        </is>
-      </c>
-      <c r="C281" s="5" t="inlineStr">
-        <is>
-          <t>Hijri calendar</t>
-        </is>
-      </c>
-      <c r="D281" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E281" s="5" t="inlineStr">
-        <is>
-          <t>{day} {month} {year} H</t>
-        </is>
-      </c>
-      <c r="F281" s="5" t="inlineStr">
-        <is>
-          <t>{day} {month} {year} AH</t>
-        </is>
-      </c>
-      <c r="G281" s="5" t="inlineStr"/>
-      <c r="H281" s="6" t="inlineStr"/>
-      <c r="I281" s="6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I281"/>
+  <autoFilter ref="A1:I280"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H281" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H280" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,Revisi,Hapus"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/copy/izzah-copy-id-en.xlsx
+++ b/docs/copy/izzah-copy-id-en.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Glossary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Copy'!$A$1:$I$280</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Copy'!$A$1:$I$291</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Religious'!$A$1:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Glossary'!$A$1:$E$13</definedName>
   </definedNames>
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I280"/>
+  <dimension ref="A1:I291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7342,74 +7342,74 @@
       <c r="I198" s="6" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="5" t="n">
+      <c r="A199" s="7" t="n">
         <v>198</v>
       </c>
-      <c r="B199" s="5" t="inlineStr">
-        <is>
-          <t>shield_label</t>
-        </is>
-      </c>
-      <c r="C199" s="5" t="inlineStr">
-        <is>
-          <t>Layar terkunci</t>
-        </is>
-      </c>
-      <c r="D199" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E199" s="5" t="inlineStr">
-        <is>
-          <t>Waktu terjaga · sampai {time}</t>
-        </is>
-      </c>
-      <c r="F199" s="5" t="inlineStr">
-        <is>
-          <t>Guarded hours · until {time}</t>
-        </is>
-      </c>
-      <c r="G199" s="5" t="inlineStr">
-        <is>
-          <t>Rendered UPPERCASE.</t>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>keeprun_title</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="inlineStr">
+        <is>
+          <t>Lindungi</t>
+        </is>
+      </c>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
+          <t>Biarkan Izzah tetap berjalan</t>
+        </is>
+      </c>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>Keep Izzah running</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>Xiaomi/Redmi/POCO only. Written for the Android build, needs review.</t>
         </is>
       </c>
       <c r="H199" s="6" t="inlineStr"/>
       <c r="I199" s="6" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="5" t="n">
+      <c r="A200" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="B200" s="5" t="inlineStr">
-        <is>
-          <t>shield_title</t>
-        </is>
-      </c>
-      <c r="C200" s="5" t="inlineStr">
-        <is>
-          <t>Layar terkunci</t>
-        </is>
-      </c>
-      <c r="D200" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E200" s="5" t="inlineStr">
-        <is>
-          <t>Sudah larut. Istirahat dulu, yuk.</t>
-        </is>
-      </c>
-      <c r="F200" s="5" t="inlineStr">
-        <is>
-          <t>It's late. Time to rest, okay?</t>
-        </is>
-      </c>
-      <c r="G200" s="5" t="inlineStr">
-        <is>
-          <t>Fits a late-night slot only. A daytime variant is proposed below.</t>
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t>keeprun_desc</t>
+        </is>
+      </c>
+      <c r="C200" s="7" t="inlineStr">
+        <is>
+          <t>Lindungi</t>
+        </is>
+      </c>
+      <c r="D200" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t>HP-mu bisa menghentikan Izzah di latar belakang. Izinkan Autostart dan lepas batas baterai supaya pagar tetap berfungsi.</t>
+        </is>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>Your phone may stop Izzah in the background. Allow Autostart and remove the battery limit so the fence keeps working.</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>Needs review.</t>
         </is>
       </c>
       <c r="H200" s="6" t="inlineStr"/>
@@ -7421,12 +7421,12 @@
       </c>
       <c r="B201" s="7" t="inlineStr">
         <is>
-          <t>shield_title_day</t>
+          <t>keeprun_autostart</t>
         </is>
       </c>
       <c r="C201" s="7" t="inlineStr">
         <is>
-          <t>Layar terkunci</t>
+          <t>Lindungi</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
@@ -7436,118 +7436,130 @@
       </c>
       <c r="E201" s="7" t="inlineStr">
         <is>
-          <t>Sebentar dulu. Tarik napas, yuk.</t>
+          <t>Izinkan Autostart</t>
         </is>
       </c>
       <c r="F201" s="7" t="inlineStr">
         <is>
-          <t>Hold on a moment. Let's take a breath.</t>
+          <t>Allow Autostart</t>
         </is>
       </c>
       <c r="G201" s="7" t="inlineStr">
         <is>
-          <t>For daytime slots (e.g. 13.00–15.00).</t>
+          <t>Opens the vendor Autostart screen.</t>
         </is>
       </c>
       <c r="H201" s="6" t="inlineStr"/>
       <c r="I201" s="6" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="5" t="n">
+      <c r="A202" s="7" t="n">
         <v>201</v>
       </c>
-      <c r="B202" s="5" t="inlineStr">
-        <is>
-          <t>shield_body</t>
-        </is>
-      </c>
-      <c r="C202" s="5" t="inlineStr">
-        <is>
-          <t>Layar terkunci</t>
-        </is>
-      </c>
-      <c r="D202" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E202" s="5" t="inlineStr">
-        <is>
-          <t>Kamu sendiri yang memasang pagar ini, di saat kamu sedang kuat.</t>
-        </is>
-      </c>
-      <c r="F202" s="5" t="inlineStr">
-        <is>
-          <t>You put up this fence yourself, at a moment you were strong.</t>
-        </is>
-      </c>
-      <c r="G202" s="5" t="inlineStr"/>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>keeprun_battery</t>
+        </is>
+      </c>
+      <c r="C202" s="7" t="inlineStr">
+        <is>
+          <t>Lindungi</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>Lepas batas baterai</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>Remove battery limit</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>Opens the vendor battery screen.</t>
+        </is>
+      </c>
       <c r="H202" s="6" t="inlineStr"/>
       <c r="I202" s="6" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="5" t="n">
+      <c r="A203" s="7" t="n">
         <v>202</v>
       </c>
-      <c r="B203" s="5" t="inlineStr">
-        <is>
-          <t>shield_take_jeda</t>
-        </is>
-      </c>
-      <c r="C203" s="5" t="inlineStr">
-        <is>
-          <t>Layar terkunci</t>
-        </is>
-      </c>
-      <c r="D203" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E203" s="5" t="inlineStr">
-        <is>
-          <t>Ambil jeda 60 detik</t>
-        </is>
-      </c>
-      <c r="F203" s="5" t="inlineStr">
-        <is>
-          <t>Take a 60-second pause</t>
-        </is>
-      </c>
-      <c r="G203" s="5" t="inlineStr"/>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>keeprun_done</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t>Lindungi</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>Sudah kuatur</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>All set</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>Hides the card for good.</t>
+        </is>
+      </c>
       <c r="H203" s="6" t="inlineStr"/>
       <c r="I203" s="6" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="5" t="n">
+      <c r="A204" s="7" t="n">
         <v>203</v>
       </c>
-      <c r="B204" s="5" t="inlineStr">
-        <is>
-          <t>shield_close_app</t>
-        </is>
-      </c>
-      <c r="C204" s="5" t="inlineStr">
-        <is>
-          <t>Layar terkunci</t>
-        </is>
-      </c>
-      <c r="D204" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E204" s="5" t="inlineStr">
-        <is>
-          <t>Tutup aplikasi</t>
-        </is>
-      </c>
-      <c r="F204" s="5" t="inlineStr">
-        <is>
-          <t>Close the app</t>
-        </is>
-      </c>
-      <c r="G204" s="5" t="inlineStr"/>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t>apppicker_title</t>
+        </is>
+      </c>
+      <c r="C204" s="7" t="inlineStr">
+        <is>
+          <t>Pilih aplikasi</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>Pilih aplikasi</t>
+        </is>
+      </c>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>Choose apps</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>Title of the app picker opened from Protect. Needs review.</t>
+        </is>
+      </c>
       <c r="H204" s="6" t="inlineStr"/>
       <c r="I204" s="6" t="inlineStr"/>
     </row>
@@ -7557,12 +7569,12 @@
       </c>
       <c r="B205" s="7" t="inlineStr">
         <is>
-          <t>shield_continue</t>
+          <t>apppicker_suggested</t>
         </is>
       </c>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>Layar terkunci</t>
+          <t>Pilih aplikasi</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
@@ -7572,151 +7584,167 @@
       </c>
       <c r="E205" s="7" t="inlineStr">
         <is>
-          <t>Tetap lanjutkan</t>
+          <t>Disarankan</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
-          <t>Continue anyway</t>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="G205" s="7" t="inlineStr">
         <is>
-          <t>Needed for 'Pengingat lembut' mode, where the design has no continue button.</t>
+          <t>Small header over the suggested browsers and social apps that are installed.</t>
         </is>
       </c>
       <c r="H205" s="6" t="inlineStr"/>
       <c r="I205" s="6" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="5" t="n">
+      <c r="A206" s="7" t="n">
         <v>205</v>
       </c>
-      <c r="B206" s="5" t="inlineStr">
-        <is>
-          <t>shield_note_gentle</t>
-        </is>
-      </c>
-      <c r="C206" s="5" t="inlineStr">
-        <is>
-          <t>Layar terkunci</t>
-        </is>
-      </c>
-      <c r="D206" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E206" s="5" t="inlineStr">
-        <is>
-          <t>Kamu tetap bisa melanjutkan jika memang perlu</t>
-        </is>
-      </c>
-      <c r="F206" s="5" t="inlineStr">
-        <is>
-          <t>You can still continue if you really need to</t>
-        </is>
-      </c>
-      <c r="G206" s="5" t="inlineStr"/>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>apppicker_all</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr">
+        <is>
+          <t>Pilih aplikasi</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>Semua aplikasi</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>All apps</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>Small header over the alphabetical list.</t>
+        </is>
+      </c>
       <c r="H206" s="6" t="inlineStr"/>
       <c r="I206" s="6" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="5" t="n">
+      <c r="A207" s="7" t="n">
         <v>206</v>
       </c>
-      <c r="B207" s="5" t="inlineStr">
-        <is>
-          <t>shield_note_pause</t>
-        </is>
-      </c>
-      <c r="C207" s="5" t="inlineStr">
-        <is>
-          <t>Layar terkunci</t>
-        </is>
-      </c>
-      <c r="D207" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E207" s="5" t="inlineStr">
-        <is>
-          <t>Setelah jeda, aplikasi terbuka 5 menit</t>
-        </is>
-      </c>
-      <c r="F207" s="5" t="inlineStr">
-        <is>
-          <t>After the pause, the app opens for 5 minutes</t>
-        </is>
-      </c>
-      <c r="G207" s="5" t="inlineStr"/>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>apppicker_search</t>
+        </is>
+      </c>
+      <c r="C207" s="7" t="inlineStr">
+        <is>
+          <t>Pilih aplikasi</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>Cari aplikasi</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>Search apps</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>Search field placeholder.</t>
+        </is>
+      </c>
       <c r="H207" s="6" t="inlineStr"/>
       <c r="I207" s="6" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="5" t="n">
+      <c r="A208" s="7" t="n">
         <v>207</v>
       </c>
-      <c r="B208" s="5" t="inlineStr">
-        <is>
-          <t>shield_note_full</t>
-        </is>
-      </c>
-      <c r="C208" s="5" t="inlineStr">
-        <is>
-          <t>Layar terkunci</t>
-        </is>
-      </c>
-      <c r="D208" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E208" s="5" t="inlineStr">
-        <is>
-          <t>Terbuka lagi pukul {time}</t>
-        </is>
-      </c>
-      <c r="F208" s="5" t="inlineStr">
-        <is>
-          <t>Opens again at {time}</t>
-        </is>
-      </c>
-      <c r="G208" s="5" t="inlineStr"/>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>slot_edit_from</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="inlineStr">
+        <is>
+          <t>Lindungi</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>Dari</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>Label above the start time picker in the schedule editor. Needs review.</t>
+        </is>
+      </c>
       <c r="H208" s="6" t="inlineStr"/>
       <c r="I208" s="6" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="5" t="n">
+      <c r="A209" s="7" t="n">
         <v>208</v>
       </c>
-      <c r="B209" s="5" t="inlineStr">
-        <is>
-          <t>settings_title</t>
-        </is>
-      </c>
-      <c r="C209" s="5" t="inlineStr">
-        <is>
-          <t>Pengaturan</t>
-        </is>
-      </c>
-      <c r="D209" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E209" s="5" t="inlineStr">
-        <is>
-          <t>Pengaturan</t>
-        </is>
-      </c>
-      <c r="F209" s="5" t="inlineStr">
-        <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="G209" s="5" t="inlineStr"/>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>slot_edit_to</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr">
+        <is>
+          <t>Lindungi</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>Sampai</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>Label above the end time picker in the schedule editor. Needs review.</t>
+        </is>
+      </c>
       <c r="H209" s="6" t="inlineStr"/>
       <c r="I209" s="6" t="inlineStr"/>
     </row>
@@ -7726,12 +7754,12 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>settings_profile_title</t>
+          <t>shield_label</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Layar terkunci</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
@@ -7741,15 +7769,19 @@
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>Akun anonim</t>
+          <t>Waktu terjaga · sampai {time}</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>Anonymous account</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr"/>
+          <t>Guarded hours · until {time}</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="inlineStr">
+        <is>
+          <t>Rendered UPPERCASE.</t>
+        </is>
+      </c>
       <c r="H210" s="6" t="inlineStr"/>
       <c r="I210" s="6" t="inlineStr"/>
     </row>
@@ -7759,12 +7791,12 @@
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>settings_profile_sub</t>
+          <t>shield_title</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Layar terkunci</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
@@ -7774,85 +7806,89 @@
       </c>
       <c r="E211" s="5" t="inlineStr">
         <is>
-          <t>Tanpa email · data hanya di HP ini</t>
+          <t>Sudah larut. Istirahat dulu, yuk.</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>No email · data stays on this phone</t>
-        </is>
-      </c>
-      <c r="G211" s="5" t="inlineStr"/>
+          <t>It's late. Time to rest, okay?</t>
+        </is>
+      </c>
+      <c r="G211" s="5" t="inlineStr">
+        <is>
+          <t>Fits a late-night slot only. A daytime variant is proposed below.</t>
+        </is>
+      </c>
       <c r="H211" s="6" t="inlineStr"/>
       <c r="I211" s="6" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="n">
+      <c r="A212" s="7" t="n">
         <v>211</v>
       </c>
-      <c r="B212" s="5" t="inlineStr">
-        <is>
-          <t>settings_group_privacy</t>
-        </is>
-      </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>Pengaturan</t>
-        </is>
-      </c>
-      <c r="D212" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E212" s="5" t="inlineStr">
-        <is>
-          <t>Privasi</t>
-        </is>
-      </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>Privacy</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr"/>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t>shield_title_day</t>
+        </is>
+      </c>
+      <c r="C212" s="7" t="inlineStr">
+        <is>
+          <t>Layar terkunci</t>
+        </is>
+      </c>
+      <c r="D212" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>Sebentar dulu. Tarik napas, yuk.</t>
+        </is>
+      </c>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>Hold on a moment. Let's take a breath.</t>
+        </is>
+      </c>
+      <c r="G212" s="7" t="inlineStr">
+        <is>
+          <t>For daytime slots (e.g. 13.00–15.00).</t>
+        </is>
+      </c>
       <c r="H212" s="6" t="inlineStr"/>
       <c r="I212" s="6" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="8" t="n">
+      <c r="A213" s="5" t="n">
         <v>212</v>
       </c>
-      <c r="B213" s="8" t="inlineStr">
-        <is>
-          <t>settings_pin_lock</t>
-        </is>
-      </c>
-      <c r="C213" s="8" t="inlineStr">
-        <is>
-          <t>Pengaturan</t>
-        </is>
-      </c>
-      <c r="D213" s="8" t="inlineStr">
-        <is>
-          <t>ANDROID</t>
-        </is>
-      </c>
-      <c r="E213" s="8" t="inlineStr">
-        <is>
-          <t>Kunci dengan PIN &amp; sidik jari</t>
-        </is>
-      </c>
-      <c r="F213" s="8" t="inlineStr">
-        <is>
-          <t>Lock with PIN &amp; fingerprint</t>
-        </is>
-      </c>
-      <c r="G213" s="8" t="inlineStr">
-        <is>
-          <t>Original: '…&amp; Face ID'.</t>
-        </is>
-      </c>
+      <c r="B213" s="5" t="inlineStr">
+        <is>
+          <t>shield_body</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>Layar terkunci</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="inlineStr">
+        <is>
+          <t>Kamu sendiri yang memasang pagar ini, di saat kamu sedang kuat.</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>You put up this fence yourself, at a moment you were strong.</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr"/>
       <c r="H213" s="6" t="inlineStr"/>
       <c r="I213" s="6" t="inlineStr"/>
     </row>
@@ -7862,12 +7898,12 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>settings_disguise</t>
+          <t>shield_take_jeda</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Layar terkunci</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
@@ -7877,12 +7913,12 @@
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>Ikon &amp; nama samaran</t>
+          <t>Ambil jeda 60 detik</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>Disguised icon &amp; name</t>
+          <t>Take a 60-second pause</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr"/>
@@ -7895,12 +7931,12 @@
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>settings_hide_search</t>
+          <t>shield_close_app</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Layar terkunci</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
@@ -7910,19 +7946,15 @@
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>Sembunyikan dari pencarian HP</t>
+          <t>Tutup aplikasi</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>Hide from phone search</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr">
-        <is>
-          <t>Android has no reliable API for this. Proposal: remove it, or replace it with 'Sembunyikan isi di layar Recent' / 'Hide content in Recents' (FLAG_SECURE).</t>
-        </is>
-      </c>
+          <t>Close the app</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr"/>
       <c r="H215" s="6" t="inlineStr"/>
       <c r="I215" s="6" t="inlineStr"/>
     </row>
@@ -7932,12 +7964,12 @@
       </c>
       <c r="B216" s="7" t="inlineStr">
         <is>
-          <t>settings_hide_recents</t>
+          <t>shield_continue</t>
         </is>
       </c>
       <c r="C216" s="7" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Layar terkunci</t>
         </is>
       </c>
       <c r="D216" s="7" t="inlineStr">
@@ -7947,17 +7979,17 @@
       </c>
       <c r="E216" s="7" t="inlineStr">
         <is>
-          <t>Sembunyikan isi di layar Recent</t>
+          <t>Tetap lanjutkan</t>
         </is>
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
-          <t>Hide content in Recents</t>
+          <t>Continue anyway</t>
         </is>
       </c>
       <c r="G216" s="7" t="inlineStr">
         <is>
-          <t>Android replacement for the row above (FLAG_SECURE also blocks screenshots).</t>
+          <t>Needed for 'Pengingat lembut' mode, where the design has no continue button.</t>
         </is>
       </c>
       <c r="H216" s="6" t="inlineStr"/>
@@ -7969,12 +8001,12 @@
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>settings_group_journey</t>
+          <t>shield_note_gentle</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Layar terkunci</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
@@ -7984,12 +8016,12 @@
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>Perjalanan</t>
+          <t>Kamu tetap bisa melanjutkan jika memang perlu</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>Journey</t>
+          <t>You can still continue if you really need to</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr"/>
@@ -8002,12 +8034,12 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>settings_target</t>
+          <t>shield_note_pause</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Layar terkunci</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
@@ -8017,12 +8049,12 @@
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Setelah jeda, aplikasi terbuka 5 menit</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>After the pause, the app opens for 5 minutes</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr"/>
@@ -8035,12 +8067,12 @@
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>settings_target_value</t>
+          <t>shield_note_full</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Layar terkunci</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
@@ -8050,19 +8082,15 @@
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>{n} hari</t>
+          <t>Terbuka lagi pukul {time}</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>{n} days</t>
-        </is>
-      </c>
-      <c r="G219" s="5" t="inlineStr">
-        <is>
-          <t>PLURAL in EN.</t>
-        </is>
-      </c>
+          <t>Opens again at {time}</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="inlineStr"/>
       <c r="H219" s="6" t="inlineStr"/>
       <c r="I219" s="6" t="inlineStr"/>
     </row>
@@ -8072,7 +8100,7 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>settings_reminders</t>
+          <t>settings_title</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
@@ -8087,12 +8115,12 @@
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>Pengingat sholat &amp; dzikir</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>Prayer &amp; dhikr reminders</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr"/>
@@ -8105,7 +8133,7 @@
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>settings_schedule</t>
+          <t>settings_profile_title</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
@@ -8120,12 +8148,12 @@
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>Jadwal waktu terjaga</t>
+          <t>Akun anonim</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>Guarded-hours schedule</t>
+          <t>Anonymous account</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr"/>
@@ -8138,7 +8166,7 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>settings_group_data</t>
+          <t>settings_profile_sub</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
@@ -8153,12 +8181,12 @@
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>Data &amp; bantuan</t>
+          <t>Tanpa email · data hanya di HP ini</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Data &amp; help</t>
+          <t>No email · data stays on this phone</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr"/>
@@ -8171,7 +8199,7 @@
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>settings_export_delete</t>
+          <t>settings_group_privacy</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
@@ -8186,12 +8214,12 @@
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>Ekspor &amp; hapus data</t>
+          <t>Privasi</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>Export &amp; delete data</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr"/>
@@ -8199,76 +8227,72 @@
       <c r="I223" s="6" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="5" t="n">
+      <c r="A224" s="8" t="n">
         <v>223</v>
       </c>
-      <c r="B224" s="5" t="inlineStr">
-        <is>
-          <t>settings_counselor</t>
-        </is>
-      </c>
-      <c r="C224" s="5" t="inlineStr">
+      <c r="B224" s="8" t="inlineStr">
+        <is>
+          <t>settings_pin_lock</t>
+        </is>
+      </c>
+      <c r="C224" s="8" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D224" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E224" s="5" t="inlineStr">
-        <is>
-          <t>Bicara dengan konselor</t>
-        </is>
-      </c>
-      <c r="F224" s="5" t="inlineStr">
-        <is>
-          <t>Talk to a counselor</t>
-        </is>
-      </c>
-      <c r="G224" s="5" t="inlineStr">
-        <is>
-          <t>Where does it go? Needs a real contact or link before release.</t>
+      <c r="D224" s="8" t="inlineStr">
+        <is>
+          <t>ANDROID</t>
+        </is>
+      </c>
+      <c r="E224" s="8" t="inlineStr">
+        <is>
+          <t>Kunci dengan PIN &amp; sidik jari</t>
+        </is>
+      </c>
+      <c r="F224" s="8" t="inlineStr">
+        <is>
+          <t>Lock with PIN &amp; fingerprint</t>
+        </is>
+      </c>
+      <c r="G224" s="8" t="inlineStr">
+        <is>
+          <t>Original: '…&amp; Face ID'.</t>
         </is>
       </c>
       <c r="H224" s="6" t="inlineStr"/>
       <c r="I224" s="6" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="7" t="n">
+      <c r="A225" s="5" t="n">
         <v>224</v>
       </c>
-      <c r="B225" s="7" t="inlineStr">
-        <is>
-          <t>counselor_placeholder</t>
-        </is>
-      </c>
-      <c r="C225" s="7" t="inlineStr">
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>settings_disguise</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D225" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E225" s="7" t="inlineStr">
-        <is>
-          <t>Segera hadir. Kami sedang menyiapkan kontak konselor yang tepercaya.</t>
-        </is>
-      </c>
-      <c r="F225" s="7" t="inlineStr">
-        <is>
-          <t>Coming soon. We're preparing a trusted counselor contact.</t>
-        </is>
-      </c>
-      <c r="G225" s="7" t="inlineStr">
-        <is>
-          <t>Shown in the counselor sheet until a real contact or link exists.</t>
-        </is>
-      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="inlineStr">
+        <is>
+          <t>Ikon &amp; nama samaran</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="inlineStr">
+        <is>
+          <t>Disguised icon &amp; name</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="inlineStr"/>
       <c r="H225" s="6" t="inlineStr"/>
       <c r="I225" s="6" t="inlineStr"/>
     </row>
@@ -8278,7 +8302,7 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>settings_about</t>
+          <t>settings_hide_search</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
@@ -8293,15 +8317,19 @@
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>Tentang Izzah</t>
+          <t>Sembunyikan dari pencarian HP</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>About Izzah</t>
-        </is>
-      </c>
-      <c r="G226" s="5" t="inlineStr"/>
+          <t>Hide from phone search</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="inlineStr">
+        <is>
+          <t>Android has no reliable API for this. Proposal: remove it, or replace it with 'Sembunyikan isi di layar Recent' / 'Hide content in Recents' (FLAG_SECURE).</t>
+        </is>
+      </c>
       <c r="H226" s="6" t="inlineStr"/>
       <c r="I226" s="6" t="inlineStr"/>
     </row>
@@ -8311,7 +8339,7 @@
       </c>
       <c r="B227" s="7" t="inlineStr">
         <is>
-          <t>settings_language</t>
+          <t>settings_hide_recents</t>
         </is>
       </c>
       <c r="C227" s="7" t="inlineStr">
@@ -8326,124 +8354,120 @@
       </c>
       <c r="E227" s="7" t="inlineStr">
         <is>
-          <t>Bahasa</t>
+          <t>Sembunyikan isi di layar Recent</t>
         </is>
       </c>
       <c r="F227" s="7" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Hide content in Recents</t>
         </is>
       </c>
       <c r="G227" s="7" t="inlineStr">
         <is>
-          <t>Language picker row, under Privasi or a new 'Umum' group.</t>
+          <t>Android replacement for the row above (FLAG_SECURE also blocks screenshots).</t>
         </is>
       </c>
       <c r="H227" s="6" t="inlineStr"/>
       <c r="I227" s="6" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="7" t="n">
+      <c r="A228" s="5" t="n">
         <v>227</v>
       </c>
-      <c r="B228" s="7" t="inlineStr">
-        <is>
-          <t>language_system</t>
-        </is>
-      </c>
-      <c r="C228" s="7" t="inlineStr">
+      <c r="B228" s="5" t="inlineStr">
+        <is>
+          <t>settings_group_journey</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D228" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E228" s="7" t="inlineStr">
-        <is>
-          <t>Ikuti sistem</t>
-        </is>
-      </c>
-      <c r="F228" s="7" t="inlineStr">
-        <is>
-          <t>System default</t>
-        </is>
-      </c>
-      <c r="G228" s="7" t="inlineStr"/>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E228" s="5" t="inlineStr">
+        <is>
+          <t>Perjalanan</t>
+        </is>
+      </c>
+      <c r="F228" s="5" t="inlineStr">
+        <is>
+          <t>Journey</t>
+        </is>
+      </c>
+      <c r="G228" s="5" t="inlineStr"/>
       <c r="H228" s="6" t="inlineStr"/>
       <c r="I228" s="6" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="7" t="n">
+      <c r="A229" s="5" t="n">
         <v>228</v>
       </c>
-      <c r="B229" s="7" t="inlineStr">
-        <is>
-          <t>language_id</t>
-        </is>
-      </c>
-      <c r="C229" s="7" t="inlineStr">
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>settings_target</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D229" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E229" s="7" t="inlineStr">
-        <is>
-          <t>Bahasa Indonesia</t>
-        </is>
-      </c>
-      <c r="F229" s="7" t="inlineStr">
-        <is>
-          <t>Bahasa Indonesia</t>
-        </is>
-      </c>
-      <c r="G229" s="7" t="inlineStr">
-        <is>
-          <t>Always shown in its own language.</t>
-        </is>
-      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="G229" s="5" t="inlineStr"/>
       <c r="H229" s="6" t="inlineStr"/>
       <c r="I229" s="6" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="7" t="n">
+      <c r="A230" s="5" t="n">
         <v>229</v>
       </c>
-      <c r="B230" s="7" t="inlineStr">
-        <is>
-          <t>language_en</t>
-        </is>
-      </c>
-      <c r="C230" s="7" t="inlineStr">
+      <c r="B230" s="5" t="inlineStr">
+        <is>
+          <t>settings_target_value</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="inlineStr">
         <is>
           <t>Pengaturan</t>
         </is>
       </c>
-      <c r="D230" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E230" s="7" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="F230" s="7" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G230" s="7" t="inlineStr">
-        <is>
-          <t>Always shown in its own language.</t>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="inlineStr">
+        <is>
+          <t>{n} hari</t>
+        </is>
+      </c>
+      <c r="F230" s="5" t="inlineStr">
+        <is>
+          <t>{n} days</t>
+        </is>
+      </c>
+      <c r="G230" s="5" t="inlineStr">
+        <is>
+          <t>PLURAL in EN.</t>
         </is>
       </c>
       <c r="H230" s="6" t="inlineStr"/>
@@ -8455,12 +8479,12 @@
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>disguise_title</t>
+          <t>settings_reminders</t>
         </is>
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>Ikon samaran</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
@@ -8470,12 +8494,12 @@
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>Ikon samaran</t>
+          <t>Pengingat sholat &amp; dzikir</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>Disguised icon</t>
+          <t>Prayer &amp; dhikr reminders</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr"/>
@@ -8488,12 +8512,12 @@
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>disguise_desc</t>
+          <t>settings_schedule</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>Ikon samaran</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
@@ -8503,12 +8527,12 @@
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>Ganti ikon dan nama di layar HP supaya tidak menarik perhatian.</t>
+          <t>Jadwal waktu terjaga</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>Change the icon and name on your home screen so it doesn't draw attention.</t>
+          <t>Guarded-hours schedule</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr"/>
@@ -8521,12 +8545,12 @@
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>disguise_izzah</t>
+          <t>settings_group_data</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>Ikon samaran</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
@@ -8536,12 +8560,12 @@
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>Izzah</t>
+          <t>Data &amp; bantuan</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>Izzah</t>
+          <t>Data &amp; help</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr"/>
@@ -8554,12 +8578,12 @@
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>disguise_steps</t>
+          <t>settings_export_delete</t>
         </is>
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>Ikon samaran</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
@@ -8569,19 +8593,15 @@
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>Langkah</t>
+          <t>Ekspor &amp; hapus data</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G234" s="5" t="inlineStr">
-        <is>
-          <t>This becomes the launcher label, so it's localized too.</t>
-        </is>
-      </c>
+          <t>Export &amp; delete data</t>
+        </is>
+      </c>
+      <c r="G234" s="5" t="inlineStr"/>
       <c r="H234" s="6" t="inlineStr"/>
       <c r="I234" s="6" t="inlineStr"/>
     </row>
@@ -8591,12 +8611,12 @@
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>disguise_focus</t>
+          <t>settings_counselor</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>Ikon samaran</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
@@ -8606,217 +8626,233 @@
       </c>
       <c r="E235" s="5" t="inlineStr">
         <is>
-          <t>Fokus</t>
+          <t>Bicara dengan konselor</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>Focus</t>
-        </is>
-      </c>
-      <c r="G235" s="5" t="inlineStr"/>
+          <t>Talk to a counselor</t>
+        </is>
+      </c>
+      <c r="G235" s="5" t="inlineStr">
+        <is>
+          <t>Where does it go? Needs a real contact or link before release.</t>
+        </is>
+      </c>
       <c r="H235" s="6" t="inlineStr"/>
       <c r="I235" s="6" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="5" t="n">
+      <c r="A236" s="7" t="n">
         <v>235</v>
       </c>
-      <c r="B236" s="5" t="inlineStr">
-        <is>
-          <t>disguise_notes</t>
-        </is>
-      </c>
-      <c r="C236" s="5" t="inlineStr">
-        <is>
-          <t>Ikon samaran</t>
-        </is>
-      </c>
-      <c r="D236" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E236" s="5" t="inlineStr">
-        <is>
-          <t>Catatan</t>
-        </is>
-      </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="G236" s="5" t="inlineStr"/>
+      <c r="B236" s="7" t="inlineStr">
+        <is>
+          <t>counselor_placeholder</t>
+        </is>
+      </c>
+      <c r="C236" s="7" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E236" s="7" t="inlineStr">
+        <is>
+          <t>Segera hadir. Kami sedang menyiapkan kontak konselor yang tepercaya.</t>
+        </is>
+      </c>
+      <c r="F236" s="7" t="inlineStr">
+        <is>
+          <t>Coming soon. We're preparing a trusted counselor contact.</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>Shown in the counselor sheet until a real contact or link exists.</t>
+        </is>
+      </c>
       <c r="H236" s="6" t="inlineStr"/>
       <c r="I236" s="6" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="8" t="n">
+      <c r="A237" s="5" t="n">
         <v>236</v>
       </c>
-      <c r="B237" s="8" t="inlineStr">
-        <is>
-          <t>disguise_footer</t>
-        </is>
-      </c>
-      <c r="C237" s="8" t="inlineStr">
-        <is>
-          <t>Ikon samaran</t>
-        </is>
-      </c>
-      <c r="D237" s="8" t="inlineStr">
-        <is>
-          <t>ANDROID</t>
-        </is>
-      </c>
-      <c r="E237" s="8" t="inlineStr">
-        <is>
-          <t>Nama di notifikasi tetap “Izzah”, tapi isinya selalu netral.</t>
-        </is>
-      </c>
-      <c r="F237" s="8" t="inlineStr">
-        <is>
-          <t>Notifications still show “Izzah”, but their content is always neutral.</t>
-        </is>
-      </c>
-      <c r="G237" s="8" t="inlineStr">
-        <is>
-          <t>Original: 'Notifikasi akan memakai nama yang sama.' Android always shows the application label in notifications; an activity-alias can't change it.</t>
-        </is>
-      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>settings_about</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E237" s="5" t="inlineStr">
+        <is>
+          <t>Tentang Izzah</t>
+        </is>
+      </c>
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>About Izzah</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="inlineStr"/>
       <c r="H237" s="6" t="inlineStr"/>
       <c r="I237" s="6" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="n">
+      <c r="A238" s="7" t="n">
         <v>237</v>
       </c>
-      <c r="B238" s="5" t="inlineStr">
-        <is>
-          <t>data_title</t>
-        </is>
-      </c>
-      <c r="C238" s="5" t="inlineStr">
-        <is>
-          <t>Datamu</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E238" s="5" t="inlineStr">
-        <is>
-          <t>Datamu</t>
-        </is>
-      </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>Your data</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr"/>
+      <c r="B238" s="7" t="inlineStr">
+        <is>
+          <t>settings_language</t>
+        </is>
+      </c>
+      <c r="C238" s="7" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="D238" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E238" s="7" t="inlineStr">
+        <is>
+          <t>Bahasa</t>
+        </is>
+      </c>
+      <c r="F238" s="7" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="inlineStr">
+        <is>
+          <t>Language picker row, under Privasi or a new 'Umum' group.</t>
+        </is>
+      </c>
       <c r="H238" s="6" t="inlineStr"/>
       <c r="I238" s="6" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="n">
+      <c r="A239" s="7" t="n">
         <v>238</v>
       </c>
-      <c r="B239" s="5" t="inlineStr">
-        <is>
-          <t>data_desc</t>
-        </is>
-      </c>
-      <c r="C239" s="5" t="inlineStr">
-        <is>
-          <t>Datamu</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E239" s="5" t="inlineStr">
-        <is>
-          <t>Semua tersimpan di HP ini. Tidak ada di server kami.</t>
-        </is>
-      </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>Everything is stored on this phone. Nothing is on our servers.</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr"/>
+      <c r="B239" s="7" t="inlineStr">
+        <is>
+          <t>language_system</t>
+        </is>
+      </c>
+      <c r="C239" s="7" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="D239" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E239" s="7" t="inlineStr">
+        <is>
+          <t>Ikuti sistem</t>
+        </is>
+      </c>
+      <c r="F239" s="7" t="inlineStr">
+        <is>
+          <t>System default</t>
+        </is>
+      </c>
+      <c r="G239" s="7" t="inlineStr"/>
       <c r="H239" s="6" t="inlineStr"/>
       <c r="I239" s="6" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="n">
+      <c r="A240" s="7" t="n">
         <v>239</v>
       </c>
-      <c r="B240" s="5" t="inlineStr">
-        <is>
-          <t>data_export_title</t>
-        </is>
-      </c>
-      <c r="C240" s="5" t="inlineStr">
-        <is>
-          <t>Datamu</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E240" s="5" t="inlineStr">
-        <is>
-          <t>Ekspor cadangan</t>
-        </is>
-      </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>Export a backup</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr"/>
+      <c r="B240" s="7" t="inlineStr">
+        <is>
+          <t>language_id</t>
+        </is>
+      </c>
+      <c r="C240" s="7" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="D240" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E240" s="7" t="inlineStr">
+        <is>
+          <t>Bahasa Indonesia</t>
+        </is>
+      </c>
+      <c r="F240" s="7" t="inlineStr">
+        <is>
+          <t>Bahasa Indonesia</t>
+        </is>
+      </c>
+      <c r="G240" s="7" t="inlineStr">
+        <is>
+          <t>Always shown in its own language.</t>
+        </is>
+      </c>
       <c r="H240" s="6" t="inlineStr"/>
       <c r="I240" s="6" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="n">
+      <c r="A241" s="7" t="n">
         <v>240</v>
       </c>
-      <c r="B241" s="5" t="inlineStr">
-        <is>
-          <t>data_export_desc</t>
-        </is>
-      </c>
-      <c r="C241" s="5" t="inlineStr">
-        <is>
-          <t>Datamu</t>
-        </is>
-      </c>
-      <c r="D241" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E241" s="5" t="inlineStr">
-        <is>
-          <t>File terenkripsi dengan PIN-mu. Pakai saat pindah HP.</t>
-        </is>
-      </c>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>A file encrypted with your PIN. Use it when you switch phones.</t>
-        </is>
-      </c>
-      <c r="G241" s="5" t="inlineStr"/>
+      <c r="B241" s="7" t="inlineStr">
+        <is>
+          <t>language_en</t>
+        </is>
+      </c>
+      <c r="C241" s="7" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="D241" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E241" s="7" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="F241" s="7" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G241" s="7" t="inlineStr">
+        <is>
+          <t>Always shown in its own language.</t>
+        </is>
+      </c>
       <c r="H241" s="6" t="inlineStr"/>
       <c r="I241" s="6" t="inlineStr"/>
     </row>
@@ -8826,12 +8862,12 @@
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>data_export_cta</t>
+          <t>disguise_title</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>Datamu</t>
+          <t>Ikon samaran</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
@@ -8841,12 +8877,12 @@
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>Buat file cadangan</t>
+          <t>Ikon samaran</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>Create backup file</t>
+          <t>Disguised icon</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr"/>
@@ -8854,107 +8890,103 @@
       <c r="I242" s="6" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="7" t="n">
+      <c r="A243" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="B243" s="7" t="inlineStr">
-        <is>
-          <t>data_import_wrong_pin</t>
-        </is>
-      </c>
-      <c r="C243" s="7" t="inlineStr">
-        <is>
-          <t>Datamu</t>
-        </is>
-      </c>
-      <c r="D243" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E243" s="7" t="inlineStr">
-        <is>
-          <t>PIN cadangan tidak cocok.</t>
-        </is>
-      </c>
-      <c r="F243" s="7" t="inlineStr">
-        <is>
-          <t>The backup PIN doesn't match.</t>
-        </is>
-      </c>
-      <c r="G243" s="7" t="inlineStr"/>
+      <c r="B243" s="5" t="inlineStr">
+        <is>
+          <t>disguise_desc</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>Ikon samaran</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="inlineStr">
+        <is>
+          <t>Ganti ikon dan nama di layar HP supaya tidak menarik perhatian.</t>
+        </is>
+      </c>
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>Change the icon and name on your home screen so it doesn't draw attention.</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr"/>
       <c r="H243" s="6" t="inlineStr"/>
       <c r="I243" s="6" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="7" t="n">
+      <c r="A244" s="5" t="n">
         <v>243</v>
       </c>
-      <c r="B244" s="7" t="inlineStr">
-        <is>
-          <t>data_export_done</t>
-        </is>
-      </c>
-      <c r="C244" s="7" t="inlineStr">
-        <is>
-          <t>Datamu</t>
-        </is>
-      </c>
-      <c r="D244" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E244" s="7" t="inlineStr">
-        <is>
-          <t>Cadangan tersimpan.</t>
-        </is>
-      </c>
-      <c r="F244" s="7" t="inlineStr">
-        <is>
-          <t>Backup saved.</t>
-        </is>
-      </c>
-      <c r="G244" s="7" t="inlineStr">
-        <is>
-          <t>Toast after the system save dialog.</t>
-        </is>
-      </c>
+      <c r="B244" s="5" t="inlineStr">
+        <is>
+          <t>disguise_izzah</t>
+        </is>
+      </c>
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>Ikon samaran</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E244" s="5" t="inlineStr">
+        <is>
+          <t>Izzah</t>
+        </is>
+      </c>
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>Izzah</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="inlineStr"/>
       <c r="H244" s="6" t="inlineStr"/>
       <c r="I244" s="6" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="7" t="n">
+      <c r="A245" s="5" t="n">
         <v>244</v>
       </c>
-      <c r="B245" s="7" t="inlineStr">
-        <is>
-          <t>data_import_cta</t>
-        </is>
-      </c>
-      <c r="C245" s="7" t="inlineStr">
-        <is>
-          <t>Datamu</t>
-        </is>
-      </c>
-      <c r="D245" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E245" s="7" t="inlineStr">
-        <is>
-          <t>Pulihkan dari cadangan</t>
-        </is>
-      </c>
-      <c r="F245" s="7" t="inlineStr">
-        <is>
-          <t>Restore from backup</t>
-        </is>
-      </c>
-      <c r="G245" s="7" t="inlineStr">
-        <is>
-          <t>Without this, the export is useless on a new phone. Proposed for v1.</t>
+      <c r="B245" s="5" t="inlineStr">
+        <is>
+          <t>disguise_steps</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="inlineStr">
+        <is>
+          <t>Ikon samaran</t>
+        </is>
+      </c>
+      <c r="D245" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E245" s="5" t="inlineStr">
+        <is>
+          <t>Langkah</t>
+        </is>
+      </c>
+      <c r="F245" s="5" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G245" s="5" t="inlineStr">
+        <is>
+          <t>This becomes the launcher label, so it's localized too.</t>
         </is>
       </c>
       <c r="H245" s="6" t="inlineStr"/>
@@ -8966,12 +8998,12 @@
       </c>
       <c r="B246" s="5" t="inlineStr">
         <is>
-          <t>data_delete_title</t>
+          <t>disguise_focus</t>
         </is>
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>Datamu</t>
+          <t>Ikon samaran</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
@@ -8981,12 +9013,12 @@
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>Hapus semua data</t>
+          <t>Fokus</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>Delete all data</t>
+          <t>Focus</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr"/>
@@ -8999,12 +9031,12 @@
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>data_delete_desc</t>
+          <t>disguise_notes</t>
         </is>
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>Datamu</t>
+          <t>Ikon samaran</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
@@ -9014,12 +9046,12 @@
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>Progres, jurnal, dan pengaturan akan hilang permanen.</t>
+          <t>Catatan</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>Your progress, journal and settings will be permanently erased.</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr"/>
@@ -9027,35 +9059,39 @@
       <c r="I247" s="6" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="5" t="n">
+      <c r="A248" s="8" t="n">
         <v>247</v>
       </c>
-      <c r="B248" s="5" t="inlineStr">
-        <is>
-          <t>data_delete_cta</t>
-        </is>
-      </c>
-      <c r="C248" s="5" t="inlineStr">
-        <is>
-          <t>Datamu</t>
-        </is>
-      </c>
-      <c r="D248" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E248" s="5" t="inlineStr">
-        <is>
-          <t>Hapus data</t>
-        </is>
-      </c>
-      <c r="F248" s="5" t="inlineStr">
-        <is>
-          <t>Delete data</t>
-        </is>
-      </c>
-      <c r="G248" s="5" t="inlineStr"/>
+      <c r="B248" s="8" t="inlineStr">
+        <is>
+          <t>disguise_footer</t>
+        </is>
+      </c>
+      <c r="C248" s="8" t="inlineStr">
+        <is>
+          <t>Ikon samaran</t>
+        </is>
+      </c>
+      <c r="D248" s="8" t="inlineStr">
+        <is>
+          <t>ANDROID</t>
+        </is>
+      </c>
+      <c r="E248" s="8" t="inlineStr">
+        <is>
+          <t>Nama di notifikasi tetap “Izzah”, tapi isinya selalu netral.</t>
+        </is>
+      </c>
+      <c r="F248" s="8" t="inlineStr">
+        <is>
+          <t>Notifications still show “Izzah”, but their content is always neutral.</t>
+        </is>
+      </c>
+      <c r="G248" s="8" t="inlineStr">
+        <is>
+          <t>Original: 'Notifikasi akan memakai nama yang sama.' Android always shows the application label in notifications; an activity-alias can't change it.</t>
+        </is>
+      </c>
       <c r="H248" s="6" t="inlineStr"/>
       <c r="I248" s="6" t="inlineStr"/>
     </row>
@@ -9065,12 +9101,12 @@
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>delete_sheet_title</t>
+          <t>data_title</t>
         </is>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>Hapus (sheet)</t>
+          <t>Datamu</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
@@ -9080,12 +9116,12 @@
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>Yakin hapus semua?</t>
+          <t>Datamu</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>Delete everything?</t>
+          <t>Your data</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr"/>
@@ -9098,12 +9134,12 @@
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>delete_sheet_body</t>
+          <t>data_desc</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>Hapus (sheet)</t>
+          <t>Datamu</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
@@ -9113,12 +9149,12 @@
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>Ini tidak bisa dibatalkan. Kalau hanya ingin istirahat, kamu bisa menjeda pengingat saja.</t>
+          <t>Semua tersimpan di HP ini. Tidak ada di server kami.</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>This can't be undone. If you just need a break, you can pause the reminders instead.</t>
+          <t>Everything is stored on this phone. Nothing is on our servers.</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr"/>
@@ -9131,12 +9167,12 @@
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>delete_sheet_confirm</t>
+          <t>data_export_title</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>Hapus (sheet)</t>
+          <t>Datamu</t>
         </is>
       </c>
       <c r="D251" s="5" t="inlineStr">
@@ -9146,12 +9182,12 @@
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>Ya, hapus semuanya</t>
+          <t>Ekspor cadangan</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>Yes, delete everything</t>
+          <t>Export a backup</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr"/>
@@ -9164,12 +9200,12 @@
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>common_cancel</t>
+          <t>data_export_desc</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>Hapus (sheet)</t>
+          <t>Datamu</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
@@ -9179,12 +9215,12 @@
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>Batal</t>
+          <t>File terenkripsi dengan PIN-mu. Pakai saat pindah HP.</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>A file encrypted with your PIN. Use it when you switch phones.</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr"/>
@@ -9197,12 +9233,12 @@
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>unlock_title</t>
+          <t>data_export_cta</t>
         </is>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>Buka dengan PIN</t>
+          <t>Datamu</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
@@ -9212,12 +9248,12 @@
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>Masukkan PIN</t>
+          <t>Buat file cadangan</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>Enter your PIN</t>
+          <t>Create backup file</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr"/>
@@ -9225,35 +9261,35 @@
       <c r="I253" s="6" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="5" t="n">
+      <c r="A254" s="7" t="n">
         <v>253</v>
       </c>
-      <c r="B254" s="5" t="inlineStr">
-        <is>
-          <t>unlock_subtitle</t>
-        </is>
-      </c>
-      <c r="C254" s="5" t="inlineStr">
-        <is>
-          <t>Buka dengan PIN</t>
-        </is>
-      </c>
-      <c r="D254" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E254" s="5" t="inlineStr">
-        <is>
-          <t>Assalamu’alaikum. Selamat datang kembali.</t>
-        </is>
-      </c>
-      <c r="F254" s="5" t="inlineStr">
-        <is>
-          <t>Assalamu’alaikum. Welcome back.</t>
-        </is>
-      </c>
-      <c r="G254" s="5" t="inlineStr"/>
+      <c r="B254" s="7" t="inlineStr">
+        <is>
+          <t>data_import_wrong_pin</t>
+        </is>
+      </c>
+      <c r="C254" s="7" t="inlineStr">
+        <is>
+          <t>Datamu</t>
+        </is>
+      </c>
+      <c r="D254" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E254" s="7" t="inlineStr">
+        <is>
+          <t>PIN cadangan tidak cocok.</t>
+        </is>
+      </c>
+      <c r="F254" s="7" t="inlineStr">
+        <is>
+          <t>The backup PIN doesn't match.</t>
+        </is>
+      </c>
+      <c r="G254" s="7" t="inlineStr"/>
       <c r="H254" s="6" t="inlineStr"/>
       <c r="I254" s="6" t="inlineStr"/>
     </row>
@@ -9263,12 +9299,12 @@
       </c>
       <c r="B255" s="7" t="inlineStr">
         <is>
-          <t>unlock_wrong</t>
+          <t>data_export_done</t>
         </is>
       </c>
       <c r="C255" s="7" t="inlineStr">
         <is>
-          <t>Buka dengan PIN</t>
+          <t>Datamu</t>
         </is>
       </c>
       <c r="D255" s="7" t="inlineStr">
@@ -9278,15 +9314,19 @@
       </c>
       <c r="E255" s="7" t="inlineStr">
         <is>
-          <t>PIN salah. Coba lagi.</t>
+          <t>Cadangan tersimpan.</t>
         </is>
       </c>
       <c r="F255" s="7" t="inlineStr">
         <is>
-          <t>Wrong PIN. Try again.</t>
-        </is>
-      </c>
-      <c r="G255" s="7" t="inlineStr"/>
+          <t>Backup saved.</t>
+        </is>
+      </c>
+      <c r="G255" s="7" t="inlineStr">
+        <is>
+          <t>Toast after the system save dialog.</t>
+        </is>
+      </c>
       <c r="H255" s="6" t="inlineStr"/>
       <c r="I255" s="6" t="inlineStr"/>
     </row>
@@ -9296,12 +9336,12 @@
       </c>
       <c r="B256" s="7" t="inlineStr">
         <is>
-          <t>unlock_cooldown</t>
+          <t>data_import_cta</t>
         </is>
       </c>
       <c r="C256" s="7" t="inlineStr">
         <is>
-          <t>Buka dengan PIN</t>
+          <t>Datamu</t>
         </is>
       </c>
       <c r="D256" s="7" t="inlineStr">
@@ -9311,159 +9351,151 @@
       </c>
       <c r="E256" s="7" t="inlineStr">
         <is>
-          <t>Terlalu banyak percobaan. Coba lagi dalam {seconds} detik.</t>
+          <t>Pulihkan dari cadangan</t>
         </is>
       </c>
       <c r="F256" s="7" t="inlineStr">
         <is>
-          <t>Too many tries. Try again in {seconds} seconds.</t>
+          <t>Restore from backup</t>
         </is>
       </c>
       <c r="G256" s="7" t="inlineStr">
         <is>
-          <t>After 5 wrong PINs: 30 s cooldown. PLURAL in EN.</t>
+          <t>Without this, the export is useless on a new phone. Proposed for v1.</t>
         </is>
       </c>
       <c r="H256" s="6" t="inlineStr"/>
       <c r="I256" s="6" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="7" t="n">
+      <c r="A257" s="5" t="n">
         <v>256</v>
       </c>
-      <c r="B257" s="7" t="inlineStr">
-        <is>
-          <t>unlock_forgot</t>
-        </is>
-      </c>
-      <c r="C257" s="7" t="inlineStr">
-        <is>
-          <t>Buka dengan PIN</t>
-        </is>
-      </c>
-      <c r="D257" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E257" s="7" t="inlineStr">
-        <is>
-          <t>Lupa PIN?</t>
-        </is>
-      </c>
-      <c r="F257" s="7" t="inlineStr">
-        <is>
-          <t>Forgot your PIN?</t>
-        </is>
-      </c>
-      <c r="G257" s="7" t="inlineStr"/>
+      <c r="B257" s="5" t="inlineStr">
+        <is>
+          <t>data_delete_title</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="inlineStr">
+        <is>
+          <t>Datamu</t>
+        </is>
+      </c>
+      <c r="D257" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E257" s="5" t="inlineStr">
+        <is>
+          <t>Hapus semua data</t>
+        </is>
+      </c>
+      <c r="F257" s="5" t="inlineStr">
+        <is>
+          <t>Delete all data</t>
+        </is>
+      </c>
+      <c r="G257" s="5" t="inlineStr"/>
       <c r="H257" s="6" t="inlineStr"/>
       <c r="I257" s="6" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="7" t="n">
+      <c r="A258" s="5" t="n">
         <v>257</v>
       </c>
-      <c r="B258" s="7" t="inlineStr">
-        <is>
-          <t>unlock_forgot_body</t>
-        </is>
-      </c>
-      <c r="C258" s="7" t="inlineStr">
-        <is>
-          <t>Buka dengan PIN</t>
-        </is>
-      </c>
-      <c r="D258" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E258" s="7" t="inlineStr">
-        <is>
-          <t>Karena akunmu anonim, PIN tidak bisa dipulihkan. Kamu bisa menghapus data dan mulai dari awal, atau memulihkan dari file cadangan.</t>
-        </is>
-      </c>
-      <c r="F258" s="7" t="inlineStr">
-        <is>
-          <t>Your account is anonymous, so the PIN can't be recovered. You can delete your data and start fresh, or restore from a backup file.</t>
-        </is>
-      </c>
-      <c r="G258" s="7" t="inlineStr">
-        <is>
-          <t>Bottom sheet. Buttons reuse delete_sheet_confirm + data_import_cta + common_cancel.</t>
-        </is>
-      </c>
+      <c r="B258" s="5" t="inlineStr">
+        <is>
+          <t>data_delete_desc</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="inlineStr">
+        <is>
+          <t>Datamu</t>
+        </is>
+      </c>
+      <c r="D258" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="inlineStr">
+        <is>
+          <t>Progres, jurnal, dan pengaturan akan hilang permanen.</t>
+        </is>
+      </c>
+      <c r="F258" s="5" t="inlineStr">
+        <is>
+          <t>Your progress, journal and settings will be permanently erased.</t>
+        </is>
+      </c>
+      <c r="G258" s="5" t="inlineStr"/>
       <c r="H258" s="6" t="inlineStr"/>
       <c r="I258" s="6" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="7" t="n">
+      <c r="A259" s="5" t="n">
         <v>258</v>
       </c>
-      <c r="B259" s="7" t="inlineStr">
-        <is>
-          <t>biometric_title</t>
-        </is>
-      </c>
-      <c r="C259" s="7" t="inlineStr">
-        <is>
-          <t>Buka dengan PIN</t>
-        </is>
-      </c>
-      <c r="D259" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E259" s="7" t="inlineStr">
-        <is>
-          <t>Buka Izzah</t>
-        </is>
-      </c>
-      <c r="F259" s="7" t="inlineStr">
-        <is>
-          <t>Unlock Izzah</t>
-        </is>
-      </c>
-      <c r="G259" s="7" t="inlineStr">
-        <is>
-          <t>Title of the system BiometricPrompt. Shows the disguise name if a disguise is active.</t>
-        </is>
-      </c>
+      <c r="B259" s="5" t="inlineStr">
+        <is>
+          <t>data_delete_cta</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="inlineStr">
+        <is>
+          <t>Datamu</t>
+        </is>
+      </c>
+      <c r="D259" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E259" s="5" t="inlineStr">
+        <is>
+          <t>Hapus data</t>
+        </is>
+      </c>
+      <c r="F259" s="5" t="inlineStr">
+        <is>
+          <t>Delete data</t>
+        </is>
+      </c>
+      <c r="G259" s="5" t="inlineStr"/>
       <c r="H259" s="6" t="inlineStr"/>
       <c r="I259" s="6" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="7" t="n">
+      <c r="A260" s="5" t="n">
         <v>259</v>
       </c>
-      <c r="B260" s="7" t="inlineStr">
-        <is>
-          <t>biometric_use_pin</t>
-        </is>
-      </c>
-      <c r="C260" s="7" t="inlineStr">
-        <is>
-          <t>Buka dengan PIN</t>
-        </is>
-      </c>
-      <c r="D260" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E260" s="7" t="inlineStr">
-        <is>
-          <t>Pakai PIN</t>
-        </is>
-      </c>
-      <c r="F260" s="7" t="inlineStr">
-        <is>
-          <t>Use PIN</t>
-        </is>
-      </c>
-      <c r="G260" s="7" t="inlineStr"/>
+      <c r="B260" s="5" t="inlineStr">
+        <is>
+          <t>delete_sheet_title</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="inlineStr">
+        <is>
+          <t>Hapus (sheet)</t>
+        </is>
+      </c>
+      <c r="D260" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="inlineStr">
+        <is>
+          <t>Yakin hapus semua?</t>
+        </is>
+      </c>
+      <c r="F260" s="5" t="inlineStr">
+        <is>
+          <t>Delete everything?</t>
+        </is>
+      </c>
+      <c r="G260" s="5" t="inlineStr"/>
       <c r="H260" s="6" t="inlineStr"/>
       <c r="I260" s="6" t="inlineStr"/>
     </row>
@@ -9473,12 +9505,12 @@
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>notif_prayer_body</t>
+          <t>delete_sheet_body</t>
         </is>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>Notifikasi (sistem)</t>
+          <t>Hapus (sheet)</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
@@ -9488,155 +9520,147 @@
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>Waktunya {prayer}. Sejenak untuk dirimu.</t>
+          <t>Ini tidak bisa dibatalkan. Kalau hanya ingin istirahat, kamu bisa menjeda pengingat saja.</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>Time for {prayer}. A moment for yourself.</t>
-        </is>
-      </c>
-      <c r="G261" s="5" t="inlineStr">
-        <is>
-          <t>RULE: no notification may mention porn, relapse or addiction.</t>
-        </is>
-      </c>
+          <t>This can't be undone. If you just need a break, you can pause the reminders instead.</t>
+        </is>
+      </c>
+      <c r="G261" s="5" t="inlineStr"/>
       <c r="H261" s="6" t="inlineStr"/>
       <c r="I261" s="6" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="7" t="n">
+      <c r="A262" s="5" t="n">
         <v>261</v>
       </c>
-      <c r="B262" s="7" t="inlineStr">
-        <is>
-          <t>notif_dzikir_morning</t>
-        </is>
-      </c>
-      <c r="C262" s="7" t="inlineStr">
-        <is>
-          <t>Notifikasi (sistem)</t>
-        </is>
-      </c>
-      <c r="D262" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E262" s="7" t="inlineStr">
-        <is>
-          <t>Pagi yang baru. Ada waktu sebentar untuk dirimu?</t>
-        </is>
-      </c>
-      <c r="F262" s="7" t="inlineStr">
-        <is>
-          <t>A fresh morning. Got a minute for yourself?</t>
-        </is>
-      </c>
-      <c r="G262" s="7" t="inlineStr"/>
+      <c r="B262" s="5" t="inlineStr">
+        <is>
+          <t>delete_sheet_confirm</t>
+        </is>
+      </c>
+      <c r="C262" s="5" t="inlineStr">
+        <is>
+          <t>Hapus (sheet)</t>
+        </is>
+      </c>
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="inlineStr">
+        <is>
+          <t>Ya, hapus semuanya</t>
+        </is>
+      </c>
+      <c r="F262" s="5" t="inlineStr">
+        <is>
+          <t>Yes, delete everything</t>
+        </is>
+      </c>
+      <c r="G262" s="5" t="inlineStr"/>
       <c r="H262" s="6" t="inlineStr"/>
       <c r="I262" s="6" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="7" t="n">
+      <c r="A263" s="5" t="n">
         <v>262</v>
       </c>
-      <c r="B263" s="7" t="inlineStr">
-        <is>
-          <t>notif_dzikir_evening</t>
-        </is>
-      </c>
-      <c r="C263" s="7" t="inlineStr">
-        <is>
-          <t>Notifikasi (sistem)</t>
-        </is>
-      </c>
-      <c r="D263" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E263" s="7" t="inlineStr">
-        <is>
-          <t>Sore menjelang. Sejenak untuk menenangkan hati.</t>
-        </is>
-      </c>
-      <c r="F263" s="7" t="inlineStr">
-        <is>
-          <t>Evening is here. A moment to settle your heart.</t>
-        </is>
-      </c>
-      <c r="G263" s="7" t="inlineStr"/>
+      <c r="B263" s="5" t="inlineStr">
+        <is>
+          <t>common_cancel</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>Hapus (sheet)</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>Batal</t>
+        </is>
+      </c>
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+      <c r="G263" s="5" t="inlineStr"/>
       <c r="H263" s="6" t="inlineStr"/>
       <c r="I263" s="6" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="7" t="n">
+      <c r="A264" s="5" t="n">
         <v>263</v>
       </c>
-      <c r="B264" s="7" t="inlineStr">
-        <is>
-          <t>notif_checkin</t>
-        </is>
-      </c>
-      <c r="C264" s="7" t="inlineStr">
-        <is>
-          <t>Notifikasi (sistem)</t>
-        </is>
-      </c>
-      <c r="D264" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E264" s="7" t="inlineStr">
-        <is>
-          <t>Bagaimana harimu? Catat sebentar sebelum istirahat.</t>
-        </is>
-      </c>
-      <c r="F264" s="7" t="inlineStr">
-        <is>
-          <t>How was your day? A quick note before you rest.</t>
-        </is>
-      </c>
-      <c r="G264" s="7" t="inlineStr"/>
+      <c r="B264" s="5" t="inlineStr">
+        <is>
+          <t>unlock_title</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t>Buka dengan PIN</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E264" s="5" t="inlineStr">
+        <is>
+          <t>Masukkan PIN</t>
+        </is>
+      </c>
+      <c r="F264" s="5" t="inlineStr">
+        <is>
+          <t>Enter your PIN</t>
+        </is>
+      </c>
+      <c r="G264" s="5" t="inlineStr"/>
       <c r="H264" s="6" t="inlineStr"/>
       <c r="I264" s="6" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="7" t="n">
+      <c r="A265" s="5" t="n">
         <v>264</v>
       </c>
-      <c r="B265" s="7" t="inlineStr">
-        <is>
-          <t>notif_channel_reminders</t>
-        </is>
-      </c>
-      <c r="C265" s="7" t="inlineStr">
-        <is>
-          <t>Notifikasi (sistem)</t>
-        </is>
-      </c>
-      <c r="D265" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="E265" s="7" t="inlineStr">
-        <is>
-          <t>Pengingat</t>
-        </is>
-      </c>
-      <c r="F265" s="7" t="inlineStr">
-        <is>
-          <t>Reminders</t>
-        </is>
-      </c>
-      <c r="G265" s="7" t="inlineStr">
-        <is>
-          <t>Android notification channel name (visible in system settings).</t>
-        </is>
-      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>unlock_subtitle</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>Buka dengan PIN</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="inlineStr">
+        <is>
+          <t>Assalamu’alaikum. Selamat datang kembali.</t>
+        </is>
+      </c>
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>Assalamu’alaikum. Welcome back.</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr"/>
       <c r="H265" s="6" t="inlineStr"/>
       <c r="I265" s="6" t="inlineStr"/>
     </row>
@@ -9646,12 +9670,12 @@
       </c>
       <c r="B266" s="7" t="inlineStr">
         <is>
-          <t>notif_channel_protect</t>
+          <t>unlock_wrong</t>
         </is>
       </c>
       <c r="C266" s="7" t="inlineStr">
         <is>
-          <t>Notifikasi (sistem)</t>
+          <t>Buka dengan PIN</t>
         </is>
       </c>
       <c r="D266" s="7" t="inlineStr">
@@ -9661,19 +9685,15 @@
       </c>
       <c r="E266" s="7" t="inlineStr">
         <is>
-          <t>Penjagaan aktif</t>
+          <t>PIN salah. Coba lagi.</t>
         </is>
       </c>
       <c r="F266" s="7" t="inlineStr">
         <is>
-          <t>Protection running</t>
-        </is>
-      </c>
-      <c r="G266" s="7" t="inlineStr">
-        <is>
-          <t>Foreground service channel for the blocker.</t>
-        </is>
-      </c>
+          <t>Wrong PIN. Try again.</t>
+        </is>
+      </c>
+      <c r="G266" s="7" t="inlineStr"/>
       <c r="H266" s="6" t="inlineStr"/>
       <c r="I266" s="6" t="inlineStr"/>
     </row>
@@ -9683,12 +9703,12 @@
       </c>
       <c r="B267" s="7" t="inlineStr">
         <is>
-          <t>notif_protect_ongoing</t>
+          <t>unlock_cooldown</t>
         </is>
       </c>
       <c r="C267" s="7" t="inlineStr">
         <is>
-          <t>Notifikasi (sistem)</t>
+          <t>Buka dengan PIN</t>
         </is>
       </c>
       <c r="D267" s="7" t="inlineStr">
@@ -9698,155 +9718,159 @@
       </c>
       <c r="E267" s="7" t="inlineStr">
         <is>
-          <t>Berjalan di latar belakang.</t>
+          <t>Terlalu banyak percobaan. Coba lagi dalam {seconds} detik.</t>
         </is>
       </c>
       <c r="F267" s="7" t="inlineStr">
         <is>
-          <t>Running in the background.</t>
+          <t>Too many tries. Try again in {seconds} seconds.</t>
         </is>
       </c>
       <c r="G267" s="7" t="inlineStr">
         <is>
-          <t>Persistent foreground-service notification. Must stay neutral.</t>
+          <t>After 5 wrong PINs: 30 s cooldown. PLURAL in EN.</t>
         </is>
       </c>
       <c r="H267" s="6" t="inlineStr"/>
       <c r="I267" s="6" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="n">
+      <c r="A268" s="7" t="n">
         <v>267</v>
       </c>
-      <c r="B268" s="5" t="inlineStr">
-        <is>
-          <t>hijri_month_1</t>
-        </is>
-      </c>
-      <c r="C268" s="5" t="inlineStr">
-        <is>
-          <t>Hijri calendar</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E268" s="5" t="inlineStr">
-        <is>
-          <t>Muharram</t>
-        </is>
-      </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>Muharram</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="inlineStr">
-        <is>
-          <t>Used by {hijri}.</t>
-        </is>
-      </c>
+      <c r="B268" s="7" t="inlineStr">
+        <is>
+          <t>unlock_forgot</t>
+        </is>
+      </c>
+      <c r="C268" s="7" t="inlineStr">
+        <is>
+          <t>Buka dengan PIN</t>
+        </is>
+      </c>
+      <c r="D268" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E268" s="7" t="inlineStr">
+        <is>
+          <t>Lupa PIN?</t>
+        </is>
+      </c>
+      <c r="F268" s="7" t="inlineStr">
+        <is>
+          <t>Forgot your PIN?</t>
+        </is>
+      </c>
+      <c r="G268" s="7" t="inlineStr"/>
       <c r="H268" s="6" t="inlineStr"/>
       <c r="I268" s="6" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="5" t="n">
+      <c r="A269" s="7" t="n">
         <v>268</v>
       </c>
-      <c r="B269" s="5" t="inlineStr">
-        <is>
-          <t>hijri_month_2</t>
-        </is>
-      </c>
-      <c r="C269" s="5" t="inlineStr">
-        <is>
-          <t>Hijri calendar</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E269" s="5" t="inlineStr">
-        <is>
-          <t>Safar</t>
-        </is>
-      </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>Safar</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr"/>
+      <c r="B269" s="7" t="inlineStr">
+        <is>
+          <t>unlock_forgot_body</t>
+        </is>
+      </c>
+      <c r="C269" s="7" t="inlineStr">
+        <is>
+          <t>Buka dengan PIN</t>
+        </is>
+      </c>
+      <c r="D269" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E269" s="7" t="inlineStr">
+        <is>
+          <t>Karena akunmu anonim, PIN tidak bisa dipulihkan. Kamu bisa menghapus data dan mulai dari awal, atau memulihkan dari file cadangan.</t>
+        </is>
+      </c>
+      <c r="F269" s="7" t="inlineStr">
+        <is>
+          <t>Your account is anonymous, so the PIN can't be recovered. You can delete your data and start fresh, or restore from a backup file.</t>
+        </is>
+      </c>
+      <c r="G269" s="7" t="inlineStr">
+        <is>
+          <t>Bottom sheet. Buttons reuse delete_sheet_confirm + data_import_cta + common_cancel.</t>
+        </is>
+      </c>
       <c r="H269" s="6" t="inlineStr"/>
       <c r="I269" s="6" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="n">
+      <c r="A270" s="7" t="n">
         <v>269</v>
       </c>
-      <c r="B270" s="5" t="inlineStr">
-        <is>
-          <t>hijri_month_3</t>
-        </is>
-      </c>
-      <c r="C270" s="5" t="inlineStr">
-        <is>
-          <t>Hijri calendar</t>
-        </is>
-      </c>
-      <c r="D270" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E270" s="5" t="inlineStr">
-        <is>
-          <t>Rabiul Awal</t>
-        </is>
-      </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>Rabi‘ al-Awwal</t>
-        </is>
-      </c>
-      <c r="G270" s="5" t="inlineStr"/>
+      <c r="B270" s="7" t="inlineStr">
+        <is>
+          <t>biometric_title</t>
+        </is>
+      </c>
+      <c r="C270" s="7" t="inlineStr">
+        <is>
+          <t>Buka dengan PIN</t>
+        </is>
+      </c>
+      <c r="D270" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E270" s="7" t="inlineStr">
+        <is>
+          <t>Buka Izzah</t>
+        </is>
+      </c>
+      <c r="F270" s="7" t="inlineStr">
+        <is>
+          <t>Unlock Izzah</t>
+        </is>
+      </c>
+      <c r="G270" s="7" t="inlineStr">
+        <is>
+          <t>Title of the system BiometricPrompt. Shows the disguise name if a disguise is active.</t>
+        </is>
+      </c>
       <c r="H270" s="6" t="inlineStr"/>
       <c r="I270" s="6" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="5" t="n">
+      <c r="A271" s="7" t="n">
         <v>270</v>
       </c>
-      <c r="B271" s="5" t="inlineStr">
-        <is>
-          <t>hijri_month_4</t>
-        </is>
-      </c>
-      <c r="C271" s="5" t="inlineStr">
-        <is>
-          <t>Hijri calendar</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E271" s="5" t="inlineStr">
-        <is>
-          <t>Rabiul Akhir</t>
-        </is>
-      </c>
-      <c r="F271" s="5" t="inlineStr">
-        <is>
-          <t>Rabi‘ al-Thani</t>
-        </is>
-      </c>
-      <c r="G271" s="5" t="inlineStr"/>
+      <c r="B271" s="7" t="inlineStr">
+        <is>
+          <t>biometric_use_pin</t>
+        </is>
+      </c>
+      <c r="C271" s="7" t="inlineStr">
+        <is>
+          <t>Buka dengan PIN</t>
+        </is>
+      </c>
+      <c r="D271" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E271" s="7" t="inlineStr">
+        <is>
+          <t>Pakai PIN</t>
+        </is>
+      </c>
+      <c r="F271" s="7" t="inlineStr">
+        <is>
+          <t>Use PIN</t>
+        </is>
+      </c>
+      <c r="G271" s="7" t="inlineStr"/>
       <c r="H271" s="6" t="inlineStr"/>
       <c r="I271" s="6" t="inlineStr"/>
     </row>
@@ -9856,12 +9880,12 @@
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_5</t>
+          <t>notif_prayer_body</t>
         </is>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>Hijri calendar</t>
+          <t>Notifikasi (sistem)</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
@@ -9871,213 +9895,229 @@
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>Jumadil Awal</t>
+          <t>Waktunya {prayer}. Sejenak untuk dirimu.</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>Jumada al-Ula</t>
-        </is>
-      </c>
-      <c r="G272" s="5" t="inlineStr"/>
+          <t>Time for {prayer}. A moment for yourself.</t>
+        </is>
+      </c>
+      <c r="G272" s="5" t="inlineStr">
+        <is>
+          <t>RULE: no notification may mention porn, relapse or addiction.</t>
+        </is>
+      </c>
       <c r="H272" s="6" t="inlineStr"/>
       <c r="I272" s="6" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="5" t="n">
+      <c r="A273" s="7" t="n">
         <v>272</v>
       </c>
-      <c r="B273" s="5" t="inlineStr">
-        <is>
-          <t>hijri_month_6</t>
-        </is>
-      </c>
-      <c r="C273" s="5" t="inlineStr">
-        <is>
-          <t>Hijri calendar</t>
-        </is>
-      </c>
-      <c r="D273" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E273" s="5" t="inlineStr">
-        <is>
-          <t>Jumadil Akhir</t>
-        </is>
-      </c>
-      <c r="F273" s="5" t="inlineStr">
-        <is>
-          <t>Jumada al-Akhirah</t>
-        </is>
-      </c>
-      <c r="G273" s="5" t="inlineStr"/>
+      <c r="B273" s="7" t="inlineStr">
+        <is>
+          <t>notif_dzikir_morning</t>
+        </is>
+      </c>
+      <c r="C273" s="7" t="inlineStr">
+        <is>
+          <t>Notifikasi (sistem)</t>
+        </is>
+      </c>
+      <c r="D273" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E273" s="7" t="inlineStr">
+        <is>
+          <t>Pagi yang baru. Ada waktu sebentar untuk dirimu?</t>
+        </is>
+      </c>
+      <c r="F273" s="7" t="inlineStr">
+        <is>
+          <t>A fresh morning. Got a minute for yourself?</t>
+        </is>
+      </c>
+      <c r="G273" s="7" t="inlineStr"/>
       <c r="H273" s="6" t="inlineStr"/>
       <c r="I273" s="6" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="5" t="n">
+      <c r="A274" s="7" t="n">
         <v>273</v>
       </c>
-      <c r="B274" s="5" t="inlineStr">
-        <is>
-          <t>hijri_month_7</t>
-        </is>
-      </c>
-      <c r="C274" s="5" t="inlineStr">
-        <is>
-          <t>Hijri calendar</t>
-        </is>
-      </c>
-      <c r="D274" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E274" s="5" t="inlineStr">
-        <is>
-          <t>Rajab</t>
-        </is>
-      </c>
-      <c r="F274" s="5" t="inlineStr">
-        <is>
-          <t>Rajab</t>
-        </is>
-      </c>
-      <c r="G274" s="5" t="inlineStr"/>
+      <c r="B274" s="7" t="inlineStr">
+        <is>
+          <t>notif_dzikir_evening</t>
+        </is>
+      </c>
+      <c r="C274" s="7" t="inlineStr">
+        <is>
+          <t>Notifikasi (sistem)</t>
+        </is>
+      </c>
+      <c r="D274" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E274" s="7" t="inlineStr">
+        <is>
+          <t>Sore menjelang. Sejenak untuk menenangkan hati.</t>
+        </is>
+      </c>
+      <c r="F274" s="7" t="inlineStr">
+        <is>
+          <t>Evening is here. A moment to settle your heart.</t>
+        </is>
+      </c>
+      <c r="G274" s="7" t="inlineStr"/>
       <c r="H274" s="6" t="inlineStr"/>
       <c r="I274" s="6" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="5" t="n">
+      <c r="A275" s="7" t="n">
         <v>274</v>
       </c>
-      <c r="B275" s="5" t="inlineStr">
-        <is>
-          <t>hijri_month_8</t>
-        </is>
-      </c>
-      <c r="C275" s="5" t="inlineStr">
-        <is>
-          <t>Hijri calendar</t>
-        </is>
-      </c>
-      <c r="D275" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E275" s="5" t="inlineStr">
-        <is>
-          <t>Sya’ban</t>
-        </is>
-      </c>
-      <c r="F275" s="5" t="inlineStr">
-        <is>
-          <t>Sha‘ban</t>
-        </is>
-      </c>
-      <c r="G275" s="5" t="inlineStr"/>
+      <c r="B275" s="7" t="inlineStr">
+        <is>
+          <t>notif_checkin</t>
+        </is>
+      </c>
+      <c r="C275" s="7" t="inlineStr">
+        <is>
+          <t>Notifikasi (sistem)</t>
+        </is>
+      </c>
+      <c r="D275" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E275" s="7" t="inlineStr">
+        <is>
+          <t>Bagaimana harimu? Catat sebentar sebelum istirahat.</t>
+        </is>
+      </c>
+      <c r="F275" s="7" t="inlineStr">
+        <is>
+          <t>How was your day? A quick note before you rest.</t>
+        </is>
+      </c>
+      <c r="G275" s="7" t="inlineStr"/>
       <c r="H275" s="6" t="inlineStr"/>
       <c r="I275" s="6" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="5" t="n">
+      <c r="A276" s="7" t="n">
         <v>275</v>
       </c>
-      <c r="B276" s="5" t="inlineStr">
-        <is>
-          <t>hijri_month_9</t>
-        </is>
-      </c>
-      <c r="C276" s="5" t="inlineStr">
-        <is>
-          <t>Hijri calendar</t>
-        </is>
-      </c>
-      <c r="D276" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E276" s="5" t="inlineStr">
-        <is>
-          <t>Ramadhan</t>
-        </is>
-      </c>
-      <c r="F276" s="5" t="inlineStr">
-        <is>
-          <t>Ramadan</t>
-        </is>
-      </c>
-      <c r="G276" s="5" t="inlineStr"/>
+      <c r="B276" s="7" t="inlineStr">
+        <is>
+          <t>notif_channel_reminders</t>
+        </is>
+      </c>
+      <c r="C276" s="7" t="inlineStr">
+        <is>
+          <t>Notifikasi (sistem)</t>
+        </is>
+      </c>
+      <c r="D276" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E276" s="7" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="F276" s="7" t="inlineStr">
+        <is>
+          <t>Reminders</t>
+        </is>
+      </c>
+      <c r="G276" s="7" t="inlineStr">
+        <is>
+          <t>Android notification channel name (visible in system settings).</t>
+        </is>
+      </c>
       <c r="H276" s="6" t="inlineStr"/>
       <c r="I276" s="6" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="5" t="n">
+      <c r="A277" s="7" t="n">
         <v>276</v>
       </c>
-      <c r="B277" s="5" t="inlineStr">
-        <is>
-          <t>hijri_month_10</t>
-        </is>
-      </c>
-      <c r="C277" s="5" t="inlineStr">
-        <is>
-          <t>Hijri calendar</t>
-        </is>
-      </c>
-      <c r="D277" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E277" s="5" t="inlineStr">
-        <is>
-          <t>Syawal</t>
-        </is>
-      </c>
-      <c r="F277" s="5" t="inlineStr">
-        <is>
-          <t>Shawwal</t>
-        </is>
-      </c>
-      <c r="G277" s="5" t="inlineStr"/>
+      <c r="B277" s="7" t="inlineStr">
+        <is>
+          <t>notif_channel_protect</t>
+        </is>
+      </c>
+      <c r="C277" s="7" t="inlineStr">
+        <is>
+          <t>Notifikasi (sistem)</t>
+        </is>
+      </c>
+      <c r="D277" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E277" s="7" t="inlineStr">
+        <is>
+          <t>Penjagaan aktif</t>
+        </is>
+      </c>
+      <c r="F277" s="7" t="inlineStr">
+        <is>
+          <t>Protection running</t>
+        </is>
+      </c>
+      <c r="G277" s="7" t="inlineStr">
+        <is>
+          <t>Foreground service channel for the blocker.</t>
+        </is>
+      </c>
       <c r="H277" s="6" t="inlineStr"/>
       <c r="I277" s="6" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="5" t="n">
+      <c r="A278" s="7" t="n">
         <v>277</v>
       </c>
-      <c r="B278" s="5" t="inlineStr">
-        <is>
-          <t>hijri_month_11</t>
-        </is>
-      </c>
-      <c r="C278" s="5" t="inlineStr">
-        <is>
-          <t>Hijri calendar</t>
-        </is>
-      </c>
-      <c r="D278" s="5" t="inlineStr">
-        <is>
-          <t>DESIGN</t>
-        </is>
-      </c>
-      <c r="E278" s="5" t="inlineStr">
-        <is>
-          <t>Dzulqa’dah</t>
-        </is>
-      </c>
-      <c r="F278" s="5" t="inlineStr">
-        <is>
-          <t>Dhu al-Qa‘dah</t>
-        </is>
-      </c>
-      <c r="G278" s="5" t="inlineStr"/>
+      <c r="B278" s="7" t="inlineStr">
+        <is>
+          <t>notif_protect_ongoing</t>
+        </is>
+      </c>
+      <c r="C278" s="7" t="inlineStr">
+        <is>
+          <t>Notifikasi (sistem)</t>
+        </is>
+      </c>
+      <c r="D278" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E278" s="7" t="inlineStr">
+        <is>
+          <t>Berjalan di latar belakang.</t>
+        </is>
+      </c>
+      <c r="F278" s="7" t="inlineStr">
+        <is>
+          <t>Running in the background.</t>
+        </is>
+      </c>
+      <c r="G278" s="7" t="inlineStr">
+        <is>
+          <t>Persistent foreground-service notification. Must stay neutral.</t>
+        </is>
+      </c>
       <c r="H278" s="6" t="inlineStr"/>
       <c r="I278" s="6" t="inlineStr"/>
     </row>
@@ -10087,7 +10127,7 @@
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>hijri_month_12</t>
+          <t>hijri_month_1</t>
         </is>
       </c>
       <c r="C279" s="5" t="inlineStr">
@@ -10102,15 +10142,19 @@
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>Dzulhijjah</t>
+          <t>Muharram</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>Dhu al-Hijjah</t>
-        </is>
-      </c>
-      <c r="G279" s="5" t="inlineStr"/>
+          <t>Muharram</t>
+        </is>
+      </c>
+      <c r="G279" s="5" t="inlineStr">
+        <is>
+          <t>Used by {hijri}.</t>
+        </is>
+      </c>
       <c r="H279" s="6" t="inlineStr"/>
       <c r="I279" s="6" t="inlineStr"/>
     </row>
@@ -10120,7 +10164,7 @@
       </c>
       <c r="B280" s="5" t="inlineStr">
         <is>
-          <t>hijri_suffix</t>
+          <t>hijri_month_2</t>
         </is>
       </c>
       <c r="C280" s="5" t="inlineStr">
@@ -10135,22 +10179,385 @@
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>{day} {month} {year} H</t>
+          <t>Safar</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>{day} {month} {year} AH</t>
+          <t>Safar</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr"/>
       <c r="H280" s="6" t="inlineStr"/>
       <c r="I280" s="6" t="inlineStr"/>
     </row>
+    <row r="281">
+      <c r="A281" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="5" t="inlineStr">
+        <is>
+          <t>hijri_month_3</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="inlineStr">
+        <is>
+          <t>Rabiul Awal</t>
+        </is>
+      </c>
+      <c r="F281" s="5" t="inlineStr">
+        <is>
+          <t>Rabi‘ al-Awwal</t>
+        </is>
+      </c>
+      <c r="G281" s="5" t="inlineStr"/>
+      <c r="H281" s="6" t="inlineStr"/>
+      <c r="I281" s="6" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="5" t="inlineStr">
+        <is>
+          <t>hijri_month_4</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D282" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="inlineStr">
+        <is>
+          <t>Rabiul Akhir</t>
+        </is>
+      </c>
+      <c r="F282" s="5" t="inlineStr">
+        <is>
+          <t>Rabi‘ al-Thani</t>
+        </is>
+      </c>
+      <c r="G282" s="5" t="inlineStr"/>
+      <c r="H282" s="6" t="inlineStr"/>
+      <c r="I282" s="6" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="5" t="inlineStr">
+        <is>
+          <t>hijri_month_5</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="inlineStr">
+        <is>
+          <t>Jumadil Awal</t>
+        </is>
+      </c>
+      <c r="F283" s="5" t="inlineStr">
+        <is>
+          <t>Jumada al-Ula</t>
+        </is>
+      </c>
+      <c r="G283" s="5" t="inlineStr"/>
+      <c r="H283" s="6" t="inlineStr"/>
+      <c r="I283" s="6" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="5" t="inlineStr">
+        <is>
+          <t>hijri_month_6</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D284" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E284" s="5" t="inlineStr">
+        <is>
+          <t>Jumadil Akhir</t>
+        </is>
+      </c>
+      <c r="F284" s="5" t="inlineStr">
+        <is>
+          <t>Jumada al-Akhirah</t>
+        </is>
+      </c>
+      <c r="G284" s="5" t="inlineStr"/>
+      <c r="H284" s="6" t="inlineStr"/>
+      <c r="I284" s="6" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="5" t="inlineStr">
+        <is>
+          <t>hijri_month_7</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D285" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="inlineStr">
+        <is>
+          <t>Rajab</t>
+        </is>
+      </c>
+      <c r="F285" s="5" t="inlineStr">
+        <is>
+          <t>Rajab</t>
+        </is>
+      </c>
+      <c r="G285" s="5" t="inlineStr"/>
+      <c r="H285" s="6" t="inlineStr"/>
+      <c r="I285" s="6" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="5" t="inlineStr">
+        <is>
+          <t>hijri_month_8</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D286" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E286" s="5" t="inlineStr">
+        <is>
+          <t>Sya’ban</t>
+        </is>
+      </c>
+      <c r="F286" s="5" t="inlineStr">
+        <is>
+          <t>Sha‘ban</t>
+        </is>
+      </c>
+      <c r="G286" s="5" t="inlineStr"/>
+      <c r="H286" s="6" t="inlineStr"/>
+      <c r="I286" s="6" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="5" t="inlineStr">
+        <is>
+          <t>hijri_month_9</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D287" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="inlineStr">
+        <is>
+          <t>Ramadhan</t>
+        </is>
+      </c>
+      <c r="F287" s="5" t="inlineStr">
+        <is>
+          <t>Ramadan</t>
+        </is>
+      </c>
+      <c r="G287" s="5" t="inlineStr"/>
+      <c r="H287" s="6" t="inlineStr"/>
+      <c r="I287" s="6" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="5" t="inlineStr">
+        <is>
+          <t>hijri_month_10</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D288" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="inlineStr">
+        <is>
+          <t>Syawal</t>
+        </is>
+      </c>
+      <c r="F288" s="5" t="inlineStr">
+        <is>
+          <t>Shawwal</t>
+        </is>
+      </c>
+      <c r="G288" s="5" t="inlineStr"/>
+      <c r="H288" s="6" t="inlineStr"/>
+      <c r="I288" s="6" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="5" t="inlineStr">
+        <is>
+          <t>hijri_month_11</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D289" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="inlineStr">
+        <is>
+          <t>Dzulqa’dah</t>
+        </is>
+      </c>
+      <c r="F289" s="5" t="inlineStr">
+        <is>
+          <t>Dhu al-Qa‘dah</t>
+        </is>
+      </c>
+      <c r="G289" s="5" t="inlineStr"/>
+      <c r="H289" s="6" t="inlineStr"/>
+      <c r="I289" s="6" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="5" t="inlineStr">
+        <is>
+          <t>hijri_month_12</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D290" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="inlineStr">
+        <is>
+          <t>Dzulhijjah</t>
+        </is>
+      </c>
+      <c r="F290" s="5" t="inlineStr">
+        <is>
+          <t>Dhu al-Hijjah</t>
+        </is>
+      </c>
+      <c r="G290" s="5" t="inlineStr"/>
+      <c r="H290" s="6" t="inlineStr"/>
+      <c r="I290" s="6" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="5" t="inlineStr">
+        <is>
+          <t>hijri_suffix</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t>Hijri calendar</t>
+        </is>
+      </c>
+      <c r="D291" s="5" t="inlineStr">
+        <is>
+          <t>DESIGN</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="inlineStr">
+        <is>
+          <t>{day} {month} {year} H</t>
+        </is>
+      </c>
+      <c r="F291" s="5" t="inlineStr">
+        <is>
+          <t>{day} {month} {year} AH</t>
+        </is>
+      </c>
+      <c r="G291" s="5" t="inlineStr"/>
+      <c r="H291" s="6" t="inlineStr"/>
+      <c r="I291" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I280"/>
+  <autoFilter ref="A1:I291"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H280" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H291" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,Revisi,Hapus"</formula1>
     </dataValidation>
   </dataValidations>
